--- a/xlsx/dre/DRE_07_2026.xlsx
+++ b/xlsx/dre/DRE_07_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10012" uniqueCount="1147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10012" uniqueCount="1148">
   <si>
     <t>Movimentações Financeiras</t>
   </si>
@@ -1771,75 +1771,75 @@
     <t>R$ 11.982,47</t>
   </si>
   <si>
+    <t>R$  941,73</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>R$  491,99</t>
+  </si>
+  <si>
+    <t>R$  411,87</t>
+  </si>
+  <si>
+    <t>R$  1.440,23</t>
+  </si>
+  <si>
+    <t>91201/2</t>
+  </si>
+  <si>
+    <t>Jose Carlos de Carvalho</t>
+  </si>
+  <si>
+    <t>84401/1</t>
+  </si>
+  <si>
+    <t>R$  164,57</t>
+  </si>
+  <si>
+    <t>84401CamilaFS</t>
+  </si>
+  <si>
+    <t>85201/1</t>
+  </si>
+  <si>
+    <t>R$  2.451,16</t>
+  </si>
+  <si>
+    <t>85201BRUNOAL</t>
+  </si>
+  <si>
+    <t>R$  252,95</t>
+  </si>
+  <si>
+    <t>R$  584,82</t>
+  </si>
+  <si>
+    <t>R$  1.698,42</t>
+  </si>
+  <si>
     <t>R$  622,81</t>
   </si>
   <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>R$  491,99</t>
-  </si>
-  <si>
-    <t>Jose Carlos de Carvalho</t>
-  </si>
-  <si>
-    <t>84401/1</t>
-  </si>
-  <si>
-    <t>R$  164,57</t>
-  </si>
-  <si>
-    <t>84401CamilaFS</t>
-  </si>
-  <si>
-    <t>85201/1</t>
-  </si>
-  <si>
-    <t>R$  2.451,16</t>
-  </si>
-  <si>
-    <t>85201BRUNOAL</t>
-  </si>
-  <si>
-    <t>R$  1.440,23</t>
-  </si>
-  <si>
-    <t>91201/2</t>
-  </si>
-  <si>
-    <t>R$  411,87</t>
-  </si>
-  <si>
-    <t>R$  252,95</t>
+    <t>R$  471,77</t>
+  </si>
+  <si>
+    <t>88101/2</t>
+  </si>
+  <si>
+    <t>R$  620,43</t>
   </si>
   <si>
     <t>90001/2</t>
   </si>
   <si>
-    <t>R$  620,43</t>
-  </si>
-  <si>
-    <t>R$  941,73</t>
-  </si>
-  <si>
-    <t>R$  584,82</t>
-  </si>
-  <si>
     <t>R$  213,83</t>
   </si>
   <si>
-    <t>88101/2</t>
-  </si>
-  <si>
     <t>86102/2</t>
   </si>
   <si>
-    <t>R$  471,77</t>
-  </si>
-  <si>
-    <t>R$  1.698,42</t>
-  </si>
-  <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
   </si>
   <si>
@@ -2270,6 +2270,9 @@
   </si>
   <si>
     <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
   </si>
   <si>
     <t>R$  2.365,00</t>
@@ -18264,7 +18267,7 @@
         <v>33</v>
       </c>
       <c r="E277" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F277" t="s">
         <v>497</v>
@@ -18279,10 +18282,10 @@
         <v>583</v>
       </c>
       <c r="J277" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="K277" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="L277" t="s">
         <v>34</v>
@@ -18376,25 +18379,25 @@
         <v>34</v>
       </c>
       <c r="E279" t="s">
-        <v>258</v>
+        <v>413</v>
       </c>
       <c r="F279" t="s">
-        <v>243</v>
+        <v>497</v>
       </c>
       <c r="G279" t="s">
         <v>40</v>
       </c>
       <c r="H279" t="s">
+        <v>236</v>
+      </c>
+      <c r="I279" t="s">
         <v>586</v>
       </c>
-      <c r="I279" t="s">
-        <v>477</v>
-      </c>
       <c r="J279" t="s">
-        <v>330</v>
+        <v>59</v>
       </c>
       <c r="K279" t="s">
-        <v>247</v>
+        <v>59</v>
       </c>
       <c r="L279" t="s">
         <v>34</v>
@@ -18406,13 +18409,13 @@
         <v>46</v>
       </c>
       <c r="O279" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="P279" t="s">
-        <v>477</v>
+        <v>34</v>
       </c>
       <c r="Q279" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R279" t="s">
         <v>34</v>
@@ -18432,25 +18435,25 @@
         <v>34</v>
       </c>
       <c r="E280" t="s">
+        <v>417</v>
+      </c>
+      <c r="F280" t="s">
+        <v>497</v>
+      </c>
+      <c r="G280" t="s">
+        <v>40</v>
+      </c>
+      <c r="H280" t="s">
+        <v>236</v>
+      </c>
+      <c r="I280" t="s">
         <v>587</v>
       </c>
-      <c r="F280" t="s">
-        <v>243</v>
-      </c>
-      <c r="G280" t="s">
-        <v>40</v>
-      </c>
-      <c r="H280" t="s">
-        <v>539</v>
-      </c>
-      <c r="I280" t="s">
-        <v>588</v>
-      </c>
       <c r="J280" t="s">
-        <v>330</v>
+        <v>59</v>
       </c>
       <c r="K280" t="s">
-        <v>247</v>
+        <v>59</v>
       </c>
       <c r="L280" t="s">
         <v>34</v>
@@ -18462,13 +18465,13 @@
         <v>46</v>
       </c>
       <c r="O280" t="s">
-        <v>589</v>
+        <v>34</v>
       </c>
       <c r="P280" t="s">
-        <v>588</v>
+        <v>34</v>
       </c>
       <c r="Q280" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R280" t="s">
         <v>34</v>
@@ -18488,25 +18491,25 @@
         <v>34</v>
       </c>
       <c r="E281" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F281" t="s">
-        <v>243</v>
+        <v>497</v>
       </c>
       <c r="G281" t="s">
         <v>40</v>
       </c>
       <c r="H281" t="s">
-        <v>539</v>
+        <v>236</v>
       </c>
       <c r="I281" t="s">
-        <v>591</v>
+        <v>566</v>
       </c>
       <c r="J281" t="s">
-        <v>330</v>
+        <v>58</v>
       </c>
       <c r="K281" t="s">
-        <v>247</v>
+        <v>58</v>
       </c>
       <c r="L281" t="s">
         <v>34</v>
@@ -18518,13 +18521,13 @@
         <v>46</v>
       </c>
       <c r="O281" t="s">
-        <v>592</v>
+        <v>34</v>
       </c>
       <c r="P281" t="s">
-        <v>591</v>
+        <v>34</v>
       </c>
       <c r="Q281" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R281" t="s">
         <v>34</v>
@@ -18544,25 +18547,25 @@
         <v>34</v>
       </c>
       <c r="E282" t="s">
-        <v>417</v>
+        <v>300</v>
       </c>
       <c r="F282" t="s">
-        <v>497</v>
+        <v>243</v>
       </c>
       <c r="G282" t="s">
         <v>40</v>
       </c>
       <c r="H282" t="s">
-        <v>236</v>
+        <v>578</v>
       </c>
       <c r="I282" t="s">
-        <v>593</v>
+        <v>496</v>
       </c>
       <c r="J282" t="s">
-        <v>59</v>
+        <v>307</v>
       </c>
       <c r="K282" t="s">
-        <v>59</v>
+        <v>247</v>
       </c>
       <c r="L282" t="s">
         <v>34</v>
@@ -18574,13 +18577,13 @@
         <v>46</v>
       </c>
       <c r="O282" t="s">
-        <v>34</v>
+        <v>303</v>
       </c>
       <c r="P282" t="s">
-        <v>34</v>
+        <v>496</v>
       </c>
       <c r="Q282" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R282" t="s">
         <v>34</v>
@@ -18600,25 +18603,25 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>594</v>
+        <v>258</v>
       </c>
       <c r="F283" t="s">
-        <v>497</v>
+        <v>243</v>
       </c>
       <c r="G283" t="s">
         <v>40</v>
       </c>
       <c r="H283" t="s">
-        <v>236</v>
+        <v>589</v>
       </c>
       <c r="I283" t="s">
-        <v>566</v>
+        <v>477</v>
       </c>
       <c r="J283" t="s">
-        <v>58</v>
+        <v>330</v>
       </c>
       <c r="K283" t="s">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="L283" t="s">
         <v>34</v>
@@ -18630,13 +18633,13 @@
         <v>46</v>
       </c>
       <c r="O283" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="P283" t="s">
-        <v>34</v>
+        <v>477</v>
       </c>
       <c r="Q283" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R283" t="s">
         <v>34</v>
@@ -18656,7 +18659,7 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>293</v>
+        <v>590</v>
       </c>
       <c r="F284" t="s">
         <v>243</v>
@@ -18668,10 +18671,10 @@
         <v>539</v>
       </c>
       <c r="I284" t="s">
-        <v>490</v>
+        <v>591</v>
       </c>
       <c r="J284" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="K284" t="s">
         <v>247</v>
@@ -18686,10 +18689,10 @@
         <v>46</v>
       </c>
       <c r="O284" t="s">
-        <v>70</v>
+        <v>592</v>
       </c>
       <c r="P284" t="s">
-        <v>490</v>
+        <v>591</v>
       </c>
       <c r="Q284" t="s">
         <v>46</v>
@@ -18712,7 +18715,7 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>279</v>
+        <v>593</v>
       </c>
       <c r="F285" t="s">
         <v>243</v>
@@ -18724,13 +18727,13 @@
         <v>539</v>
       </c>
       <c r="I285" t="s">
-        <v>495</v>
+        <v>594</v>
       </c>
       <c r="J285" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="K285" t="s">
-        <v>59</v>
+        <v>247</v>
       </c>
       <c r="L285" t="s">
         <v>34</v>
@@ -18742,10 +18745,10 @@
         <v>46</v>
       </c>
       <c r="O285" t="s">
-        <v>281</v>
+        <v>595</v>
       </c>
       <c r="P285" t="s">
-        <v>495</v>
+        <v>594</v>
       </c>
       <c r="Q285" t="s">
         <v>46</v>
@@ -18768,22 +18771,22 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>413</v>
+        <v>279</v>
       </c>
       <c r="F286" t="s">
-        <v>497</v>
+        <v>243</v>
       </c>
       <c r="G286" t="s">
         <v>40</v>
       </c>
       <c r="H286" t="s">
-        <v>236</v>
+        <v>539</v>
       </c>
       <c r="I286" t="s">
-        <v>595</v>
+        <v>495</v>
       </c>
       <c r="J286" t="s">
-        <v>59</v>
+        <v>307</v>
       </c>
       <c r="K286" t="s">
         <v>59</v>
@@ -18798,13 +18801,13 @@
         <v>46</v>
       </c>
       <c r="O286" t="s">
-        <v>34</v>
+        <v>281</v>
       </c>
       <c r="P286" t="s">
-        <v>34</v>
+        <v>495</v>
       </c>
       <c r="Q286" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R286" t="s">
         <v>34</v>
@@ -18824,22 +18827,22 @@
         <v>34</v>
       </c>
       <c r="E287" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="F287" t="s">
-        <v>497</v>
+        <v>243</v>
       </c>
       <c r="G287" t="s">
         <v>40</v>
       </c>
       <c r="H287" t="s">
-        <v>584</v>
+        <v>539</v>
       </c>
       <c r="I287" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="J287" t="s">
-        <v>59</v>
+        <v>307</v>
       </c>
       <c r="K287" t="s">
         <v>247</v>
@@ -18854,13 +18857,13 @@
         <v>46</v>
       </c>
       <c r="O287" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="P287" t="s">
-        <v>34</v>
+        <v>490</v>
       </c>
       <c r="Q287" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R287" t="s">
         <v>34</v>
@@ -18880,7 +18883,7 @@
         <v>34</v>
       </c>
       <c r="E288" t="s">
-        <v>300</v>
+        <v>249</v>
       </c>
       <c r="F288" t="s">
         <v>243</v>
@@ -18892,7 +18895,7 @@
         <v>578</v>
       </c>
       <c r="I288" t="s">
-        <v>496</v>
+        <v>596</v>
       </c>
       <c r="J288" t="s">
         <v>307</v>
@@ -18910,10 +18913,10 @@
         <v>46</v>
       </c>
       <c r="O288" t="s">
-        <v>303</v>
+        <v>251</v>
       </c>
       <c r="P288" t="s">
-        <v>496</v>
+        <v>596</v>
       </c>
       <c r="Q288" t="s">
         <v>46</v>
@@ -18936,22 +18939,22 @@
         <v>34</v>
       </c>
       <c r="E289" t="s">
-        <v>249</v>
+        <v>313</v>
       </c>
       <c r="F289" t="s">
-        <v>243</v>
+        <v>497</v>
       </c>
       <c r="G289" t="s">
         <v>40</v>
       </c>
       <c r="H289" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="I289" t="s">
-        <v>596</v>
+        <v>484</v>
       </c>
       <c r="J289" t="s">
-        <v>307</v>
+        <v>59</v>
       </c>
       <c r="K289" t="s">
         <v>247</v>
@@ -18966,13 +18969,13 @@
         <v>46</v>
       </c>
       <c r="O289" t="s">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="P289" t="s">
-        <v>596</v>
+        <v>34</v>
       </c>
       <c r="Q289" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R289" t="s">
         <v>34</v>
@@ -18992,7 +18995,7 @@
         <v>34</v>
       </c>
       <c r="E290" t="s">
-        <v>597</v>
+        <v>396</v>
       </c>
       <c r="F290" t="s">
         <v>497</v>
@@ -19001,16 +19004,16 @@
         <v>40</v>
       </c>
       <c r="H290" t="s">
-        <v>236</v>
+        <v>584</v>
       </c>
       <c r="I290" t="s">
-        <v>560</v>
+        <v>597</v>
       </c>
       <c r="J290" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K290" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="L290" t="s">
         <v>34</v>
@@ -19048,7 +19051,7 @@
         <v>34</v>
       </c>
       <c r="E291" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="F291" t="s">
         <v>497</v>
@@ -19057,16 +19060,16 @@
         <v>40</v>
       </c>
       <c r="H291" t="s">
-        <v>578</v>
+        <v>236</v>
       </c>
       <c r="I291" t="s">
         <v>598</v>
       </c>
       <c r="J291" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="K291" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="L291" t="s">
         <v>34</v>
@@ -19104,7 +19107,7 @@
         <v>34</v>
       </c>
       <c r="E292" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F292" t="s">
         <v>497</v>
@@ -19119,10 +19122,10 @@
         <v>599</v>
       </c>
       <c r="J292" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="K292" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="L292" t="s">
         <v>34</v>
@@ -19160,7 +19163,7 @@
         <v>34</v>
       </c>
       <c r="E293" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F293" t="s">
         <v>497</v>
@@ -19169,16 +19172,16 @@
         <v>40</v>
       </c>
       <c r="H293" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="I293" t="s">
         <v>600</v>
       </c>
       <c r="J293" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="K293" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="L293" t="s">
         <v>34</v>
@@ -19216,7 +19219,7 @@
         <v>34</v>
       </c>
       <c r="E294" t="s">
-        <v>295</v>
+        <v>601</v>
       </c>
       <c r="F294" t="s">
         <v>497</v>
@@ -19225,16 +19228,16 @@
         <v>40</v>
       </c>
       <c r="H294" t="s">
-        <v>586</v>
+        <v>236</v>
       </c>
       <c r="I294" t="s">
-        <v>601</v>
+        <v>563</v>
       </c>
       <c r="J294" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="K294" t="s">
-        <v>247</v>
+        <v>74</v>
       </c>
       <c r="L294" t="s">
         <v>34</v>
@@ -19272,7 +19275,7 @@
         <v>34</v>
       </c>
       <c r="E295" t="s">
-        <v>602</v>
+        <v>382</v>
       </c>
       <c r="F295" t="s">
         <v>497</v>
@@ -19281,10 +19284,10 @@
         <v>40</v>
       </c>
       <c r="H295" t="s">
-        <v>236</v>
+        <v>578</v>
       </c>
       <c r="I295" t="s">
-        <v>563</v>
+        <v>602</v>
       </c>
       <c r="J295" t="s">
         <v>74</v>
@@ -19340,13 +19343,13 @@
         <v>236</v>
       </c>
       <c r="I296" t="s">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="J296" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K296" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L296" t="s">
         <v>34</v>
@@ -19384,7 +19387,7 @@
         <v>34</v>
       </c>
       <c r="E297" t="s">
-        <v>392</v>
+        <v>295</v>
       </c>
       <c r="F297" t="s">
         <v>497</v>
@@ -19393,16 +19396,16 @@
         <v>40</v>
       </c>
       <c r="H297" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="I297" t="s">
         <v>604</v>
       </c>
       <c r="J297" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="K297" t="s">
-        <v>132</v>
+        <v>247</v>
       </c>
       <c r="L297" t="s">
         <v>34</v>
@@ -19440,7 +19443,7 @@
         <v>34</v>
       </c>
       <c r="E298" t="s">
-        <v>388</v>
+        <v>605</v>
       </c>
       <c r="F298" t="s">
         <v>497</v>
@@ -19452,13 +19455,13 @@
         <v>236</v>
       </c>
       <c r="I298" t="s">
-        <v>605</v>
+        <v>541</v>
       </c>
       <c r="J298" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="K298" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="L298" t="s">
         <v>34</v>
@@ -24265,10 +24268,10 @@
         <v>40</v>
       </c>
       <c r="H384" t="s">
-        <v>556</v>
+        <v>750</v>
       </c>
       <c r="I384" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="J384" t="s">
         <v>712</v>
@@ -24277,7 +24280,7 @@
         <v>363</v>
       </c>
       <c r="L384" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="M384" t="s">
         <v>743</v>
@@ -24289,7 +24292,7 @@
         <v>47</v>
       </c>
       <c r="P384" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="Q384" t="s">
         <v>46</v>
@@ -24321,10 +24324,10 @@
         <v>40</v>
       </c>
       <c r="H385" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="I385" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="J385" t="s">
         <v>712</v>
@@ -24333,7 +24336,7 @@
         <v>363</v>
       </c>
       <c r="L385" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="M385" t="s">
         <v>743</v>
@@ -24345,7 +24348,7 @@
         <v>47</v>
       </c>
       <c r="P385" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="Q385" t="s">
         <v>46</v>
@@ -24368,7 +24371,7 @@
         <v>34</v>
       </c>
       <c r="E386" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F386" t="s">
         <v>39</v>
@@ -24377,10 +24380,10 @@
         <v>40</v>
       </c>
       <c r="H386" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="I386" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="J386" t="s">
         <v>318</v>
@@ -24401,7 +24404,7 @@
         <v>47</v>
       </c>
       <c r="P386" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="Q386" t="s">
         <v>46</v>
@@ -24436,16 +24439,16 @@
         <v>539</v>
       </c>
       <c r="I387" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="J387" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K387" t="s">
         <v>363</v>
       </c>
       <c r="L387" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="M387" t="s">
         <v>743</v>
@@ -24457,7 +24460,7 @@
         <v>47</v>
       </c>
       <c r="P387" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="Q387" t="s">
         <v>46</v>
@@ -24492,16 +24495,16 @@
         <v>473</v>
       </c>
       <c r="I388" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="J388" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="K388" t="s">
         <v>363</v>
       </c>
       <c r="L388" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M388" t="s">
         <v>743</v>
@@ -24513,7 +24516,7 @@
         <v>47</v>
       </c>
       <c r="P388" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="Q388" t="s">
         <v>46</v>
@@ -24536,7 +24539,7 @@
         <v>34</v>
       </c>
       <c r="E389" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F389" t="s">
         <v>39</v>
@@ -24545,13 +24548,13 @@
         <v>40</v>
       </c>
       <c r="H389" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="I389" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="J389" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="K389" t="s">
         <v>97</v>
@@ -24569,7 +24572,7 @@
         <v>47</v>
       </c>
       <c r="P389" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="Q389" t="s">
         <v>46</v>
@@ -24592,7 +24595,7 @@
         <v>34</v>
       </c>
       <c r="E390" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="F390" t="s">
         <v>39</v>
@@ -24604,7 +24607,7 @@
         <v>527</v>
       </c>
       <c r="I390" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="J390" t="s">
         <v>318</v>
@@ -24625,7 +24628,7 @@
         <v>47</v>
       </c>
       <c r="P390" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="Q390" t="s">
         <v>46</v>
@@ -24660,16 +24663,16 @@
         <v>543</v>
       </c>
       <c r="I391" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="J391" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K391" t="s">
         <v>363</v>
       </c>
       <c r="L391" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M391" t="s">
         <v>743</v>
@@ -24681,7 +24684,7 @@
         <v>47</v>
       </c>
       <c r="P391" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="Q391" t="s">
         <v>46</v>
@@ -24713,10 +24716,10 @@
         <v>40</v>
       </c>
       <c r="H392" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="I392" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="J392" t="s">
         <v>712</v>
@@ -24725,7 +24728,7 @@
         <v>363</v>
       </c>
       <c r="L392" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="M392" t="s">
         <v>743</v>
@@ -24737,7 +24740,7 @@
         <v>47</v>
       </c>
       <c r="P392" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="Q392" t="s">
         <v>46</v>
@@ -24760,7 +24763,7 @@
         <v>34</v>
       </c>
       <c r="E393" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="F393" t="s">
         <v>39</v>
@@ -24775,7 +24778,7 @@
         <v>122</v>
       </c>
       <c r="J393" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="K393" t="s">
         <v>318</v>
@@ -24825,7 +24828,7 @@
         <v>40</v>
       </c>
       <c r="H394" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="I394" t="s">
         <v>122</v>
@@ -24837,7 +24840,7 @@
         <v>363</v>
       </c>
       <c r="L394" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M394" t="s">
         <v>743</v>
@@ -24881,10 +24884,10 @@
         <v>40</v>
       </c>
       <c r="H395" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="I395" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J395" t="s">
         <v>712</v>
@@ -24893,7 +24896,7 @@
         <v>363</v>
       </c>
       <c r="L395" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="M395" t="s">
         <v>743</v>
@@ -24905,7 +24908,7 @@
         <v>47</v>
       </c>
       <c r="P395" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="Q395" t="s">
         <v>46</v>
@@ -24916,13 +24919,13 @@
     </row>
     <row r="396">
       <c r="A396" t="s" s="1">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B396" t="s" s="1">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C396" t="s" s="1">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D396" t="s" s="1">
         <v>33</v>
@@ -24972,13 +24975,13 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
+        <v>783</v>
+      </c>
+      <c r="B397" t="s">
         <v>782</v>
       </c>
-      <c r="B397" t="s">
-        <v>781</v>
-      </c>
       <c r="C397" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D397" t="s">
         <v>33</v>
@@ -25005,10 +25008,10 @@
         <v>132</v>
       </c>
       <c r="L397" t="s">
+        <v>784</v>
+      </c>
+      <c r="M397" t="s">
         <v>783</v>
-      </c>
-      <c r="M397" t="s">
-        <v>782</v>
       </c>
       <c r="N397" t="s">
         <v>46</v>
@@ -25028,13 +25031,13 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="1">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B398" t="s" s="1">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C398" t="s" s="1">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D398" t="s" s="1">
         <v>33</v>
@@ -25084,13 +25087,13 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
+        <v>787</v>
+      </c>
+      <c r="B399" t="s">
         <v>786</v>
       </c>
-      <c r="B399" t="s">
-        <v>785</v>
-      </c>
       <c r="C399" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D399" t="s">
         <v>33</v>
@@ -25117,10 +25120,10 @@
         <v>132</v>
       </c>
       <c r="L399" t="s">
+        <v>788</v>
+      </c>
+      <c r="M399" t="s">
         <v>787</v>
-      </c>
-      <c r="M399" t="s">
-        <v>786</v>
       </c>
       <c r="N399" t="s">
         <v>46</v>
@@ -25140,13 +25143,13 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="1">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B400" t="s" s="1">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C400" t="s" s="1">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D400" t="s" s="1">
         <v>33</v>
@@ -25196,13 +25199,13 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B401" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C401" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D401" t="s">
         <v>33</v>
@@ -25217,10 +25220,10 @@
         <v>40</v>
       </c>
       <c r="H401" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="I401" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="J401" t="s">
         <v>210</v>
@@ -25229,10 +25232,10 @@
         <v>132</v>
       </c>
       <c r="L401" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M401" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="N401" t="s">
         <v>46</v>
@@ -25241,7 +25244,7 @@
         <v>47</v>
       </c>
       <c r="P401" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="Q401" t="s">
         <v>46</v>
@@ -25252,19 +25255,19 @@
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B402" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C402" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D402" t="s">
         <v>33</v>
       </c>
       <c r="E402" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="F402" t="s">
         <v>39</v>
@@ -25273,10 +25276,10 @@
         <v>40</v>
       </c>
       <c r="H402" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="I402" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="J402" t="s">
         <v>91</v>
@@ -25285,10 +25288,10 @@
         <v>43</v>
       </c>
       <c r="L402" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M402" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="N402" t="s">
         <v>46</v>
@@ -25297,7 +25300,7 @@
         <v>47</v>
       </c>
       <c r="P402" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="Q402" t="s">
         <v>46</v>
@@ -25308,13 +25311,13 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="1">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B403" t="s" s="1">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C403" t="s" s="1">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D403" t="s" s="1">
         <v>33</v>
@@ -25364,19 +25367,19 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B404" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C404" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D404" t="s">
         <v>33</v>
       </c>
       <c r="E404" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F404" t="s">
         <v>688</v>
@@ -25388,7 +25391,7 @@
         <v>236</v>
       </c>
       <c r="I404" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="J404" t="s">
         <v>210</v>
@@ -25400,7 +25403,7 @@
         <v>34</v>
       </c>
       <c r="M404" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="N404" t="s">
         <v>46</v>
@@ -25420,7 +25423,7 @@
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B405" t="s">
         <v>34</v>
@@ -25444,7 +25447,7 @@
         <v>236</v>
       </c>
       <c r="I405" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="J405" t="s">
         <v>210</v>
@@ -25456,7 +25459,7 @@
         <v>34</v>
       </c>
       <c r="M405" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="N405" t="s">
         <v>46</v>
@@ -25476,19 +25479,19 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B406" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C406" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D406" t="s">
         <v>33</v>
       </c>
       <c r="E406" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F406" t="s">
         <v>39</v>
@@ -25497,10 +25500,10 @@
         <v>40</v>
       </c>
       <c r="H406" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="I406" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="J406" t="s">
         <v>58</v>
@@ -25509,10 +25512,10 @@
         <v>156</v>
       </c>
       <c r="L406" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="M406" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N406" t="s">
         <v>46</v>
@@ -25521,7 +25524,7 @@
         <v>47</v>
       </c>
       <c r="P406" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="Q406" t="s">
         <v>46</v>
@@ -25532,13 +25535,13 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="1">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B407" t="s" s="1">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C407" t="s" s="1">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D407" t="s" s="1">
         <v>33</v>
@@ -25588,13 +25591,13 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="1">
+        <v>816</v>
+      </c>
+      <c r="B408" t="s" s="1">
         <v>815</v>
       </c>
-      <c r="B408" t="s" s="1">
-        <v>814</v>
-      </c>
       <c r="C408" t="s" s="1">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D408" t="s" s="1">
         <v>33</v>
@@ -25644,19 +25647,19 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B409" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C409" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D409" t="s">
         <v>33</v>
       </c>
       <c r="E409" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F409" t="s">
         <v>39</v>
@@ -25668,7 +25671,7 @@
         <v>473</v>
       </c>
       <c r="I409" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="J409" t="s">
         <v>318</v>
@@ -25680,7 +25683,7 @@
         <v>34</v>
       </c>
       <c r="M409" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="N409" t="s">
         <v>46</v>
@@ -25689,7 +25692,7 @@
         <v>47</v>
       </c>
       <c r="P409" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="Q409" t="s">
         <v>46</v>
@@ -25700,7 +25703,7 @@
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B410" t="s">
         <v>34</v>
@@ -25712,7 +25715,7 @@
         <v>34</v>
       </c>
       <c r="E410" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F410" t="s">
         <v>39</v>
@@ -25724,7 +25727,7 @@
         <v>535</v>
       </c>
       <c r="I410" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="J410" t="s">
         <v>318</v>
@@ -25736,7 +25739,7 @@
         <v>34</v>
       </c>
       <c r="M410" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="N410" t="s">
         <v>46</v>
@@ -25745,7 +25748,7 @@
         <v>47</v>
       </c>
       <c r="P410" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="Q410" t="s">
         <v>46</v>
@@ -25756,13 +25759,13 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="1">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B411" t="s" s="1">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C411" t="s" s="1">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D411" t="s" s="1">
         <v>33</v>
@@ -25812,13 +25815,13 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="1">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B412" t="s" s="1">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C412" t="s" s="1">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D412" t="s" s="1">
         <v>33</v>
@@ -25868,19 +25871,19 @@
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B413" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C413" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D413" t="s">
         <v>33</v>
       </c>
       <c r="E413" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F413" t="s">
         <v>207</v>
@@ -25889,10 +25892,10 @@
         <v>40</v>
       </c>
       <c r="H413" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="I413" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="J413" t="s">
         <v>712</v>
@@ -25901,10 +25904,10 @@
         <v>318</v>
       </c>
       <c r="L413" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="M413" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N413" t="s">
         <v>46</v>
@@ -25913,7 +25916,7 @@
         <v>47</v>
       </c>
       <c r="P413" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="Q413" t="s">
         <v>46</v>
@@ -25924,19 +25927,19 @@
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B414" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C414" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D414" t="s">
         <v>33</v>
       </c>
       <c r="E414" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F414" t="s">
         <v>39</v>
@@ -25948,7 +25951,7 @@
         <v>196</v>
       </c>
       <c r="I414" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="J414" t="s">
         <v>74</v>
@@ -25960,7 +25963,7 @@
         <v>34</v>
       </c>
       <c r="M414" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="N414" t="s">
         <v>46</v>
@@ -25969,7 +25972,7 @@
         <v>47</v>
       </c>
       <c r="P414" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="Q414" t="s">
         <v>46</v>
@@ -25980,13 +25983,13 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="1">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B415" t="s" s="1">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C415" t="s" s="1">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D415" t="s" s="1">
         <v>33</v>
@@ -26036,19 +26039,19 @@
     </row>
     <row r="416">
       <c r="A416" t="s">
+        <v>838</v>
+      </c>
+      <c r="B416" t="s">
         <v>837</v>
       </c>
-      <c r="B416" t="s">
-        <v>836</v>
-      </c>
       <c r="C416" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D416" t="s">
         <v>33</v>
       </c>
       <c r="E416" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="F416" t="s">
         <v>207</v>
@@ -26057,22 +26060,22 @@
         <v>40</v>
       </c>
       <c r="H416" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="I416" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="J416" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="K416" t="s">
         <v>666</v>
       </c>
       <c r="L416" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M416" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="N416" t="s">
         <v>46</v>
@@ -26081,7 +26084,7 @@
         <v>47</v>
       </c>
       <c r="P416" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="Q416" t="s">
         <v>46</v>
@@ -26092,13 +26095,13 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="1">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B417" t="s" s="1">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C417" t="s" s="1">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D417" t="s" s="1">
         <v>33</v>
@@ -26148,13 +26151,13 @@
     </row>
     <row r="418">
       <c r="A418" t="s">
+        <v>846</v>
+      </c>
+      <c r="B418" t="s">
         <v>845</v>
       </c>
-      <c r="B418" t="s">
-        <v>844</v>
-      </c>
       <c r="C418" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D418" t="s">
         <v>33</v>
@@ -26169,10 +26172,10 @@
         <v>40</v>
       </c>
       <c r="H418" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="I418" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="J418" t="s">
         <v>712</v>
@@ -26181,10 +26184,10 @@
         <v>363</v>
       </c>
       <c r="L418" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="M418" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="N418" t="s">
         <v>46</v>
@@ -26193,7 +26196,7 @@
         <v>47</v>
       </c>
       <c r="P418" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="Q418" t="s">
         <v>46</v>
@@ -26204,13 +26207,13 @@
     </row>
     <row r="419">
       <c r="A419" t="s" s="1">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B419" t="s" s="1">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C419" t="s" s="1">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D419" t="s" s="1">
         <v>33</v>
@@ -26260,19 +26263,19 @@
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B420" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C420" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D420" t="s">
         <v>33</v>
       </c>
       <c r="E420" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="F420" t="s">
         <v>207</v>
@@ -26281,22 +26284,22 @@
         <v>40</v>
       </c>
       <c r="H420" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="I420" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="J420" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="K420" t="s">
         <v>146</v>
       </c>
       <c r="L420" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="M420" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="N420" t="s">
         <v>46</v>
@@ -26305,7 +26308,7 @@
         <v>47</v>
       </c>
       <c r="P420" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="Q420" t="s">
         <v>46</v>
@@ -26316,13 +26319,13 @@
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B421" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C421" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D421" t="s">
         <v>33</v>
@@ -26337,22 +26340,22 @@
         <v>40</v>
       </c>
       <c r="H421" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="I421" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="J421" t="s">
         <v>712</v>
       </c>
       <c r="K421" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="L421" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="M421" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="N421" t="s">
         <v>46</v>
@@ -26361,7 +26364,7 @@
         <v>47</v>
       </c>
       <c r="P421" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="Q421" t="s">
         <v>46</v>
@@ -26372,13 +26375,13 @@
     </row>
     <row r="422">
       <c r="A422" t="s" s="1">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B422" t="s" s="1">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C422" t="s" s="1">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D422" t="s" s="1">
         <v>33</v>
@@ -26428,19 +26431,19 @@
     </row>
     <row r="423">
       <c r="A423" t="s">
+        <v>865</v>
+      </c>
+      <c r="B423" t="s">
         <v>864</v>
       </c>
-      <c r="B423" t="s">
-        <v>863</v>
-      </c>
       <c r="C423" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D423" t="s">
         <v>33</v>
       </c>
       <c r="E423" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F423" t="s">
         <v>207</v>
@@ -26449,10 +26452,10 @@
         <v>40</v>
       </c>
       <c r="H423" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="I423" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="J423" t="s">
         <v>712</v>
@@ -26461,10 +26464,10 @@
         <v>318</v>
       </c>
       <c r="L423" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="M423" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="N423" t="s">
         <v>46</v>
@@ -26473,7 +26476,7 @@
         <v>47</v>
       </c>
       <c r="P423" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="Q423" t="s">
         <v>46</v>
@@ -26484,13 +26487,13 @@
     </row>
     <row r="424">
       <c r="A424" t="s" s="1">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B424" t="s" s="1">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C424" t="s" s="1">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D424" t="s" s="1">
         <v>33</v>
@@ -26540,19 +26543,19 @@
     </row>
     <row r="425">
       <c r="A425" t="s">
+        <v>871</v>
+      </c>
+      <c r="B425" t="s">
         <v>870</v>
       </c>
-      <c r="B425" t="s">
-        <v>869</v>
-      </c>
       <c r="C425" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D425" t="s">
         <v>33</v>
       </c>
       <c r="E425" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F425" t="s">
         <v>39</v>
@@ -26561,10 +26564,10 @@
         <v>40</v>
       </c>
       <c r="H425" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="I425" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="J425" t="s">
         <v>330</v>
@@ -26576,7 +26579,7 @@
         <v>34</v>
       </c>
       <c r="M425" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="N425" t="s">
         <v>46</v>
@@ -26585,7 +26588,7 @@
         <v>47</v>
       </c>
       <c r="P425" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="Q425" t="s">
         <v>46</v>
@@ -26596,7 +26599,7 @@
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B426" t="s">
         <v>34</v>
@@ -26608,7 +26611,7 @@
         <v>34</v>
       </c>
       <c r="E426" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F426" t="s">
         <v>39</v>
@@ -26620,7 +26623,7 @@
         <v>473</v>
       </c>
       <c r="I426" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="J426" t="s">
         <v>101</v>
@@ -26629,10 +26632,10 @@
         <v>175</v>
       </c>
       <c r="L426" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="M426" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="N426" t="s">
         <v>46</v>
@@ -26641,7 +26644,7 @@
         <v>47</v>
       </c>
       <c r="P426" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="Q426" t="s">
         <v>46</v>
@@ -26652,7 +26655,7 @@
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B427" t="s">
         <v>34</v>
@@ -26664,7 +26667,7 @@
         <v>34</v>
       </c>
       <c r="E427" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="F427" t="s">
         <v>39</v>
@@ -26673,10 +26676,10 @@
         <v>40</v>
       </c>
       <c r="H427" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="I427" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="J427" t="s">
         <v>330</v>
@@ -26685,10 +26688,10 @@
         <v>156</v>
       </c>
       <c r="L427" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="M427" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="N427" t="s">
         <v>46</v>
@@ -26697,7 +26700,7 @@
         <v>47</v>
       </c>
       <c r="P427" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="Q427" t="s">
         <v>46</v>
@@ -26708,7 +26711,7 @@
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B428" t="s">
         <v>34</v>
@@ -26720,7 +26723,7 @@
         <v>34</v>
       </c>
       <c r="E428" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="F428" t="s">
         <v>39</v>
@@ -26732,7 +26735,7 @@
         <v>324</v>
       </c>
       <c r="I428" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="J428" t="s">
         <v>58</v>
@@ -26741,10 +26744,10 @@
         <v>175</v>
       </c>
       <c r="L428" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="M428" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="N428" t="s">
         <v>46</v>
@@ -26753,7 +26756,7 @@
         <v>47</v>
       </c>
       <c r="P428" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="Q428" t="s">
         <v>46</v>
@@ -26764,7 +26767,7 @@
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B429" t="s">
         <v>34</v>
@@ -26776,7 +26779,7 @@
         <v>34</v>
       </c>
       <c r="E429" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="F429" t="s">
         <v>39</v>
@@ -26785,10 +26788,10 @@
         <v>40</v>
       </c>
       <c r="H429" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="I429" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="J429" t="s">
         <v>330</v>
@@ -26797,10 +26800,10 @@
         <v>156</v>
       </c>
       <c r="L429" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="M429" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="N429" t="s">
         <v>46</v>
@@ -26809,7 +26812,7 @@
         <v>47</v>
       </c>
       <c r="P429" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="Q429" t="s">
         <v>46</v>
@@ -26820,7 +26823,7 @@
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B430" t="s">
         <v>34</v>
@@ -26832,7 +26835,7 @@
         <v>34</v>
       </c>
       <c r="E430" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F430" t="s">
         <v>39</v>
@@ -26841,10 +26844,10 @@
         <v>40</v>
       </c>
       <c r="H430" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="I430" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="J430" t="s">
         <v>330</v>
@@ -26853,10 +26856,10 @@
         <v>558</v>
       </c>
       <c r="L430" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="M430" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="N430" t="s">
         <v>46</v>
@@ -26865,7 +26868,7 @@
         <v>47</v>
       </c>
       <c r="P430" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="Q430" t="s">
         <v>46</v>
@@ -26876,7 +26879,7 @@
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B431" t="s">
         <v>34</v>
@@ -26888,7 +26891,7 @@
         <v>34</v>
       </c>
       <c r="E431" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="F431" t="s">
         <v>39</v>
@@ -26897,10 +26900,10 @@
         <v>40</v>
       </c>
       <c r="H431" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="I431" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="J431" t="s">
         <v>330</v>
@@ -26909,10 +26912,10 @@
         <v>156</v>
       </c>
       <c r="L431" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="M431" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="N431" t="s">
         <v>46</v>
@@ -26921,7 +26924,7 @@
         <v>47</v>
       </c>
       <c r="P431" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="Q431" t="s">
         <v>46</v>
@@ -26932,7 +26935,7 @@
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B432" t="s">
         <v>34</v>
@@ -26944,7 +26947,7 @@
         <v>34</v>
       </c>
       <c r="E432" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F432" t="s">
         <v>39</v>
@@ -26953,10 +26956,10 @@
         <v>40</v>
       </c>
       <c r="H432" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="I432" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="J432" t="s">
         <v>340</v>
@@ -26965,10 +26968,10 @@
         <v>69</v>
       </c>
       <c r="L432" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="M432" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="N432" t="s">
         <v>46</v>
@@ -26977,7 +26980,7 @@
         <v>47</v>
       </c>
       <c r="P432" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="Q432" t="s">
         <v>46</v>
@@ -26988,13 +26991,13 @@
     </row>
     <row r="433">
       <c r="A433" t="s" s="1">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B433" t="s" s="1">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C433" t="s" s="1">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D433" t="s" s="1">
         <v>33</v>
@@ -27044,19 +27047,19 @@
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B434" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C434" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D434" t="s">
         <v>33</v>
       </c>
       <c r="E434" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F434" t="s">
         <v>39</v>
@@ -27065,10 +27068,10 @@
         <v>40</v>
       </c>
       <c r="H434" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="I434" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="J434" t="s">
         <v>247</v>
@@ -27077,10 +27080,10 @@
         <v>91</v>
       </c>
       <c r="L434" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="M434" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="N434" t="s">
         <v>46</v>
@@ -27089,7 +27092,7 @@
         <v>47</v>
       </c>
       <c r="P434" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="Q434" t="s">
         <v>46</v>
@@ -27100,13 +27103,13 @@
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B435" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C435" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D435" t="s">
         <v>33</v>
@@ -27124,7 +27127,7 @@
         <v>160</v>
       </c>
       <c r="I435" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="J435" t="s">
         <v>712</v>
@@ -27133,10 +27136,10 @@
         <v>363</v>
       </c>
       <c r="L435" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="M435" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="N435" t="s">
         <v>46</v>
@@ -27145,7 +27148,7 @@
         <v>47</v>
       </c>
       <c r="P435" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="Q435" t="s">
         <v>46</v>
@@ -27156,19 +27159,19 @@
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B436" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C436" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D436" t="s">
         <v>33</v>
       </c>
       <c r="E436" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="F436" t="s">
         <v>207</v>
@@ -27177,22 +27180,22 @@
         <v>40</v>
       </c>
       <c r="H436" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I436" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="J436" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="K436" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="L436" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="M436" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="N436" t="s">
         <v>46</v>
@@ -27201,7 +27204,7 @@
         <v>47</v>
       </c>
       <c r="P436" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="Q436" t="s">
         <v>46</v>
@@ -27212,19 +27215,19 @@
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B437" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C437" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D437" t="s">
         <v>33</v>
       </c>
       <c r="E437" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F437" t="s">
         <v>207</v>
@@ -27233,22 +27236,22 @@
         <v>40</v>
       </c>
       <c r="H437" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="I437" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="J437" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="K437" t="s">
         <v>363</v>
       </c>
       <c r="L437" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="M437" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="N437" t="s">
         <v>46</v>
@@ -27257,7 +27260,7 @@
         <v>47</v>
       </c>
       <c r="P437" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="Q437" t="s">
         <v>46</v>
@@ -27268,13 +27271,13 @@
     </row>
     <row r="438">
       <c r="A438" t="s" s="1">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B438" t="s" s="1">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C438" t="s" s="1">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D438" t="s" s="1">
         <v>33</v>
@@ -27324,13 +27327,13 @@
     </row>
     <row r="439">
       <c r="A439" t="s">
+        <v>927</v>
+      </c>
+      <c r="B439" t="s">
         <v>926</v>
       </c>
-      <c r="B439" t="s">
-        <v>925</v>
-      </c>
       <c r="C439" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D439" t="s">
         <v>33</v>
@@ -27345,7 +27348,7 @@
         <v>40</v>
       </c>
       <c r="H439" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="I439" t="s">
         <v>354</v>
@@ -27357,10 +27360,10 @@
         <v>363</v>
       </c>
       <c r="L439" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="M439" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N439" t="s">
         <v>46</v>
@@ -27380,7 +27383,7 @@
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B440" t="s">
         <v>34</v>
@@ -27401,10 +27404,10 @@
         <v>40</v>
       </c>
       <c r="H440" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="I440" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="J440" t="s">
         <v>367</v>
@@ -27413,10 +27416,10 @@
         <v>97</v>
       </c>
       <c r="L440" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M440" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N440" t="s">
         <v>46</v>
@@ -27425,7 +27428,7 @@
         <v>47</v>
       </c>
       <c r="P440" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="Q440" t="s">
         <v>46</v>
@@ -27436,7 +27439,7 @@
     </row>
     <row r="441">
       <c r="A441" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B441" t="s">
         <v>34</v>
@@ -27448,7 +27451,7 @@
         <v>34</v>
       </c>
       <c r="E441" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F441" t="s">
         <v>207</v>
@@ -27457,22 +27460,22 @@
         <v>40</v>
       </c>
       <c r="H441" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="I441" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="J441" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="K441" t="s">
         <v>363</v>
       </c>
       <c r="L441" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="M441" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N441" t="s">
         <v>46</v>
@@ -27481,7 +27484,7 @@
         <v>47</v>
       </c>
       <c r="P441" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="Q441" t="s">
         <v>46</v>
@@ -27492,7 +27495,7 @@
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B442" t="s">
         <v>34</v>
@@ -27504,7 +27507,7 @@
         <v>34</v>
       </c>
       <c r="E442" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F442" t="s">
         <v>207</v>
@@ -27513,22 +27516,22 @@
         <v>40</v>
       </c>
       <c r="H442" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="I442" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="J442" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="K442" t="s">
         <v>363</v>
       </c>
       <c r="L442" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M442" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N442" t="s">
         <v>46</v>
@@ -27537,7 +27540,7 @@
         <v>47</v>
       </c>
       <c r="P442" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="Q442" t="s">
         <v>46</v>
@@ -27548,7 +27551,7 @@
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B443" t="s">
         <v>34</v>
@@ -27560,7 +27563,7 @@
         <v>34</v>
       </c>
       <c r="E443" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F443" t="s">
         <v>207</v>
@@ -27569,22 +27572,22 @@
         <v>40</v>
       </c>
       <c r="H443" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="I443" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="J443" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="K443" t="s">
         <v>340</v>
       </c>
       <c r="L443" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="M443" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N443" t="s">
         <v>46</v>
@@ -27593,7 +27596,7 @@
         <v>47</v>
       </c>
       <c r="P443" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="Q443" t="s">
         <v>46</v>
@@ -27604,7 +27607,7 @@
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B444" t="s">
         <v>34</v>
@@ -27616,7 +27619,7 @@
         <v>34</v>
       </c>
       <c r="E444" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F444" t="s">
         <v>207</v>
@@ -27625,22 +27628,22 @@
         <v>40</v>
       </c>
       <c r="H444" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="I444" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="J444" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="K444" t="s">
         <v>363</v>
       </c>
       <c r="L444" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="M444" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N444" t="s">
         <v>46</v>
@@ -27649,7 +27652,7 @@
         <v>47</v>
       </c>
       <c r="P444" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="Q444" t="s">
         <v>46</v>
@@ -27660,7 +27663,7 @@
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B445" t="s">
         <v>34</v>
@@ -27672,7 +27675,7 @@
         <v>34</v>
       </c>
       <c r="E445" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="F445" t="s">
         <v>207</v>
@@ -27681,22 +27684,22 @@
         <v>40</v>
       </c>
       <c r="H445" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="I445" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="J445" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="K445" t="s">
         <v>363</v>
       </c>
       <c r="L445" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M445" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="N445" t="s">
         <v>46</v>
@@ -27705,7 +27708,7 @@
         <v>47</v>
       </c>
       <c r="P445" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="Q445" t="s">
         <v>46</v>
@@ -27716,13 +27719,13 @@
     </row>
     <row r="446">
       <c r="A446" t="s" s="1">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B446" t="s" s="1">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C446" t="s" s="1">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D446" t="s" s="1">
         <v>33</v>
@@ -27772,19 +27775,19 @@
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B447" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C447" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D447" t="s">
         <v>33</v>
       </c>
       <c r="E447" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F447" t="s">
         <v>39</v>
@@ -27796,7 +27799,7 @@
         <v>473</v>
       </c>
       <c r="I447" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="J447" t="s">
         <v>156</v>
@@ -27805,10 +27808,10 @@
         <v>156</v>
       </c>
       <c r="L447" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="M447" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="N447" t="s">
         <v>46</v>
@@ -27817,7 +27820,7 @@
         <v>47</v>
       </c>
       <c r="P447" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="Q447" t="s">
         <v>46</v>
@@ -27828,19 +27831,19 @@
     </row>
     <row r="448">
       <c r="A448" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B448" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C448" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D448" t="s">
         <v>33</v>
       </c>
       <c r="E448" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F448" t="s">
         <v>39</v>
@@ -27849,10 +27852,10 @@
         <v>40</v>
       </c>
       <c r="H448" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="I448" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="J448" t="s">
         <v>69</v>
@@ -27861,10 +27864,10 @@
         <v>69</v>
       </c>
       <c r="L448" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M448" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="N448" t="s">
         <v>46</v>
@@ -27873,7 +27876,7 @@
         <v>47</v>
       </c>
       <c r="P448" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="Q448" t="s">
         <v>46</v>
@@ -27884,13 +27887,13 @@
     </row>
     <row r="449">
       <c r="A449" t="s" s="1">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B449" t="s" s="1">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C449" t="s" s="1">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D449" t="s" s="1">
         <v>33</v>
@@ -27940,13 +27943,13 @@
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B450" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C450" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D450" t="s">
         <v>33</v>
@@ -27961,10 +27964,10 @@
         <v>40</v>
       </c>
       <c r="H450" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="I450" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="J450" t="s">
         <v>712</v>
@@ -27973,10 +27976,10 @@
         <v>363</v>
       </c>
       <c r="L450" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="M450" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="N450" t="s">
         <v>46</v>
@@ -27985,7 +27988,7 @@
         <v>47</v>
       </c>
       <c r="P450" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="Q450" t="s">
         <v>46</v>
@@ -27996,19 +27999,19 @@
     </row>
     <row r="451">
       <c r="A451" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B451" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C451" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D451" t="s">
         <v>33</v>
       </c>
       <c r="E451" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F451" t="s">
         <v>39</v>
@@ -28017,10 +28020,10 @@
         <v>40</v>
       </c>
       <c r="H451" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="I451" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="J451" t="s">
         <v>65</v>
@@ -28032,7 +28035,7 @@
         <v>34</v>
       </c>
       <c r="M451" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="N451" t="s">
         <v>46</v>
@@ -28041,7 +28044,7 @@
         <v>47</v>
       </c>
       <c r="P451" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="Q451" t="s">
         <v>46</v>
@@ -28052,13 +28055,13 @@
     </row>
     <row r="452">
       <c r="A452" t="s" s="1">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B452" t="s" s="1">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C452" t="s" s="1">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D452" t="s" s="1">
         <v>33</v>
@@ -28108,13 +28111,13 @@
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B453" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C453" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D453" t="s">
         <v>33</v>
@@ -28129,10 +28132,10 @@
         <v>40</v>
       </c>
       <c r="H453" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="I453" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="J453" t="s">
         <v>210</v>
@@ -28141,10 +28144,10 @@
         <v>65</v>
       </c>
       <c r="L453" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="M453" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="N453" t="s">
         <v>46</v>
@@ -28153,7 +28156,7 @@
         <v>47</v>
       </c>
       <c r="P453" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="Q453" t="s">
         <v>46</v>
@@ -28164,19 +28167,19 @@
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B454" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C454" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D454" t="s">
         <v>33</v>
       </c>
       <c r="E454" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F454" t="s">
         <v>39</v>
@@ -28185,10 +28188,10 @@
         <v>40</v>
       </c>
       <c r="H454" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="I454" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="J454" t="s">
         <v>351</v>
@@ -28200,7 +28203,7 @@
         <v>34</v>
       </c>
       <c r="M454" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="N454" t="s">
         <v>46</v>
@@ -28209,7 +28212,7 @@
         <v>47</v>
       </c>
       <c r="P454" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q454" t="s">
         <v>46</v>
@@ -28220,13 +28223,13 @@
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B455" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C455" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D455" t="s">
         <v>33</v>
@@ -28241,10 +28244,10 @@
         <v>40</v>
       </c>
       <c r="H455" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="I455" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="J455" t="s">
         <v>712</v>
@@ -28253,10 +28256,10 @@
         <v>363</v>
       </c>
       <c r="L455" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="M455" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="N455" t="s">
         <v>46</v>
@@ -28265,7 +28268,7 @@
         <v>47</v>
       </c>
       <c r="P455" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="Q455" t="s">
         <v>46</v>
@@ -28276,7 +28279,7 @@
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B456" t="s">
         <v>34</v>
@@ -28288,7 +28291,7 @@
         <v>34</v>
       </c>
       <c r="E456" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F456" t="s">
         <v>207</v>
@@ -28297,10 +28300,10 @@
         <v>40</v>
       </c>
       <c r="H456" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="I456" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="J456" t="s">
         <v>716</v>
@@ -28309,10 +28312,10 @@
         <v>117</v>
       </c>
       <c r="L456" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="M456" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="N456" t="s">
         <v>46</v>
@@ -28321,7 +28324,7 @@
         <v>47</v>
       </c>
       <c r="P456" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="Q456" t="s">
         <v>46</v>
@@ -28332,13 +28335,13 @@
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B457" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C457" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D457" t="s">
         <v>33</v>
@@ -28353,22 +28356,22 @@
         <v>40</v>
       </c>
       <c r="H457" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="I457" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="J457" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="K457" t="s">
         <v>363</v>
       </c>
       <c r="L457" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="M457" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="N457" t="s">
         <v>46</v>
@@ -28377,7 +28380,7 @@
         <v>47</v>
       </c>
       <c r="P457" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="Q457" t="s">
         <v>46</v>
@@ -28388,13 +28391,13 @@
     </row>
     <row r="458">
       <c r="A458" t="s" s="1">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B458" t="s" s="1">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C458" t="s" s="1">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D458" t="s" s="1">
         <v>33</v>
@@ -28444,19 +28447,19 @@
     </row>
     <row r="459">
       <c r="A459" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B459" t="s">
         <v>1003</v>
       </c>
-      <c r="B459" t="s">
-        <v>1002</v>
-      </c>
       <c r="C459" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D459" t="s">
         <v>33</v>
       </c>
       <c r="E459" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F459" t="s">
         <v>39</v>
@@ -28465,10 +28468,10 @@
         <v>40</v>
       </c>
       <c r="H459" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="I459" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="J459" t="s">
         <v>297</v>
@@ -28480,7 +28483,7 @@
         <v>34</v>
       </c>
       <c r="M459" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="N459" t="s">
         <v>46</v>
@@ -28489,7 +28492,7 @@
         <v>47</v>
       </c>
       <c r="P459" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="Q459" t="s">
         <v>46</v>
@@ -28500,13 +28503,13 @@
     </row>
     <row r="460">
       <c r="A460" t="s" s="1">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B460" t="s" s="1">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C460" t="s" s="1">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D460" t="s" s="1">
         <v>33</v>
@@ -28556,13 +28559,13 @@
     </row>
     <row r="461">
       <c r="A461" t="s" s="1">
+        <v>1009</v>
+      </c>
+      <c r="B461" t="s" s="1">
         <v>1008</v>
       </c>
-      <c r="B461" t="s" s="1">
-        <v>1007</v>
-      </c>
       <c r="C461" t="s" s="1">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D461" t="s" s="1">
         <v>33</v>
@@ -28612,13 +28615,13 @@
     </row>
     <row r="462">
       <c r="A462" t="s" s="1">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B462" t="s" s="1">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C462" t="s" s="1">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D462" t="s" s="1">
         <v>33</v>
@@ -28668,19 +28671,19 @@
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B463" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C463" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D463" t="s">
         <v>33</v>
       </c>
       <c r="E463" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F463" t="s">
         <v>39</v>
@@ -28689,10 +28692,10 @@
         <v>40</v>
       </c>
       <c r="H463" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="I463" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="J463" t="s">
         <v>330</v>
@@ -28704,7 +28707,7 @@
         <v>34</v>
       </c>
       <c r="M463" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="N463" t="s">
         <v>46</v>
@@ -28713,7 +28716,7 @@
         <v>47</v>
       </c>
       <c r="P463" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="Q463" t="s">
         <v>46</v>
@@ -28724,13 +28727,13 @@
     </row>
     <row r="464">
       <c r="A464" t="s" s="1">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B464" t="s" s="1">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C464" t="s" s="1">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D464" t="s" s="1">
         <v>33</v>
@@ -28780,13 +28783,13 @@
     </row>
     <row r="465">
       <c r="A465" t="s" s="1">
+        <v>1017</v>
+      </c>
+      <c r="B465" t="s" s="1">
         <v>1016</v>
       </c>
-      <c r="B465" t="s" s="1">
-        <v>1015</v>
-      </c>
       <c r="C465" t="s" s="1">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D465" t="s" s="1">
         <v>33</v>
@@ -28836,13 +28839,13 @@
     </row>
     <row r="466">
       <c r="A466" t="s" s="1">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B466" t="s" s="1">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C466" t="s" s="1">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D466" t="s" s="1">
         <v>33</v>
@@ -28892,13 +28895,13 @@
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B467" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C467" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D467" t="s">
         <v>33</v>
@@ -28913,10 +28916,10 @@
         <v>40</v>
       </c>
       <c r="H467" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I467" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="J467" t="s">
         <v>97</v>
@@ -28925,10 +28928,10 @@
         <v>97</v>
       </c>
       <c r="L467" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M467" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N467" t="s">
         <v>46</v>
@@ -28948,7 +28951,7 @@
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B468" t="s">
         <v>34</v>
@@ -28969,10 +28972,10 @@
         <v>40</v>
       </c>
       <c r="H468" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I468" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="J468" t="s">
         <v>302</v>
@@ -28981,10 +28984,10 @@
         <v>247</v>
       </c>
       <c r="L468" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M468" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N468" t="s">
         <v>46</v>
@@ -29004,7 +29007,7 @@
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B469" t="s">
         <v>34</v>
@@ -29025,10 +29028,10 @@
         <v>40</v>
       </c>
       <c r="H469" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I469" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="J469" t="s">
         <v>87</v>
@@ -29037,10 +29040,10 @@
         <v>87</v>
       </c>
       <c r="L469" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M469" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N469" t="s">
         <v>46</v>
@@ -29060,7 +29063,7 @@
     </row>
     <row r="470">
       <c r="A470" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B470" t="s">
         <v>34</v>
@@ -29081,10 +29084,10 @@
         <v>40</v>
       </c>
       <c r="H470" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I470" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="J470" t="s">
         <v>74</v>
@@ -29093,10 +29096,10 @@
         <v>74</v>
       </c>
       <c r="L470" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M470" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N470" t="s">
         <v>46</v>
@@ -29116,7 +29119,7 @@
     </row>
     <row r="471">
       <c r="A471" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B471" t="s">
         <v>34</v>
@@ -29137,10 +29140,10 @@
         <v>40</v>
       </c>
       <c r="H471" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I471" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="J471" t="s">
         <v>65</v>
@@ -29149,10 +29152,10 @@
         <v>247</v>
       </c>
       <c r="L471" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M471" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N471" t="s">
         <v>46</v>
@@ -29172,7 +29175,7 @@
     </row>
     <row r="472">
       <c r="A472" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B472" t="s">
         <v>34</v>
@@ -29193,10 +29196,10 @@
         <v>40</v>
       </c>
       <c r="H472" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I472" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="J472" t="s">
         <v>58</v>
@@ -29205,10 +29208,10 @@
         <v>58</v>
       </c>
       <c r="L472" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M472" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N472" t="s">
         <v>46</v>
@@ -29228,7 +29231,7 @@
     </row>
     <row r="473">
       <c r="A473" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B473" t="s">
         <v>34</v>
@@ -29249,10 +29252,10 @@
         <v>40</v>
       </c>
       <c r="H473" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I473" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="J473" t="s">
         <v>117</v>
@@ -29261,10 +29264,10 @@
         <v>117</v>
       </c>
       <c r="L473" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M473" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N473" t="s">
         <v>46</v>
@@ -29284,7 +29287,7 @@
     </row>
     <row r="474">
       <c r="A474" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B474" t="s">
         <v>34</v>
@@ -29305,10 +29308,10 @@
         <v>40</v>
       </c>
       <c r="H474" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I474" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="J474" t="s">
         <v>69</v>
@@ -29317,10 +29320,10 @@
         <v>247</v>
       </c>
       <c r="L474" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M474" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N474" t="s">
         <v>46</v>
@@ -29340,7 +29343,7 @@
     </row>
     <row r="475">
       <c r="A475" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B475" t="s">
         <v>34</v>
@@ -29361,10 +29364,10 @@
         <v>40</v>
       </c>
       <c r="H475" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I475" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="J475" t="s">
         <v>132</v>
@@ -29373,10 +29376,10 @@
         <v>132</v>
       </c>
       <c r="L475" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M475" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N475" t="s">
         <v>46</v>
@@ -29396,7 +29399,7 @@
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B476" t="s">
         <v>34</v>
@@ -29417,10 +29420,10 @@
         <v>40</v>
       </c>
       <c r="H476" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I476" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="J476" t="s">
         <v>109</v>
@@ -29429,10 +29432,10 @@
         <v>109</v>
       </c>
       <c r="L476" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M476" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N476" t="s">
         <v>46</v>
@@ -29452,7 +29455,7 @@
     </row>
     <row r="477">
       <c r="A477" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B477" t="s">
         <v>34</v>
@@ -29473,10 +29476,10 @@
         <v>40</v>
       </c>
       <c r="H477" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I477" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="J477" t="s">
         <v>59</v>
@@ -29485,10 +29488,10 @@
         <v>59</v>
       </c>
       <c r="L477" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M477" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N477" t="s">
         <v>46</v>
@@ -29508,7 +29511,7 @@
     </row>
     <row r="478">
       <c r="A478" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B478" t="s">
         <v>34</v>
@@ -29529,10 +29532,10 @@
         <v>40</v>
       </c>
       <c r="H478" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I478" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="J478" t="s">
         <v>59</v>
@@ -29541,10 +29544,10 @@
         <v>59</v>
       </c>
       <c r="L478" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M478" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N478" t="s">
         <v>46</v>
@@ -29564,7 +29567,7 @@
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B479" t="s">
         <v>34</v>
@@ -29585,10 +29588,10 @@
         <v>40</v>
       </c>
       <c r="H479" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I479" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="J479" t="s">
         <v>59</v>
@@ -29597,10 +29600,10 @@
         <v>247</v>
       </c>
       <c r="L479" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M479" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N479" t="s">
         <v>46</v>
@@ -29620,7 +29623,7 @@
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B480" t="s">
         <v>34</v>
@@ -29641,10 +29644,10 @@
         <v>40</v>
       </c>
       <c r="H480" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I480" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="J480" t="s">
         <v>59</v>
@@ -29653,10 +29656,10 @@
         <v>59</v>
       </c>
       <c r="L480" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M480" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N480" t="s">
         <v>46</v>
@@ -29676,7 +29679,7 @@
     </row>
     <row r="481">
       <c r="A481" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B481" t="s">
         <v>34</v>
@@ -29697,10 +29700,10 @@
         <v>40</v>
       </c>
       <c r="H481" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I481" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="J481" t="s">
         <v>146</v>
@@ -29709,10 +29712,10 @@
         <v>146</v>
       </c>
       <c r="L481" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M481" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N481" t="s">
         <v>46</v>
@@ -29732,7 +29735,7 @@
     </row>
     <row r="482">
       <c r="A482" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B482" t="s">
         <v>34</v>
@@ -29753,10 +29756,10 @@
         <v>40</v>
       </c>
       <c r="H482" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I482" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="J482" t="s">
         <v>58</v>
@@ -29765,10 +29768,10 @@
         <v>58</v>
       </c>
       <c r="L482" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M482" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N482" t="s">
         <v>46</v>
@@ -29788,7 +29791,7 @@
     </row>
     <row r="483">
       <c r="A483" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B483" t="s">
         <v>34</v>
@@ -29809,10 +29812,10 @@
         <v>40</v>
       </c>
       <c r="H483" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I483" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="J483" t="s">
         <v>59</v>
@@ -29821,10 +29824,10 @@
         <v>59</v>
       </c>
       <c r="L483" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M483" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N483" t="s">
         <v>46</v>
@@ -29844,7 +29847,7 @@
     </row>
     <row r="484">
       <c r="A484" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B484" t="s">
         <v>34</v>
@@ -29865,10 +29868,10 @@
         <v>40</v>
       </c>
       <c r="H484" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I484" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="J484" t="s">
         <v>59</v>
@@ -29877,10 +29880,10 @@
         <v>59</v>
       </c>
       <c r="L484" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M484" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N484" t="s">
         <v>46</v>
@@ -29900,7 +29903,7 @@
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B485" t="s">
         <v>34</v>
@@ -29921,10 +29924,10 @@
         <v>40</v>
       </c>
       <c r="H485" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="I485" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="J485" t="s">
         <v>58</v>
@@ -29933,10 +29936,10 @@
         <v>58</v>
       </c>
       <c r="L485" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M485" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N485" t="s">
         <v>46</v>
@@ -29956,7 +29959,7 @@
     </row>
     <row r="486">
       <c r="A486" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B486" t="s">
         <v>34</v>
@@ -29977,10 +29980,10 @@
         <v>40</v>
       </c>
       <c r="H486" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I486" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="J486" t="s">
         <v>59</v>
@@ -29989,10 +29992,10 @@
         <v>59</v>
       </c>
       <c r="L486" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M486" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N486" t="s">
         <v>46</v>
@@ -30012,7 +30015,7 @@
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B487" t="s">
         <v>34</v>
@@ -30033,10 +30036,10 @@
         <v>40</v>
       </c>
       <c r="H487" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I487" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="J487" t="s">
         <v>65</v>
@@ -30045,10 +30048,10 @@
         <v>247</v>
       </c>
       <c r="L487" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M487" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="N487" t="s">
         <v>46</v>
@@ -30068,7 +30071,7 @@
     </row>
     <row r="488">
       <c r="A488" t="s" s="1">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B488" t="s" s="1">
         <v>32</v>
@@ -30124,7 +30127,7 @@
     </row>
     <row r="489">
       <c r="A489" t="s" s="1">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B489" t="s" s="1">
         <v>32</v>
@@ -30180,7 +30183,7 @@
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B490" t="s">
         <v>32</v>
@@ -30236,7 +30239,7 @@
     </row>
     <row r="491">
       <c r="A491" t="s" s="1">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B491" t="s" s="1">
         <v>49</v>
@@ -30292,7 +30295,7 @@
     </row>
     <row r="492">
       <c r="A492" t="s" s="1">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B492" t="s" s="1">
         <v>49</v>
@@ -30348,7 +30351,7 @@
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B493" t="s">
         <v>49</v>
@@ -30404,7 +30407,7 @@
     </row>
     <row r="494">
       <c r="A494" t="s" s="1">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B494" t="s" s="1">
         <v>202</v>
@@ -30460,7 +30463,7 @@
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B495" t="s">
         <v>202</v>
@@ -30516,13 +30519,13 @@
     </row>
     <row r="496">
       <c r="A496" t="s" s="1">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B496" t="s" s="1">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C496" t="s" s="1">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D496" t="s" s="1">
         <v>33</v>
@@ -30572,7 +30575,7 @@
     </row>
     <row r="497">
       <c r="A497" t="s" s="1">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B497" t="s" s="1">
         <v>224</v>
@@ -30628,7 +30631,7 @@
     </row>
     <row r="498">
       <c r="A498" t="s" s="1">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B498" t="s" s="1">
         <v>226</v>
@@ -30684,7 +30687,7 @@
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B499" t="s">
         <v>226</v>
@@ -30740,7 +30743,7 @@
     </row>
     <row r="500">
       <c r="A500" t="s" s="1">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B500" t="s" s="1">
         <v>369</v>
@@ -30796,7 +30799,7 @@
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B501" t="s">
         <v>369</v>
@@ -30852,13 +30855,13 @@
     </row>
     <row r="502">
       <c r="A502" t="s" s="1">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B502" t="s" s="1">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C502" t="s" s="1">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="D502" t="s" s="1">
         <v>33</v>
@@ -30908,13 +30911,13 @@
     </row>
     <row r="503">
       <c r="A503" t="s" s="1">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B503" t="s" s="1">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C503" t="s" s="1">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D503" t="s" s="1">
         <v>33</v>
@@ -30964,7 +30967,7 @@
     </row>
     <row r="504">
       <c r="A504" t="s" s="1">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B504" t="s" s="1">
         <v>456</v>
@@ -31020,7 +31023,7 @@
     </row>
     <row r="505">
       <c r="A505" t="s" s="1">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B505" t="s" s="1">
         <v>458</v>
@@ -31076,7 +31079,7 @@
     </row>
     <row r="506">
       <c r="A506" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B506" t="s">
         <v>460</v>
@@ -31132,7 +31135,7 @@
     </row>
     <row r="507">
       <c r="A507" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B507" t="s">
         <v>469</v>
@@ -31188,7 +31191,7 @@
     </row>
     <row r="508">
       <c r="A508" t="s" s="1">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B508" t="s" s="1">
         <v>649</v>
@@ -31244,7 +31247,7 @@
     </row>
     <row r="509">
       <c r="A509" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B509" t="s">
         <v>649</v>
@@ -31300,7 +31303,7 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="1">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B510" t="s" s="1">
         <v>656</v>
@@ -31356,7 +31359,7 @@
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B511" t="s">
         <v>658</v>
@@ -31412,7 +31415,7 @@
     </row>
     <row r="512">
       <c r="A512" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B512" t="s">
         <v>683</v>
@@ -31468,7 +31471,7 @@
     </row>
     <row r="513">
       <c r="A513" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B513" t="s">
         <v>690</v>
@@ -31524,7 +31527,7 @@
     </row>
     <row r="514">
       <c r="A514" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B514" t="s">
         <v>697</v>
@@ -31580,7 +31583,7 @@
     </row>
     <row r="515">
       <c r="A515" t="s" s="1">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B515" t="s" s="1">
         <v>732</v>
@@ -31636,7 +31639,7 @@
     </row>
     <row r="516">
       <c r="A516" t="s" s="1">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B516" t="s" s="1">
         <v>734</v>
@@ -31692,7 +31695,7 @@
     </row>
     <row r="517">
       <c r="A517" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B517" t="s">
         <v>736</v>
@@ -31748,7 +31751,7 @@
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B518" t="s">
         <v>740</v>
@@ -31804,13 +31807,13 @@
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B519" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C519" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D519" t="s">
         <v>33</v>
@@ -31860,13 +31863,13 @@
     </row>
     <row r="520">
       <c r="A520" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B520" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C520" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D520" t="s">
         <v>33</v>
@@ -31916,13 +31919,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B521" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C521" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D521" t="s">
         <v>33</v>
@@ -31972,13 +31975,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="1">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B522" t="s" s="1">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C522" t="s" s="1">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D522" t="s" s="1">
         <v>33</v>
@@ -32028,13 +32031,13 @@
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B523" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C523" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D523" t="s">
         <v>33</v>
@@ -32084,13 +32087,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B524" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C524" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D524" t="s">
         <v>33</v>
@@ -32140,13 +32143,13 @@
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B525" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C525" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D525" t="s">
         <v>33</v>
@@ -32196,13 +32199,13 @@
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B526" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C526" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D526" t="s">
         <v>33</v>
@@ -32252,13 +32255,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B527" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C527" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D527" t="s">
         <v>33</v>
@@ -32308,13 +32311,13 @@
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B528" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C528" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D528" t="s">
         <v>33</v>
@@ -32364,13 +32367,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B529" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C529" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D529" t="s">
         <v>33</v>
@@ -32420,13 +32423,13 @@
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B530" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C530" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D530" t="s">
         <v>33</v>
@@ -32476,13 +32479,13 @@
     </row>
     <row r="531">
       <c r="A531" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B531" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C531" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D531" t="s">
         <v>33</v>
@@ -32532,13 +32535,13 @@
     </row>
     <row r="532">
       <c r="A532" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B532" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C532" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D532" t="s">
         <v>33</v>
@@ -32588,13 +32591,13 @@
     </row>
     <row r="533">
       <c r="A533" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B533" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C533" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D533" t="s">
         <v>33</v>
@@ -32644,13 +32647,13 @@
     </row>
     <row r="534">
       <c r="A534" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B534" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C534" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D534" t="s">
         <v>33</v>
@@ -32700,13 +32703,13 @@
     </row>
     <row r="535">
       <c r="A535" t="s" s="1">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B535" t="s" s="1">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C535" t="s" s="1">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D535" t="s" s="1">
         <v>33</v>
@@ -32756,13 +32759,13 @@
     </row>
     <row r="536">
       <c r="A536" t="s" s="1">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B536" t="s" s="1">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C536" t="s" s="1">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="D536" t="s" s="1">
         <v>33</v>
@@ -32812,13 +32815,13 @@
     </row>
     <row r="537">
       <c r="A537" t="s" s="1">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B537" t="s" s="1">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C537" t="s" s="1">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D537" t="s" s="1">
         <v>33</v>
@@ -32868,13 +32871,13 @@
     </row>
     <row r="538">
       <c r="A538" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B538" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C538" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D538" t="s">
         <v>33</v>
@@ -32924,13 +32927,13 @@
     </row>
     <row r="539">
       <c r="A539" t="s" s="1">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B539" t="s" s="1">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C539" t="s" s="1">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D539" t="s" s="1">
         <v>33</v>
@@ -32980,13 +32983,13 @@
     </row>
     <row r="540">
       <c r="A540" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B540" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C540" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D540" t="s">
         <v>33</v>
@@ -33036,13 +33039,13 @@
     </row>
     <row r="541">
       <c r="A541" t="s" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B541" t="s" s="1">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C541" t="s" s="1">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D541" t="s" s="1">
         <v>33</v>
@@ -33092,13 +33095,13 @@
     </row>
     <row r="542">
       <c r="A542" t="s" s="1">
+        <v>1104</v>
+      </c>
+      <c r="B542" t="s" s="1">
         <v>1103</v>
       </c>
-      <c r="B542" t="s" s="1">
-        <v>1102</v>
-      </c>
       <c r="C542" t="s" s="1">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D542" t="s" s="1">
         <v>33</v>
@@ -33148,13 +33151,13 @@
     </row>
     <row r="543">
       <c r="A543" t="s" s="1">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B543" t="s" s="1">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C543" t="s" s="1">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D543" t="s" s="1">
         <v>33</v>
@@ -33204,7 +33207,7 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="1">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B544" t="s" s="1">
         <v>49</v>
@@ -33260,13 +33263,13 @@
     </row>
     <row r="545">
       <c r="A545" t="s" s="1">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B545" t="s" s="1">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="C545" t="s" s="1">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D545" t="s" s="1">
         <v>33</v>
@@ -33316,7 +33319,7 @@
     </row>
     <row r="546">
       <c r="A546" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B546" t="s">
         <v>202</v>
@@ -33372,7 +33375,7 @@
     </row>
     <row r="547">
       <c r="A547" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B547" t="s">
         <v>224</v>
@@ -33428,7 +33431,7 @@
     </row>
     <row r="548">
       <c r="A548" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B548" t="s">
         <v>456</v>
@@ -33484,13 +33487,13 @@
     </row>
     <row r="549">
       <c r="A549" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B549" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C549" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D549" t="s">
         <v>33</v>
@@ -33540,13 +33543,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="1">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B550" t="s" s="1">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C550" t="s" s="1">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D550" t="s" s="1">
         <v>33</v>
@@ -33596,7 +33599,7 @@
     </row>
     <row r="551">
       <c r="A551" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B551" t="s">
         <v>732</v>
@@ -33652,13 +33655,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B552" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C552" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D552" t="s">
         <v>33</v>
@@ -33708,7 +33711,7 @@
     </row>
     <row r="553">
       <c r="A553" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B553" t="s">
         <v>49</v>
@@ -33764,13 +33767,13 @@
     </row>
     <row r="554">
       <c r="A554" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B554" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C554" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D554" t="s">
         <v>33</v>
@@ -33820,13 +33823,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B555" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C555" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D555" t="s">
         <v>33</v>
@@ -33876,7 +33879,7 @@
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B556" t="s">
         <v>226</v>
@@ -33932,7 +33935,7 @@
     </row>
     <row r="557">
       <c r="A557" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B557" t="s">
         <v>458</v>
@@ -33988,7 +33991,7 @@
     </row>
     <row r="558">
       <c r="A558" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B558" t="s">
         <v>734</v>
@@ -34044,13 +34047,13 @@
     </row>
     <row r="559">
       <c r="A559" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B559" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C559" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D559" t="s">
         <v>33</v>
@@ -34100,7 +34103,7 @@
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B560" t="s">
         <v>202</v>
@@ -34156,13 +34159,13 @@
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B561" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C561" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="D561" t="s">
         <v>33</v>
@@ -34212,13 +34215,13 @@
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B562" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C562" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D562" t="s">
         <v>33</v>
@@ -34268,13 +34271,13 @@
     </row>
     <row r="563">
       <c r="A563" t="s" s="1">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B563" t="s" s="1">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C563" t="s" s="1">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D563" t="s" s="1">
         <v>33</v>
@@ -34324,16 +34327,16 @@
     </row>
     <row r="564">
       <c r="A564" t="s" s="1">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B564" t="s" s="1">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C564" t="s" s="1">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D564" t="s" s="1">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="E564" t="s" s="1">
         <v>34</v>
@@ -34380,16 +34383,16 @@
     </row>
     <row r="565">
       <c r="A565" t="s" s="1">
+        <v>1134</v>
+      </c>
+      <c r="B565" t="s" s="1">
+        <v>1135</v>
+      </c>
+      <c r="C565" t="s" s="1">
+        <v>1135</v>
+      </c>
+      <c r="D565" t="s" s="1">
         <v>1133</v>
-      </c>
-      <c r="B565" t="s" s="1">
-        <v>1134</v>
-      </c>
-      <c r="C565" t="s" s="1">
-        <v>1134</v>
-      </c>
-      <c r="D565" t="s" s="1">
-        <v>1132</v>
       </c>
       <c r="E565" t="s" s="1">
         <v>34</v>
@@ -34436,16 +34439,16 @@
     </row>
     <row r="566">
       <c r="A566" t="s" s="1">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B566" t="s" s="1">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C566" t="s" s="1">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="D566" t="s" s="1">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="E566" t="s" s="1">
         <v>34</v>
@@ -34492,13 +34495,13 @@
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B567" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C567" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D567" t="s">
         <v>33</v>
@@ -34548,19 +34551,19 @@
     </row>
     <row r="568">
       <c r="A568" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B568" t="s">
         <v>1139</v>
       </c>
-      <c r="B568" t="s">
-        <v>1138</v>
-      </c>
       <c r="C568" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D568" t="s">
         <v>33</v>
       </c>
       <c r="E568" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="F568" t="s">
         <v>39</v>
@@ -34569,7 +34572,7 @@
         <v>40</v>
       </c>
       <c r="H568" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="I568" t="s">
         <v>57</v>
@@ -34581,10 +34584,10 @@
         <v>175</v>
       </c>
       <c r="L568" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="M568" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="N568" t="s">
         <v>46</v>
@@ -34604,7 +34607,7 @@
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B569" t="s">
         <v>34</v>
@@ -34616,7 +34619,7 @@
         <v>34</v>
       </c>
       <c r="E569" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="F569" t="s">
         <v>39</v>
@@ -34625,7 +34628,7 @@
         <v>40</v>
       </c>
       <c r="H569" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="I569" t="s">
         <v>57</v>
@@ -34637,10 +34640,10 @@
         <v>91</v>
       </c>
       <c r="L569" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="M569" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="N569" t="s">
         <v>46</v>
@@ -34660,7 +34663,7 @@
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B570" t="s">
         <v>34</v>
@@ -34672,7 +34675,7 @@
         <v>34</v>
       </c>
       <c r="E570" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="F570" t="s">
         <v>39</v>
@@ -34681,7 +34684,7 @@
         <v>40</v>
       </c>
       <c r="H570" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="I570" t="s">
         <v>174</v>
@@ -34693,10 +34696,10 @@
         <v>340</v>
       </c>
       <c r="L570" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="M570" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="N570" t="s">
         <v>46</v>

--- a/xlsx/dre/DRE_07_2026.xlsx
+++ b/xlsx/dre/DRE_07_2026.xlsx
@@ -615,7 +615,7 @@
     <t>4 CUSTOS E DESPESAS</t>
   </si>
   <si>
-    <t>R$ 791.465,14</t>
+    <t>R$ 791.596,20</t>
   </si>
   <si>
     <t>4.01 DEDUÇÕES DE RECEITA</t>
@@ -687,7 +687,7 @@
     <t>4.02 CUSTOS</t>
   </si>
   <si>
-    <t>R$ 335.915,11</t>
+    <t>R$ 336.046,17</t>
   </si>
   <si>
     <t>4.02.01 CUSTO DAS MERCADORIAS VENDIDAS e SERVIÇOS</t>
@@ -997,12 +997,27 @@
 </t>
   </si>
   <si>
+    <t>25/1</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4sign</t>
+  </si>
+  <si>
+    <t>Mercado livre/1</t>
+  </si>
+  <si>
+    <t>Mercado livre</t>
+  </si>
+  <si>
+    <t>R$  22,46</t>
+  </si>
+  <si>
     <t>732/1</t>
   </si>
   <si>
-    <t>Mercado livre</t>
-  </si>
-  <si>
     <t>R$  38,85</t>
   </si>
   <si>
@@ -1024,31 +1039,7 @@
     <t>11/08/26</t>
   </si>
   <si>
-    <t>727/1</t>
-  </si>
-  <si>
-    <t>626/1</t>
-  </si>
-  <si>
-    <t>R$  300,54</t>
-  </si>
-  <si>
-    <t>13/08/26</t>
-  </si>
-  <si>
-    <t>22/07/26</t>
-  </si>
-  <si>
-    <t>69/3</t>
-  </si>
-  <si>
-    <t>Leo Madeiras</t>
-  </si>
-  <si>
-    <t>R$  113,98</t>
-  </si>
-  <si>
-    <t>Leo madeiras</t>
+    <t>R$  12,40</t>
   </si>
   <si>
     <t>731/1</t>
@@ -1066,7 +1057,40 @@
 </t>
   </si>
   <si>
-    <t>R$  12,40</t>
+    <t>723/1</t>
+  </si>
+  <si>
+    <t>R$  557,76</t>
+  </si>
+  <si>
+    <t>estoque</t>
+  </si>
+  <si>
+    <t>727/1</t>
+  </si>
+  <si>
+    <t>626/1</t>
+  </si>
+  <si>
+    <t>R$  300,54</t>
+  </si>
+  <si>
+    <t>13/08/26</t>
+  </si>
+  <si>
+    <t>22/07/26</t>
+  </si>
+  <si>
+    <t>69/3</t>
+  </si>
+  <si>
+    <t>Leo Madeiras</t>
+  </si>
+  <si>
+    <t>R$  113,98</t>
+  </si>
+  <si>
+    <t>Leo madeiras</t>
   </si>
   <si>
     <t>711/1</t>
@@ -1081,30 +1105,6 @@
     <t>Estoque</t>
   </si>
   <si>
-    <t>25/1</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4sign</t>
-  </si>
-  <si>
-    <t>Mercado livre/1</t>
-  </si>
-  <si>
-    <t>R$  22,46</t>
-  </si>
-  <si>
-    <t>723/1</t>
-  </si>
-  <si>
-    <t>R$  557,76</t>
-  </si>
-  <si>
-    <t>estoque</t>
-  </si>
-  <si>
     <t>67/1</t>
   </si>
   <si>
@@ -1129,7 +1129,7 @@
     <t>4.02.02 CUSTO DE TRANSPORTE</t>
   </si>
   <si>
-    <t>R$ 39.717,40</t>
+    <t>R$ 39.848,46</t>
   </si>
   <si>
     <t>4.02.02.01 Fretes sobre compras</t>
@@ -1201,13 +1201,13 @@
     <t>87301/2</t>
   </si>
   <si>
-    <t>R$  823,54</t>
+    <t>R$  888,54</t>
   </si>
   <si>
     <t>87301/3</t>
   </si>
   <si>
-    <t>R$  839,13</t>
+    <t>R$  905,19</t>
   </si>
   <si>
     <t>88601/2</t>
@@ -1771,75 +1771,75 @@
     <t>R$ 11.982,47</t>
   </si>
   <si>
+    <t>88101/2</t>
+  </si>
+  <si>
+    <t>R$  620,43</t>
+  </si>
+  <si>
+    <t>R$  411,87</t>
+  </si>
+  <si>
+    <t>Jose Carlos de Carvalho</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>R$  491,99</t>
+  </si>
+  <si>
+    <t>84401/1</t>
+  </si>
+  <si>
+    <t>R$  164,57</t>
+  </si>
+  <si>
+    <t>84401CamilaFS</t>
+  </si>
+  <si>
+    <t>85201/1</t>
+  </si>
+  <si>
+    <t>R$  2.451,16</t>
+  </si>
+  <si>
+    <t>85201BRUNOAL</t>
+  </si>
+  <si>
+    <t>91201/2</t>
+  </si>
+  <si>
+    <t>R$  252,95</t>
+  </si>
+  <si>
+    <t>R$  584,82</t>
+  </si>
+  <si>
+    <t>R$  213,83</t>
+  </si>
+  <si>
+    <t>R$  1.440,23</t>
+  </si>
+  <si>
+    <t>R$  1.698,42</t>
+  </si>
+  <si>
+    <t>86102/2</t>
+  </si>
+  <si>
+    <t>R$  622,81</t>
+  </si>
+  <si>
+    <t>90001/2</t>
+  </si>
+  <si>
+    <t>R$  471,77</t>
+  </si>
+  <si>
     <t>R$  941,73</t>
   </si>
   <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>R$  491,99</t>
-  </si>
-  <si>
-    <t>R$  411,87</t>
-  </si>
-  <si>
-    <t>R$  1.440,23</t>
-  </si>
-  <si>
-    <t>91201/2</t>
-  </si>
-  <si>
-    <t>Jose Carlos de Carvalho</t>
-  </si>
-  <si>
-    <t>84401/1</t>
-  </si>
-  <si>
-    <t>R$  164,57</t>
-  </si>
-  <si>
-    <t>84401CamilaFS</t>
-  </si>
-  <si>
-    <t>85201/1</t>
-  </si>
-  <si>
-    <t>R$  2.451,16</t>
-  </si>
-  <si>
-    <t>85201BRUNOAL</t>
-  </si>
-  <si>
-    <t>R$  252,95</t>
-  </si>
-  <si>
-    <t>R$  584,82</t>
-  </si>
-  <si>
-    <t>R$  1.698,42</t>
-  </si>
-  <si>
-    <t>R$  622,81</t>
-  </si>
-  <si>
-    <t>R$  471,77</t>
-  </si>
-  <si>
-    <t>88101/2</t>
-  </si>
-  <si>
-    <t>R$  620,43</t>
-  </si>
-  <si>
-    <t>90001/2</t>
-  </si>
-  <si>
-    <t>R$  213,83</t>
-  </si>
-  <si>
-    <t>86102/2</t>
-  </si>
-  <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
   </si>
   <si>
@@ -2014,18 +2014,42 @@
     <t>R$  20,84</t>
   </si>
   <si>
+    <t>ADM EF/0</t>
+  </si>
+  <si>
+    <t>R$  77,99</t>
+  </si>
+  <si>
+    <t>12/07/26</t>
+  </si>
+  <si>
+    <t>13301/0</t>
+  </si>
+  <si>
+    <t>R$  11,05</t>
+  </si>
+  <si>
+    <t>FlaviaCM0013301</t>
+  </si>
+  <si>
     <t>16003/0</t>
   </si>
   <si>
     <t>R$  66,90</t>
   </si>
   <si>
-    <t>12/07/26</t>
-  </si>
-  <si>
     <t>AnaCAL0016003</t>
   </si>
   <si>
+    <t>76901/0</t>
+  </si>
+  <si>
+    <t>R$  41,15</t>
+  </si>
+  <si>
+    <t>76901JoaoMCC</t>
+  </si>
+  <si>
     <t>49301/0</t>
   </si>
   <si>
@@ -2035,24 +2059,6 @@
     <t>49301GuilhermeBN</t>
   </si>
   <si>
-    <t>13301/0</t>
-  </si>
-  <si>
-    <t>R$  11,05</t>
-  </si>
-  <si>
-    <t>FlaviaCM0013301</t>
-  </si>
-  <si>
-    <t>76901/0</t>
-  </si>
-  <si>
-    <t>R$  41,15</t>
-  </si>
-  <si>
-    <t>76901JoaoMCC</t>
-  </si>
-  <si>
     <t>42001UB/0</t>
   </si>
   <si>
@@ -2062,12 +2068,6 @@
     <t>42001LaysSB</t>
   </si>
   <si>
-    <t>ADM EF/0</t>
-  </si>
-  <si>
-    <t>R$  77,99</t>
-  </si>
-  <si>
     <t>4.03.03.02 Agregados e outros gastos de montagens</t>
   </si>
   <si>
@@ -2254,6 +2254,42 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  7.800,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>R$  2.365,00</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  1.645,16</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
+  </si>
+  <si>
     <t>Estorno emprest jul/1</t>
   </si>
   <si>
@@ -2263,6 +2299,63 @@
     <t>Estorno de empréstimo</t>
   </si>
   <si>
+    <t>Fixo jul26/1</t>
+  </si>
+  <si>
+    <t>R$  354,84</t>
+  </si>
+  <si>
+    <t>R$  1.500,00</t>
+  </si>
+  <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>722/1</t>
+  </si>
+  <si>
+    <t>06/08/26</t>
+  </si>
+  <si>
+    <t>EFRAIM RIBEIRO</t>
+  </si>
+  <si>
+    <t>R$  1.060,00</t>
+  </si>
+  <si>
+    <t>09/07/26</t>
+  </si>
+  <si>
+    <t>Fixo/1</t>
+  </si>
+  <si>
+    <t>R$  2.536,00</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.145,57</t>
+  </si>
+  <si>
+    <t>Denny Lucas - Pagamento 2026</t>
+  </si>
+  <si>
     <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
   </si>
   <si>
@@ -2270,99 +2363,6 @@
   </si>
   <si>
     <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>R$  2.365,00</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Fixo jul26/1</t>
-  </si>
-  <si>
-    <t>R$  354,84</t>
-  </si>
-  <si>
-    <t>R$  1.500,00</t>
-  </si>
-  <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
-    <t>R$  1.645,16</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>EFRAIM RIBEIRO</t>
-  </si>
-  <si>
-    <t>R$  1.060,00</t>
-  </si>
-  <si>
-    <t>09/07/26</t>
-  </si>
-  <si>
-    <t>Fixo/1</t>
-  </si>
-  <si>
-    <t>R$  2.536,00</t>
-  </si>
-  <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  7.800,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
-    <t>722/1</t>
-  </si>
-  <si>
-    <t>06/08/26</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.145,57</t>
-  </si>
-  <si>
-    <t>Denny Lucas - Pagamento 2026</t>
   </si>
   <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
@@ -3211,7 +3211,7 @@
     <t>7.05 = RESULTADO BRUTO</t>
   </si>
   <si>
-    <t>R$ 397.069,31</t>
+    <t>R$ 396.938,25</t>
   </si>
   <si>
     <t>7.06 (-) DESPESAS REGULARES</t>
@@ -3316,7 +3316,7 @@
     <t>7.07 = RESULTADO ANTES DAS DESPESAS E RECEITAS FINANCEIRAS</t>
   </si>
   <si>
-    <t>R$ 17.400,22</t>
+    <t>R$ 17.269,16</t>
   </si>
   <si>
     <t>7.08 (-) DESPESAS E RECEITAS FINANCEIRAS</t>
@@ -3340,7 +3340,7 @@
     <t>7.09 = RESULTADO OPERACIONAL</t>
   </si>
   <si>
-    <t>R$ -33.284,10</t>
+    <t>R$ -33.415,16</t>
   </si>
   <si>
     <t>7.11 = RESULTADO LÍQUIDO DO EXERCÍCIO</t>
@@ -3355,7 +3355,7 @@
     <t>7.50.02 TOTAL DOS CUSTOS VARIÁVEIS</t>
   </si>
   <si>
-    <t>R$ 680.923,48</t>
+    <t>R$ 681.054,54</t>
   </si>
   <si>
     <t>7.50.02.01 Deduções de receita</t>
@@ -3421,7 +3421,7 @@
     <t>7.70 BREAK-EVEN POINT</t>
   </si>
   <si>
-    <t>R$ 1.084.820,58</t>
+    <t>R$ 1.086.664,00</t>
   </si>
   <si>
     <t>7.80.01 Mark Up Negociado</t>
@@ -8974,25 +8974,25 @@
         <v>327</v>
       </c>
       <c r="F111" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="G111" t="s">
         <v>40</v>
       </c>
       <c r="H111" t="s">
+        <v>183</v>
+      </c>
+      <c r="I111" t="s">
         <v>328</v>
       </c>
-      <c r="I111" t="s">
+      <c r="J111" t="s">
+        <v>156</v>
+      </c>
+      <c r="K111" t="s">
+        <v>156</v>
+      </c>
+      <c r="L111" t="s">
         <v>329</v>
-      </c>
-      <c r="J111" t="s">
-        <v>330</v>
-      </c>
-      <c r="K111" t="s">
-        <v>331</v>
-      </c>
-      <c r="L111" t="s">
-        <v>34</v>
       </c>
       <c r="M111" t="s">
         <v>322</v>
@@ -9004,7 +9004,7 @@
         <v>47</v>
       </c>
       <c r="P111" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q111" t="s">
         <v>46</v>
@@ -9027,7 +9027,7 @@
         <v>34</v>
       </c>
       <c r="E112" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F112" t="s">
         <v>39</v>
@@ -9036,16 +9036,16 @@
         <v>40</v>
       </c>
       <c r="H112" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I112" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J112" t="s">
-        <v>335</v>
+        <v>175</v>
       </c>
       <c r="K112" t="s">
-        <v>331</v>
+        <v>156</v>
       </c>
       <c r="L112" t="s">
         <v>34</v>
@@ -9060,7 +9060,7 @@
         <v>47</v>
       </c>
       <c r="P112" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Q112" t="s">
         <v>46</v>
@@ -9083,7 +9083,7 @@
         <v>34</v>
       </c>
       <c r="E113" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F113" t="s">
         <v>39</v>
@@ -9092,16 +9092,16 @@
         <v>40</v>
       </c>
       <c r="H113" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I113" t="s">
         <v>334</v>
       </c>
       <c r="J113" t="s">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="K113" t="s">
-        <v>74</v>
+        <v>336</v>
       </c>
       <c r="L113" t="s">
         <v>34</v>
@@ -9148,16 +9148,16 @@
         <v>40</v>
       </c>
       <c r="H114" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="I114" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J114" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K114" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="L114" t="s">
         <v>34</v>
@@ -9172,7 +9172,7 @@
         <v>47</v>
       </c>
       <c r="P114" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q114" t="s">
         <v>46</v>
@@ -9195,28 +9195,28 @@
         <v>34</v>
       </c>
       <c r="E115" t="s">
+        <v>293</v>
+      </c>
+      <c r="F115" t="s">
+        <v>39</v>
+      </c>
+      <c r="G115" t="s">
+        <v>40</v>
+      </c>
+      <c r="H115" t="s">
+        <v>324</v>
+      </c>
+      <c r="I115" t="s">
         <v>341</v>
       </c>
-      <c r="F115" t="s">
-        <v>207</v>
-      </c>
-      <c r="G115" t="s">
-        <v>40</v>
-      </c>
-      <c r="H115" t="s">
-        <v>342</v>
-      </c>
-      <c r="I115" t="s">
-        <v>343</v>
-      </c>
       <c r="J115" t="s">
-        <v>318</v>
+        <v>247</v>
       </c>
       <c r="K115" t="s">
-        <v>91</v>
+        <v>247</v>
       </c>
       <c r="L115" t="s">
-        <v>344</v>
+        <v>34</v>
       </c>
       <c r="M115" t="s">
         <v>322</v>
@@ -9225,10 +9225,10 @@
         <v>46</v>
       </c>
       <c r="O115" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="P115" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="Q115" t="s">
         <v>46</v>
@@ -9251,7 +9251,7 @@
         <v>34</v>
       </c>
       <c r="E116" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F116" t="s">
         <v>39</v>
@@ -9260,19 +9260,19 @@
         <v>40</v>
       </c>
       <c r="H116" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="I116" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="J116" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K116" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="L116" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="M116" t="s">
         <v>322</v>
@@ -9284,7 +9284,7 @@
         <v>47</v>
       </c>
       <c r="P116" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="Q116" t="s">
         <v>46</v>
@@ -9307,7 +9307,7 @@
         <v>34</v>
       </c>
       <c r="E117" t="s">
-        <v>293</v>
+        <v>345</v>
       </c>
       <c r="F117" t="s">
         <v>39</v>
@@ -9316,19 +9316,19 @@
         <v>40</v>
       </c>
       <c r="H117" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="I117" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J117" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="K117" t="s">
-        <v>247</v>
+        <v>74</v>
       </c>
       <c r="L117" t="s">
-        <v>34</v>
+        <v>347</v>
       </c>
       <c r="M117" t="s">
         <v>322</v>
@@ -9337,10 +9337,10 @@
         <v>46</v>
       </c>
       <c r="O117" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="P117" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="Q117" t="s">
         <v>46</v>
@@ -9363,7 +9363,7 @@
         <v>34</v>
       </c>
       <c r="E118" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F118" t="s">
         <v>39</v>
@@ -9372,19 +9372,19 @@
         <v>40</v>
       </c>
       <c r="H118" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="I118" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="J118" t="s">
-        <v>351</v>
+        <v>297</v>
       </c>
       <c r="K118" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="L118" t="s">
-        <v>352</v>
+        <v>34</v>
       </c>
       <c r="M118" t="s">
         <v>322</v>
@@ -9396,7 +9396,7 @@
         <v>47</v>
       </c>
       <c r="P118" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="Q118" t="s">
         <v>46</v>
@@ -9419,28 +9419,28 @@
         <v>34</v>
       </c>
       <c r="E119" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="F119" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G119" t="s">
         <v>40</v>
       </c>
       <c r="H119" t="s">
-        <v>183</v>
+        <v>338</v>
       </c>
       <c r="I119" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="J119" t="s">
-        <v>156</v>
+        <v>351</v>
       </c>
       <c r="K119" t="s">
-        <v>156</v>
+        <v>352</v>
       </c>
       <c r="L119" t="s">
-        <v>355</v>
+        <v>34</v>
       </c>
       <c r="M119" t="s">
         <v>322</v>
@@ -9452,7 +9452,7 @@
         <v>47</v>
       </c>
       <c r="P119" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="Q119" t="s">
         <v>46</v>
@@ -9475,28 +9475,28 @@
         <v>34</v>
       </c>
       <c r="E120" t="s">
+        <v>353</v>
+      </c>
+      <c r="F120" t="s">
+        <v>207</v>
+      </c>
+      <c r="G120" t="s">
+        <v>40</v>
+      </c>
+      <c r="H120" t="s">
+        <v>354</v>
+      </c>
+      <c r="I120" t="s">
+        <v>355</v>
+      </c>
+      <c r="J120" t="s">
+        <v>318</v>
+      </c>
+      <c r="K120" t="s">
+        <v>91</v>
+      </c>
+      <c r="L120" t="s">
         <v>356</v>
-      </c>
-      <c r="F120" t="s">
-        <v>39</v>
-      </c>
-      <c r="G120" t="s">
-        <v>40</v>
-      </c>
-      <c r="H120" t="s">
-        <v>328</v>
-      </c>
-      <c r="I120" t="s">
-        <v>357</v>
-      </c>
-      <c r="J120" t="s">
-        <v>175</v>
-      </c>
-      <c r="K120" t="s">
-        <v>156</v>
-      </c>
-      <c r="L120" t="s">
-        <v>34</v>
       </c>
       <c r="M120" t="s">
         <v>322</v>
@@ -9508,7 +9508,7 @@
         <v>47</v>
       </c>
       <c r="P120" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="Q120" t="s">
         <v>46</v>
@@ -9531,7 +9531,7 @@
         <v>34</v>
       </c>
       <c r="E121" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F121" t="s">
         <v>39</v>
@@ -9540,16 +9540,16 @@
         <v>40</v>
       </c>
       <c r="H121" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="I121" t="s">
+        <v>358</v>
+      </c>
+      <c r="J121" t="s">
         <v>359</v>
       </c>
-      <c r="J121" t="s">
-        <v>297</v>
-      </c>
       <c r="K121" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="L121" t="s">
         <v>360</v>
@@ -9564,7 +9564,7 @@
         <v>47</v>
       </c>
       <c r="P121" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q121" t="s">
         <v>46</v>
@@ -9596,7 +9596,7 @@
         <v>40</v>
       </c>
       <c r="H122" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="I122" t="s">
         <v>362</v>
@@ -9652,7 +9652,7 @@
         <v>40</v>
       </c>
       <c r="H123" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="I123" t="s">
         <v>366</v>
@@ -12682,7 +12682,7 @@
         <v>474</v>
       </c>
       <c r="J177" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K177" t="s">
         <v>247</v>
@@ -12738,7 +12738,7 @@
         <v>475</v>
       </c>
       <c r="J178" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K178" t="s">
         <v>247</v>
@@ -12794,7 +12794,7 @@
         <v>477</v>
       </c>
       <c r="J179" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K179" t="s">
         <v>247</v>
@@ -12850,7 +12850,7 @@
         <v>478</v>
       </c>
       <c r="J180" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K180" t="s">
         <v>247</v>
@@ -12906,7 +12906,7 @@
         <v>479</v>
       </c>
       <c r="J181" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K181" t="s">
         <v>247</v>
@@ -12962,7 +12962,7 @@
         <v>480</v>
       </c>
       <c r="J182" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K182" t="s">
         <v>247</v>
@@ -13018,7 +13018,7 @@
         <v>481</v>
       </c>
       <c r="J183" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K183" t="s">
         <v>247</v>
@@ -13074,7 +13074,7 @@
         <v>482</v>
       </c>
       <c r="J184" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K184" t="s">
         <v>247</v>
@@ -13130,7 +13130,7 @@
         <v>484</v>
       </c>
       <c r="J185" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K185" t="s">
         <v>247</v>
@@ -13186,7 +13186,7 @@
         <v>485</v>
       </c>
       <c r="J186" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K186" t="s">
         <v>247</v>
@@ -13242,7 +13242,7 @@
         <v>486</v>
       </c>
       <c r="J187" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K187" t="s">
         <v>247</v>
@@ -13298,7 +13298,7 @@
         <v>488</v>
       </c>
       <c r="J188" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K188" t="s">
         <v>247</v>
@@ -13354,7 +13354,7 @@
         <v>490</v>
       </c>
       <c r="J189" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K189" t="s">
         <v>247</v>
@@ -13410,7 +13410,7 @@
         <v>491</v>
       </c>
       <c r="J190" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K190" t="s">
         <v>247</v>
@@ -13466,7 +13466,7 @@
         <v>492</v>
       </c>
       <c r="J191" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K191" t="s">
         <v>247</v>
@@ -13522,7 +13522,7 @@
         <v>493</v>
       </c>
       <c r="J192" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K192" t="s">
         <v>247</v>
@@ -13578,7 +13578,7 @@
         <v>494</v>
       </c>
       <c r="J193" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K193" t="s">
         <v>247</v>
@@ -13634,7 +13634,7 @@
         <v>495</v>
       </c>
       <c r="J194" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K194" t="s">
         <v>59</v>
@@ -13970,7 +13970,7 @@
         <v>507</v>
       </c>
       <c r="J200" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K200" t="s">
         <v>247</v>
@@ -14026,7 +14026,7 @@
         <v>508</v>
       </c>
       <c r="J201" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K201" t="s">
         <v>59</v>
@@ -14082,7 +14082,7 @@
         <v>509</v>
       </c>
       <c r="J202" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K202" t="s">
         <v>247</v>
@@ -14138,7 +14138,7 @@
         <v>510</v>
       </c>
       <c r="J203" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K203" t="s">
         <v>247</v>
@@ -14194,7 +14194,7 @@
         <v>511</v>
       </c>
       <c r="J204" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K204" t="s">
         <v>247</v>
@@ -14250,7 +14250,7 @@
         <v>512</v>
       </c>
       <c r="J205" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K205" t="s">
         <v>247</v>
@@ -14306,7 +14306,7 @@
         <v>513</v>
       </c>
       <c r="J206" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K206" t="s">
         <v>247</v>
@@ -14362,7 +14362,7 @@
         <v>514</v>
       </c>
       <c r="J207" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K207" t="s">
         <v>247</v>
@@ -14418,7 +14418,7 @@
         <v>515</v>
       </c>
       <c r="J208" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K208" t="s">
         <v>247</v>
@@ -14474,7 +14474,7 @@
         <v>516</v>
       </c>
       <c r="J209" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K209" t="s">
         <v>247</v>
@@ -14530,7 +14530,7 @@
         <v>517</v>
       </c>
       <c r="J210" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K210" t="s">
         <v>247</v>
@@ -14586,7 +14586,7 @@
         <v>518</v>
       </c>
       <c r="J211" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K211" t="s">
         <v>247</v>
@@ -14642,7 +14642,7 @@
         <v>519</v>
       </c>
       <c r="J212" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K212" t="s">
         <v>247</v>
@@ -14698,7 +14698,7 @@
         <v>520</v>
       </c>
       <c r="J213" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K213" t="s">
         <v>247</v>
@@ -14754,7 +14754,7 @@
         <v>521</v>
       </c>
       <c r="J214" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K214" t="s">
         <v>247</v>
@@ -14810,7 +14810,7 @@
         <v>522</v>
       </c>
       <c r="J215" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K215" t="s">
         <v>247</v>
@@ -14866,7 +14866,7 @@
         <v>524</v>
       </c>
       <c r="J216" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K216" t="s">
         <v>247</v>
@@ -14922,7 +14922,7 @@
         <v>525</v>
       </c>
       <c r="J217" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K217" t="s">
         <v>247</v>
@@ -14978,7 +14978,7 @@
         <v>526</v>
       </c>
       <c r="J218" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K218" t="s">
         <v>247</v>
@@ -15034,7 +15034,7 @@
         <v>528</v>
       </c>
       <c r="J219" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K219" t="s">
         <v>247</v>
@@ -15090,7 +15090,7 @@
         <v>529</v>
       </c>
       <c r="J220" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K220" t="s">
         <v>247</v>
@@ -15146,7 +15146,7 @@
         <v>530</v>
       </c>
       <c r="J221" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K221" t="s">
         <v>247</v>
@@ -15202,7 +15202,7 @@
         <v>531</v>
       </c>
       <c r="J222" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K222" t="s">
         <v>247</v>
@@ -15258,7 +15258,7 @@
         <v>532</v>
       </c>
       <c r="J223" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K223" t="s">
         <v>247</v>
@@ -15314,7 +15314,7 @@
         <v>534</v>
       </c>
       <c r="J224" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K224" t="s">
         <v>247</v>
@@ -15370,7 +15370,7 @@
         <v>536</v>
       </c>
       <c r="J225" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K225" t="s">
         <v>247</v>
@@ -15426,7 +15426,7 @@
         <v>537</v>
       </c>
       <c r="J226" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K226" t="s">
         <v>247</v>
@@ -15482,7 +15482,7 @@
         <v>538</v>
       </c>
       <c r="J227" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K227" t="s">
         <v>247</v>
@@ -15538,7 +15538,7 @@
         <v>540</v>
       </c>
       <c r="J228" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K228" t="s">
         <v>247</v>
@@ -15594,7 +15594,7 @@
         <v>478</v>
       </c>
       <c r="J229" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K229" t="s">
         <v>247</v>
@@ -15650,7 +15650,7 @@
         <v>475</v>
       </c>
       <c r="J230" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K230" t="s">
         <v>247</v>
@@ -15706,7 +15706,7 @@
         <v>477</v>
       </c>
       <c r="J231" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K231" t="s">
         <v>247</v>
@@ -15762,7 +15762,7 @@
         <v>541</v>
       </c>
       <c r="J232" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K232" t="s">
         <v>247</v>
@@ -15818,7 +15818,7 @@
         <v>479</v>
       </c>
       <c r="J233" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K233" t="s">
         <v>247</v>
@@ -15874,7 +15874,7 @@
         <v>480</v>
       </c>
       <c r="J234" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K234" t="s">
         <v>247</v>
@@ -15930,7 +15930,7 @@
         <v>481</v>
       </c>
       <c r="J235" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K235" t="s">
         <v>247</v>
@@ -15986,7 +15986,7 @@
         <v>482</v>
       </c>
       <c r="J236" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K236" t="s">
         <v>247</v>
@@ -16042,7 +16042,7 @@
         <v>484</v>
       </c>
       <c r="J237" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K237" t="s">
         <v>247</v>
@@ -16098,7 +16098,7 @@
         <v>485</v>
       </c>
       <c r="J238" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K238" t="s">
         <v>247</v>
@@ -16154,7 +16154,7 @@
         <v>486</v>
       </c>
       <c r="J239" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K239" t="s">
         <v>247</v>
@@ -16210,7 +16210,7 @@
         <v>488</v>
       </c>
       <c r="J240" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K240" t="s">
         <v>247</v>
@@ -16266,7 +16266,7 @@
         <v>490</v>
       </c>
       <c r="J241" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K241" t="s">
         <v>247</v>
@@ -16322,7 +16322,7 @@
         <v>491</v>
       </c>
       <c r="J242" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K242" t="s">
         <v>247</v>
@@ -16378,7 +16378,7 @@
         <v>492</v>
       </c>
       <c r="J243" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K243" t="s">
         <v>247</v>
@@ -16434,7 +16434,7 @@
         <v>493</v>
       </c>
       <c r="J244" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K244" t="s">
         <v>247</v>
@@ -16490,7 +16490,7 @@
         <v>494</v>
       </c>
       <c r="J245" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K245" t="s">
         <v>247</v>
@@ -16546,7 +16546,7 @@
         <v>495</v>
       </c>
       <c r="J246" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K246" t="s">
         <v>59</v>
@@ -16602,7 +16602,7 @@
         <v>542</v>
       </c>
       <c r="J247" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K247" t="s">
         <v>247</v>
@@ -16658,7 +16658,7 @@
         <v>544</v>
       </c>
       <c r="J248" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K248" t="s">
         <v>247</v>
@@ -16714,7 +16714,7 @@
         <v>545</v>
       </c>
       <c r="J249" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K249" t="s">
         <v>247</v>
@@ -16770,7 +16770,7 @@
         <v>546</v>
       </c>
       <c r="J250" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K250" t="s">
         <v>247</v>
@@ -16826,7 +16826,7 @@
         <v>547</v>
       </c>
       <c r="J251" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K251" t="s">
         <v>247</v>
@@ -16882,7 +16882,7 @@
         <v>548</v>
       </c>
       <c r="J252" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K252" t="s">
         <v>247</v>
@@ -16938,7 +16938,7 @@
         <v>549</v>
       </c>
       <c r="J253" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K253" t="s">
         <v>247</v>
@@ -16994,7 +16994,7 @@
         <v>550</v>
       </c>
       <c r="J254" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K254" t="s">
         <v>247</v>
@@ -17050,7 +17050,7 @@
         <v>551</v>
       </c>
       <c r="J255" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K255" t="s">
         <v>247</v>
@@ -17106,7 +17106,7 @@
         <v>552</v>
       </c>
       <c r="J256" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K256" t="s">
         <v>59</v>
@@ -18002,7 +18002,7 @@
         <v>573</v>
       </c>
       <c r="J272" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K272" t="s">
         <v>247</v>
@@ -18058,7 +18058,7 @@
         <v>574</v>
       </c>
       <c r="J273" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K273" t="s">
         <v>247</v>
@@ -18114,7 +18114,7 @@
         <v>575</v>
       </c>
       <c r="J274" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K274" t="s">
         <v>247</v>
@@ -18170,7 +18170,7 @@
         <v>576</v>
       </c>
       <c r="J275" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K275" t="s">
         <v>247</v>
@@ -18226,7 +18226,7 @@
         <v>579</v>
       </c>
       <c r="J276" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K276" t="s">
         <v>247</v>
@@ -18267,7 +18267,7 @@
         <v>33</v>
       </c>
       <c r="E277" t="s">
-        <v>405</v>
+        <v>583</v>
       </c>
       <c r="F277" t="s">
         <v>497</v>
@@ -18279,13 +18279,13 @@
         <v>236</v>
       </c>
       <c r="I277" t="s">
-        <v>583</v>
+        <v>563</v>
       </c>
       <c r="J277" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="K277" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="L277" t="s">
         <v>34</v>
@@ -18323,7 +18323,7 @@
         <v>34</v>
       </c>
       <c r="E278" t="s">
-        <v>305</v>
+        <v>382</v>
       </c>
       <c r="F278" t="s">
         <v>497</v>
@@ -18332,16 +18332,16 @@
         <v>40</v>
       </c>
       <c r="H278" t="s">
+        <v>578</v>
+      </c>
+      <c r="I278" t="s">
         <v>584</v>
       </c>
-      <c r="I278" t="s">
-        <v>585</v>
-      </c>
       <c r="J278" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="K278" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="L278" t="s">
         <v>34</v>
@@ -18391,7 +18391,7 @@
         <v>236</v>
       </c>
       <c r="I279" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J279" t="s">
         <v>59</v>
@@ -18435,25 +18435,25 @@
         <v>34</v>
       </c>
       <c r="E280" t="s">
-        <v>417</v>
+        <v>300</v>
       </c>
       <c r="F280" t="s">
-        <v>497</v>
+        <v>243</v>
       </c>
       <c r="G280" t="s">
         <v>40</v>
       </c>
       <c r="H280" t="s">
-        <v>236</v>
+        <v>578</v>
       </c>
       <c r="I280" t="s">
-        <v>587</v>
+        <v>496</v>
       </c>
       <c r="J280" t="s">
-        <v>59</v>
+        <v>307</v>
       </c>
       <c r="K280" t="s">
-        <v>59</v>
+        <v>247</v>
       </c>
       <c r="L280" t="s">
         <v>34</v>
@@ -18465,13 +18465,13 @@
         <v>46</v>
       </c>
       <c r="O280" t="s">
-        <v>34</v>
+        <v>303</v>
       </c>
       <c r="P280" t="s">
-        <v>34</v>
+        <v>496</v>
       </c>
       <c r="Q280" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R280" t="s">
         <v>34</v>
@@ -18491,25 +18491,25 @@
         <v>34</v>
       </c>
       <c r="E281" t="s">
-        <v>588</v>
+        <v>258</v>
       </c>
       <c r="F281" t="s">
-        <v>497</v>
+        <v>243</v>
       </c>
       <c r="G281" t="s">
         <v>40</v>
       </c>
       <c r="H281" t="s">
-        <v>236</v>
+        <v>586</v>
       </c>
       <c r="I281" t="s">
-        <v>566</v>
+        <v>477</v>
       </c>
       <c r="J281" t="s">
-        <v>58</v>
+        <v>335</v>
       </c>
       <c r="K281" t="s">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="L281" t="s">
         <v>34</v>
@@ -18521,13 +18521,13 @@
         <v>46</v>
       </c>
       <c r="O281" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="P281" t="s">
-        <v>34</v>
+        <v>477</v>
       </c>
       <c r="Q281" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R281" t="s">
         <v>34</v>
@@ -18547,25 +18547,25 @@
         <v>34</v>
       </c>
       <c r="E282" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F282" t="s">
-        <v>243</v>
+        <v>497</v>
       </c>
       <c r="G282" t="s">
         <v>40</v>
       </c>
       <c r="H282" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="I282" t="s">
-        <v>496</v>
+        <v>588</v>
       </c>
       <c r="J282" t="s">
-        <v>307</v>
+        <v>58</v>
       </c>
       <c r="K282" t="s">
-        <v>247</v>
+        <v>58</v>
       </c>
       <c r="L282" t="s">
         <v>34</v>
@@ -18577,13 +18577,13 @@
         <v>46</v>
       </c>
       <c r="O282" t="s">
-        <v>303</v>
+        <v>34</v>
       </c>
       <c r="P282" t="s">
-        <v>496</v>
+        <v>34</v>
       </c>
       <c r="Q282" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R282" t="s">
         <v>34</v>
@@ -18603,7 +18603,7 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>258</v>
+        <v>589</v>
       </c>
       <c r="F283" t="s">
         <v>243</v>
@@ -18612,13 +18612,13 @@
         <v>40</v>
       </c>
       <c r="H283" t="s">
-        <v>589</v>
+        <v>539</v>
       </c>
       <c r="I283" t="s">
-        <v>477</v>
+        <v>590</v>
       </c>
       <c r="J283" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K283" t="s">
         <v>247</v>
@@ -18633,10 +18633,10 @@
         <v>46</v>
       </c>
       <c r="O283" t="s">
-        <v>88</v>
+        <v>591</v>
       </c>
       <c r="P283" t="s">
-        <v>477</v>
+        <v>590</v>
       </c>
       <c r="Q283" t="s">
         <v>46</v>
@@ -18659,7 +18659,7 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F284" t="s">
         <v>243</v>
@@ -18671,10 +18671,10 @@
         <v>539</v>
       </c>
       <c r="I284" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="J284" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K284" t="s">
         <v>247</v>
@@ -18689,10 +18689,10 @@
         <v>46</v>
       </c>
       <c r="O284" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="P284" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="Q284" t="s">
         <v>46</v>
@@ -18715,25 +18715,25 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F285" t="s">
-        <v>243</v>
+        <v>497</v>
       </c>
       <c r="G285" t="s">
         <v>40</v>
       </c>
       <c r="H285" t="s">
-        <v>539</v>
+        <v>236</v>
       </c>
       <c r="I285" t="s">
-        <v>594</v>
+        <v>566</v>
       </c>
       <c r="J285" t="s">
-        <v>330</v>
+        <v>58</v>
       </c>
       <c r="K285" t="s">
-        <v>247</v>
+        <v>58</v>
       </c>
       <c r="L285" t="s">
         <v>34</v>
@@ -18745,13 +18745,13 @@
         <v>46</v>
       </c>
       <c r="O285" t="s">
-        <v>595</v>
+        <v>34</v>
       </c>
       <c r="P285" t="s">
-        <v>594</v>
+        <v>34</v>
       </c>
       <c r="Q285" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R285" t="s">
         <v>34</v>
@@ -18771,7 +18771,7 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="F286" t="s">
         <v>243</v>
@@ -18780,16 +18780,16 @@
         <v>40</v>
       </c>
       <c r="H286" t="s">
-        <v>539</v>
+        <v>578</v>
       </c>
       <c r="I286" t="s">
-        <v>495</v>
+        <v>596</v>
       </c>
       <c r="J286" t="s">
         <v>307</v>
       </c>
       <c r="K286" t="s">
-        <v>59</v>
+        <v>247</v>
       </c>
       <c r="L286" t="s">
         <v>34</v>
@@ -18801,10 +18801,10 @@
         <v>46</v>
       </c>
       <c r="O286" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="P286" t="s">
-        <v>495</v>
+        <v>596</v>
       </c>
       <c r="Q286" t="s">
         <v>46</v>
@@ -18883,7 +18883,7 @@
         <v>34</v>
       </c>
       <c r="E288" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="F288" t="s">
         <v>243</v>
@@ -18892,16 +18892,16 @@
         <v>40</v>
       </c>
       <c r="H288" t="s">
-        <v>578</v>
+        <v>539</v>
       </c>
       <c r="I288" t="s">
-        <v>596</v>
+        <v>495</v>
       </c>
       <c r="J288" t="s">
         <v>307</v>
       </c>
       <c r="K288" t="s">
-        <v>247</v>
+        <v>59</v>
       </c>
       <c r="L288" t="s">
         <v>34</v>
@@ -18913,10 +18913,10 @@
         <v>46</v>
       </c>
       <c r="O288" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="P288" t="s">
-        <v>596</v>
+        <v>495</v>
       </c>
       <c r="Q288" t="s">
         <v>46</v>
@@ -18939,7 +18939,7 @@
         <v>34</v>
       </c>
       <c r="E289" t="s">
-        <v>313</v>
+        <v>396</v>
       </c>
       <c r="F289" t="s">
         <v>497</v>
@@ -18948,16 +18948,16 @@
         <v>40</v>
       </c>
       <c r="H289" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="I289" t="s">
-        <v>484</v>
+        <v>597</v>
       </c>
       <c r="J289" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="K289" t="s">
-        <v>247</v>
+        <v>109</v>
       </c>
       <c r="L289" t="s">
         <v>34</v>
@@ -18995,7 +18995,7 @@
         <v>34</v>
       </c>
       <c r="E290" t="s">
-        <v>396</v>
+        <v>295</v>
       </c>
       <c r="F290" t="s">
         <v>497</v>
@@ -19004,16 +19004,16 @@
         <v>40</v>
       </c>
       <c r="H290" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="I290" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="J290" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="K290" t="s">
-        <v>109</v>
+        <v>247</v>
       </c>
       <c r="L290" t="s">
         <v>34</v>
@@ -19051,7 +19051,7 @@
         <v>34</v>
       </c>
       <c r="E291" t="s">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="F291" t="s">
         <v>497</v>
@@ -19063,13 +19063,13 @@
         <v>236</v>
       </c>
       <c r="I291" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="J291" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="K291" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="L291" t="s">
         <v>34</v>
@@ -19107,7 +19107,7 @@
         <v>34</v>
       </c>
       <c r="E292" t="s">
-        <v>409</v>
+        <v>313</v>
       </c>
       <c r="F292" t="s">
         <v>497</v>
@@ -19116,16 +19116,16 @@
         <v>40</v>
       </c>
       <c r="H292" t="s">
-        <v>236</v>
+        <v>587</v>
       </c>
       <c r="I292" t="s">
-        <v>599</v>
+        <v>484</v>
       </c>
       <c r="J292" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="K292" t="s">
-        <v>146</v>
+        <v>247</v>
       </c>
       <c r="L292" t="s">
         <v>34</v>
@@ -19163,7 +19163,7 @@
         <v>34</v>
       </c>
       <c r="E293" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="F293" t="s">
         <v>497</v>
@@ -19172,16 +19172,16 @@
         <v>40</v>
       </c>
       <c r="H293" t="s">
-        <v>578</v>
+        <v>236</v>
       </c>
       <c r="I293" t="s">
         <v>600</v>
       </c>
       <c r="J293" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="K293" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="L293" t="s">
         <v>34</v>
@@ -19231,13 +19231,13 @@
         <v>236</v>
       </c>
       <c r="I294" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="J294" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="K294" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L294" t="s">
         <v>34</v>
@@ -19275,7 +19275,7 @@
         <v>34</v>
       </c>
       <c r="E295" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="F295" t="s">
         <v>497</v>
@@ -19284,16 +19284,16 @@
         <v>40</v>
       </c>
       <c r="H295" t="s">
-        <v>578</v>
+        <v>236</v>
       </c>
       <c r="I295" t="s">
         <v>602</v>
       </c>
       <c r="J295" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="K295" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="L295" t="s">
         <v>34</v>
@@ -19387,7 +19387,7 @@
         <v>34</v>
       </c>
       <c r="E297" t="s">
-        <v>295</v>
+        <v>392</v>
       </c>
       <c r="F297" t="s">
         <v>497</v>
@@ -19396,16 +19396,16 @@
         <v>40</v>
       </c>
       <c r="H297" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="I297" t="s">
         <v>604</v>
       </c>
       <c r="J297" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="K297" t="s">
-        <v>247</v>
+        <v>132</v>
       </c>
       <c r="L297" t="s">
         <v>34</v>
@@ -19443,7 +19443,7 @@
         <v>34</v>
       </c>
       <c r="E298" t="s">
-        <v>605</v>
+        <v>405</v>
       </c>
       <c r="F298" t="s">
         <v>497</v>
@@ -19455,13 +19455,13 @@
         <v>236</v>
       </c>
       <c r="I298" t="s">
-        <v>541</v>
+        <v>605</v>
       </c>
       <c r="J298" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="K298" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="L298" t="s">
         <v>34</v>
@@ -21642,7 +21642,7 @@
         <v>665</v>
       </c>
       <c r="J337" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K337" t="s">
         <v>666</v>
@@ -21657,7 +21657,7 @@
         <v>46</v>
       </c>
       <c r="O337" t="s">
-        <v>667</v>
+        <v>47</v>
       </c>
       <c r="P337" t="s">
         <v>665</v>
@@ -21683,7 +21683,7 @@
         <v>34</v>
       </c>
       <c r="E338" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F338" t="s">
         <v>39</v>
@@ -21695,10 +21695,10 @@
         <v>660</v>
       </c>
       <c r="I338" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="J338" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K338" t="s">
         <v>666</v>
@@ -21713,10 +21713,10 @@
         <v>46</v>
       </c>
       <c r="O338" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P338" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="Q338" t="s">
         <v>46</v>
@@ -21739,7 +21739,7 @@
         <v>34</v>
       </c>
       <c r="E339" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F339" t="s">
         <v>39</v>
@@ -21751,10 +21751,10 @@
         <v>660</v>
       </c>
       <c r="I339" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="J339" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K339" t="s">
         <v>666</v>
@@ -21769,10 +21769,10 @@
         <v>46</v>
       </c>
       <c r="O339" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="P339" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="Q339" t="s">
         <v>46</v>
@@ -21795,7 +21795,7 @@
         <v>34</v>
       </c>
       <c r="E340" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F340" t="s">
         <v>39</v>
@@ -21807,10 +21807,10 @@
         <v>660</v>
       </c>
       <c r="I340" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="J340" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K340" t="s">
         <v>666</v>
@@ -21825,10 +21825,10 @@
         <v>46</v>
       </c>
       <c r="O340" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="P340" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="Q340" t="s">
         <v>46</v>
@@ -21851,7 +21851,7 @@
         <v>34</v>
       </c>
       <c r="E341" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="F341" t="s">
         <v>39</v>
@@ -21863,10 +21863,10 @@
         <v>660</v>
       </c>
       <c r="I341" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J341" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K341" t="s">
         <v>666</v>
@@ -21881,10 +21881,10 @@
         <v>46</v>
       </c>
       <c r="O341" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="P341" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="Q341" t="s">
         <v>46</v>
@@ -21907,7 +21907,7 @@
         <v>34</v>
       </c>
       <c r="E342" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F342" t="s">
         <v>39</v>
@@ -21919,10 +21919,10 @@
         <v>660</v>
       </c>
       <c r="I342" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="J342" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K342" t="s">
         <v>666</v>
@@ -21937,10 +21937,10 @@
         <v>46</v>
       </c>
       <c r="O342" t="s">
-        <v>47</v>
+        <v>681</v>
       </c>
       <c r="P342" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="Q342" t="s">
         <v>46</v>
@@ -22594,10 +22594,10 @@
         <v>687</v>
       </c>
       <c r="J354" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="K354" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="L354" t="s">
         <v>34</v>
@@ -24147,25 +24147,25 @@
         <v>33</v>
       </c>
       <c r="E382" t="s">
+        <v>709</v>
+      </c>
+      <c r="F382" t="s">
+        <v>207</v>
+      </c>
+      <c r="G382" t="s">
+        <v>40</v>
+      </c>
+      <c r="H382" t="s">
         <v>744</v>
-      </c>
-      <c r="F382" t="s">
-        <v>39</v>
-      </c>
-      <c r="G382" t="s">
-        <v>40</v>
-      </c>
-      <c r="H382" t="s">
-        <v>535</v>
       </c>
       <c r="I382" t="s">
         <v>745</v>
       </c>
       <c r="J382" t="s">
-        <v>318</v>
+        <v>712</v>
       </c>
       <c r="K382" t="s">
-        <v>318</v>
+        <v>363</v>
       </c>
       <c r="L382" t="s">
         <v>746</v>
@@ -24315,7 +24315,7 @@
         <v>34</v>
       </c>
       <c r="E385" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="F385" t="s">
         <v>207</v>
@@ -24324,13 +24324,13 @@
         <v>40</v>
       </c>
       <c r="H385" t="s">
+        <v>473</v>
+      </c>
+      <c r="I385" t="s">
         <v>753</v>
       </c>
-      <c r="I385" t="s">
+      <c r="J385" t="s">
         <v>754</v>
-      </c>
-      <c r="J385" t="s">
-        <v>712</v>
       </c>
       <c r="K385" t="s">
         <v>363</v>
@@ -24348,7 +24348,7 @@
         <v>47</v>
       </c>
       <c r="P385" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="Q385" t="s">
         <v>46</v>
@@ -24380,7 +24380,7 @@
         <v>40</v>
       </c>
       <c r="H386" t="s">
-        <v>589</v>
+        <v>535</v>
       </c>
       <c r="I386" t="s">
         <v>757</v>
@@ -24389,10 +24389,10 @@
         <v>318</v>
       </c>
       <c r="K386" t="s">
-        <v>452</v>
+        <v>318</v>
       </c>
       <c r="L386" t="s">
-        <v>34</v>
+        <v>758</v>
       </c>
       <c r="M386" t="s">
         <v>743</v>
@@ -24427,28 +24427,28 @@
         <v>34</v>
       </c>
       <c r="E387" t="s">
-        <v>182</v>
+        <v>759</v>
       </c>
       <c r="F387" t="s">
-        <v>207</v>
+        <v>39</v>
       </c>
       <c r="G387" t="s">
         <v>40</v>
       </c>
       <c r="H387" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="I387" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="J387" t="s">
-        <v>759</v>
+        <v>318</v>
       </c>
       <c r="K387" t="s">
-        <v>363</v>
+        <v>452</v>
       </c>
       <c r="L387" t="s">
-        <v>760</v>
+        <v>34</v>
       </c>
       <c r="M387" t="s">
         <v>743</v>
@@ -24460,7 +24460,7 @@
         <v>47</v>
       </c>
       <c r="P387" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="Q387" t="s">
         <v>46</v>
@@ -24483,7 +24483,7 @@
         <v>34</v>
       </c>
       <c r="E388" t="s">
-        <v>718</v>
+        <v>182</v>
       </c>
       <c r="F388" t="s">
         <v>207</v>
@@ -24492,7 +24492,7 @@
         <v>40</v>
       </c>
       <c r="H388" t="s">
-        <v>473</v>
+        <v>539</v>
       </c>
       <c r="I388" t="s">
         <v>761</v>
@@ -24539,7 +24539,7 @@
         <v>34</v>
       </c>
       <c r="E389" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="F389" t="s">
         <v>39</v>
@@ -24548,16 +24548,16 @@
         <v>40</v>
       </c>
       <c r="H389" t="s">
-        <v>764</v>
+        <v>578</v>
       </c>
       <c r="I389" t="s">
+        <v>122</v>
+      </c>
+      <c r="J389" t="s">
         <v>765</v>
       </c>
-      <c r="J389" t="s">
-        <v>766</v>
-      </c>
       <c r="K389" t="s">
-        <v>97</v>
+        <v>318</v>
       </c>
       <c r="L389" t="s">
         <v>34</v>
@@ -24572,7 +24572,7 @@
         <v>47</v>
       </c>
       <c r="P389" t="s">
-        <v>765</v>
+        <v>122</v>
       </c>
       <c r="Q389" t="s">
         <v>46</v>
@@ -24595,7 +24595,7 @@
         <v>34</v>
       </c>
       <c r="E390" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="F390" t="s">
         <v>39</v>
@@ -24604,16 +24604,16 @@
         <v>40</v>
       </c>
       <c r="H390" t="s">
-        <v>527</v>
+        <v>766</v>
       </c>
       <c r="I390" t="s">
+        <v>767</v>
+      </c>
+      <c r="J390" t="s">
         <v>768</v>
       </c>
-      <c r="J390" t="s">
-        <v>318</v>
-      </c>
       <c r="K390" t="s">
-        <v>318</v>
+        <v>97</v>
       </c>
       <c r="L390" t="s">
         <v>34</v>
@@ -24628,7 +24628,7 @@
         <v>47</v>
       </c>
       <c r="P390" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="Q390" t="s">
         <v>46</v>
@@ -24651,28 +24651,28 @@
         <v>34</v>
       </c>
       <c r="E391" t="s">
-        <v>182</v>
+        <v>769</v>
       </c>
       <c r="F391" t="s">
-        <v>207</v>
+        <v>39</v>
       </c>
       <c r="G391" t="s">
         <v>40</v>
       </c>
       <c r="H391" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="I391" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="J391" t="s">
-        <v>769</v>
+        <v>318</v>
       </c>
       <c r="K391" t="s">
-        <v>363</v>
+        <v>318</v>
       </c>
       <c r="L391" t="s">
-        <v>770</v>
+        <v>34</v>
       </c>
       <c r="M391" t="s">
         <v>743</v>
@@ -24684,7 +24684,7 @@
         <v>47</v>
       </c>
       <c r="P391" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="Q391" t="s">
         <v>46</v>
@@ -24719,7 +24719,7 @@
         <v>771</v>
       </c>
       <c r="I392" t="s">
-        <v>772</v>
+        <v>122</v>
       </c>
       <c r="J392" t="s">
         <v>712</v>
@@ -24728,7 +24728,7 @@
         <v>363</v>
       </c>
       <c r="L392" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="M392" t="s">
         <v>743</v>
@@ -24740,7 +24740,7 @@
         <v>47</v>
       </c>
       <c r="P392" t="s">
-        <v>772</v>
+        <v>122</v>
       </c>
       <c r="Q392" t="s">
         <v>46</v>
@@ -24763,28 +24763,28 @@
         <v>34</v>
       </c>
       <c r="E393" t="s">
+        <v>182</v>
+      </c>
+      <c r="F393" t="s">
+        <v>207</v>
+      </c>
+      <c r="G393" t="s">
+        <v>40</v>
+      </c>
+      <c r="H393" t="s">
+        <v>543</v>
+      </c>
+      <c r="I393" t="s">
+        <v>770</v>
+      </c>
+      <c r="J393" t="s">
+        <v>773</v>
+      </c>
+      <c r="K393" t="s">
+        <v>363</v>
+      </c>
+      <c r="L393" t="s">
         <v>774</v>
-      </c>
-      <c r="F393" t="s">
-        <v>39</v>
-      </c>
-      <c r="G393" t="s">
-        <v>40</v>
-      </c>
-      <c r="H393" t="s">
-        <v>578</v>
-      </c>
-      <c r="I393" t="s">
-        <v>122</v>
-      </c>
-      <c r="J393" t="s">
-        <v>775</v>
-      </c>
-      <c r="K393" t="s">
-        <v>318</v>
-      </c>
-      <c r="L393" t="s">
-        <v>34</v>
       </c>
       <c r="M393" t="s">
         <v>743</v>
@@ -24796,7 +24796,7 @@
         <v>47</v>
       </c>
       <c r="P393" t="s">
-        <v>122</v>
+        <v>770</v>
       </c>
       <c r="Q393" t="s">
         <v>46</v>
@@ -24828,10 +24828,10 @@
         <v>40</v>
       </c>
       <c r="H394" t="s">
+        <v>775</v>
+      </c>
+      <c r="I394" t="s">
         <v>776</v>
-      </c>
-      <c r="I394" t="s">
-        <v>122</v>
       </c>
       <c r="J394" t="s">
         <v>712</v>
@@ -24852,7 +24852,7 @@
         <v>47</v>
       </c>
       <c r="P394" t="s">
-        <v>122</v>
+        <v>776</v>
       </c>
       <c r="Q394" t="s">
         <v>46</v>
@@ -26570,7 +26570,7 @@
         <v>874</v>
       </c>
       <c r="J425" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K425" t="s">
         <v>74</v>
@@ -26682,7 +26682,7 @@
         <v>880</v>
       </c>
       <c r="J427" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K427" t="s">
         <v>156</v>
@@ -26794,7 +26794,7 @@
         <v>887</v>
       </c>
       <c r="J429" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K429" t="s">
         <v>156</v>
@@ -26850,7 +26850,7 @@
         <v>891</v>
       </c>
       <c r="J430" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K430" t="s">
         <v>558</v>
@@ -26906,7 +26906,7 @@
         <v>895</v>
       </c>
       <c r="J431" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K431" t="s">
         <v>156</v>
@@ -26962,7 +26962,7 @@
         <v>899</v>
       </c>
       <c r="J432" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="K432" t="s">
         <v>69</v>
@@ -27351,7 +27351,7 @@
         <v>928</v>
       </c>
       <c r="I439" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="J439" t="s">
         <v>367</v>
@@ -27372,7 +27372,7 @@
         <v>47</v>
       </c>
       <c r="P439" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="Q439" t="s">
         <v>46</v>
@@ -27581,7 +27581,7 @@
         <v>943</v>
       </c>
       <c r="K443" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="L443" t="s">
         <v>944</v>
@@ -28194,7 +28194,7 @@
         <v>988</v>
       </c>
       <c r="J454" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="K454" t="s">
         <v>58</v>
@@ -28468,7 +28468,7 @@
         <v>40</v>
       </c>
       <c r="H459" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="I459" t="s">
         <v>1006</v>
@@ -28698,7 +28698,7 @@
         <v>1014</v>
       </c>
       <c r="J463" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K463" t="s">
         <v>558</v>
@@ -34693,7 +34693,7 @@
         <v>109</v>
       </c>
       <c r="K570" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="L570" t="s">
         <v>1147</v>

--- a/xlsx/dre/DRE_07_2026.xlsx
+++ b/xlsx/dre/DRE_07_2026.xlsx
@@ -576,6 +576,21 @@
     <t>Digisac MP 2026</t>
   </si>
   <si>
+    <t>28/1</t>
+  </si>
+  <si>
+    <t>IRRF- darf</t>
+  </si>
+  <si>
+    <t>R$  3.084,28</t>
+  </si>
+  <si>
+    <t>20/08/26</t>
+  </si>
+  <si>
+    <t>IRRF</t>
+  </si>
+  <si>
     <t>27/1</t>
   </si>
   <si>
@@ -585,9 +600,6 @@
     <t>R$  1.795,63</t>
   </si>
   <si>
-    <t>20/08/26</t>
-  </si>
-  <si>
     <t>INSS</t>
   </si>
   <si>
@@ -598,18 +610,6 @@
   </si>
   <si>
     <t>R$  75,90</t>
-  </si>
-  <si>
-    <t>28/1</t>
-  </si>
-  <si>
-    <t>IRRF- darf</t>
-  </si>
-  <si>
-    <t>R$  3.084,28</t>
-  </si>
-  <si>
-    <t>IRRF</t>
   </si>
   <si>
     <t>4 CUSTOS E DESPESAS</t>
@@ -1411,21 +1411,21 @@
     <t>Retirada Lucro/1</t>
   </si>
   <si>
+    <t>Luiz Otavio de Podesta</t>
+  </si>
+  <si>
+    <t>R$  20.000,00</t>
+  </si>
+  <si>
+    <t>03/08/26</t>
+  </si>
+  <si>
     <t>LUCAS LEITE MORITA</t>
   </si>
   <si>
     <t>R$  40.000,00</t>
   </si>
   <si>
-    <t>03/08/26</t>
-  </si>
-  <si>
-    <t>R$  20.000,00</t>
-  </si>
-  <si>
-    <t>Luiz Otavio de Podesta</t>
-  </si>
-  <si>
     <t>4.03.01.02 Remuneração variável de equipe</t>
   </si>
   <si>
@@ -1960,12 +1960,12 @@
     <t>DSR julho26/1</t>
   </si>
   <si>
+    <t>R$  1.165,13</t>
+  </si>
+  <si>
     <t>R$  953,63</t>
   </si>
   <si>
-    <t>R$  1.165,13</t>
-  </si>
-  <si>
     <t>4.03.02 COMISSÕES E BÔNUS DE TERCEIROS</t>
   </si>
   <si>
@@ -2014,60 +2014,60 @@
     <t>R$  20,84</t>
   </si>
   <si>
+    <t>16003/0</t>
+  </si>
+  <si>
+    <t>R$  66,90</t>
+  </si>
+  <si>
+    <t>12/07/26</t>
+  </si>
+  <si>
+    <t>AnaCAL0016003</t>
+  </si>
+  <si>
+    <t>49301/0</t>
+  </si>
+  <si>
+    <t>R$  32,82</t>
+  </si>
+  <si>
+    <t>49301GuilhermeBN</t>
+  </si>
+  <si>
+    <t>13301/0</t>
+  </si>
+  <si>
+    <t>R$  11,05</t>
+  </si>
+  <si>
+    <t>FlaviaCM0013301</t>
+  </si>
+  <si>
+    <t>76901/0</t>
+  </si>
+  <si>
+    <t>R$  41,15</t>
+  </si>
+  <si>
+    <t>76901JoaoMCC</t>
+  </si>
+  <si>
+    <t>42001UB/0</t>
+  </si>
+  <si>
+    <t>R$  46,74</t>
+  </si>
+  <si>
+    <t>42001LaysSB</t>
+  </si>
+  <si>
     <t>ADM EF/0</t>
   </si>
   <si>
     <t>R$  77,99</t>
   </si>
   <si>
-    <t>12/07/26</t>
-  </si>
-  <si>
-    <t>13301/0</t>
-  </si>
-  <si>
-    <t>R$  11,05</t>
-  </si>
-  <si>
-    <t>FlaviaCM0013301</t>
-  </si>
-  <si>
-    <t>16003/0</t>
-  </si>
-  <si>
-    <t>R$  66,90</t>
-  </si>
-  <si>
-    <t>AnaCAL0016003</t>
-  </si>
-  <si>
-    <t>76901/0</t>
-  </si>
-  <si>
-    <t>R$  41,15</t>
-  </si>
-  <si>
-    <t>76901JoaoMCC</t>
-  </si>
-  <si>
-    <t>49301/0</t>
-  </si>
-  <si>
-    <t>R$  32,82</t>
-  </si>
-  <si>
-    <t>49301GuilhermeBN</t>
-  </si>
-  <si>
-    <t>42001UB/0</t>
-  </si>
-  <si>
-    <t>R$  46,74</t>
-  </si>
-  <si>
-    <t>42001LaysSB</t>
-  </si>
-  <si>
     <t>4.03.03.02 Agregados e outros gastos de montagens</t>
   </si>
   <si>
@@ -2080,15 +2080,15 @@
     <t>4.03.03.02.05.02 Assistência técnica medição</t>
   </si>
   <si>
+    <t>PFP</t>
+  </si>
+  <si>
     <t>L E A Medicoes Tecnicas LTDA</t>
   </si>
   <si>
     <t>R$  180,00</t>
   </si>
   <si>
-    <t>PFP</t>
-  </si>
-  <si>
     <t>4.03.03.08 Brindes (CV)</t>
   </si>
   <si>
@@ -2152,6 +2152,27 @@
     <t>12/7</t>
   </si>
   <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>R$  14,99</t>
+  </si>
+  <si>
+    <t>Google 2026</t>
+  </si>
+  <si>
+    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
+  </si>
+  <si>
+    <t>R$  4.642,50</t>
+  </si>
+  <si>
+    <t>18/02/26</t>
+  </si>
+  <si>
+    <t>Webgiga 2026</t>
+  </si>
+  <si>
     <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
   </si>
   <si>
@@ -2164,18 +2185,6 @@
     <t>MHM - Honorários 2026</t>
   </si>
   <si>
-    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
-  </si>
-  <si>
-    <t>R$  4.642,50</t>
-  </si>
-  <si>
-    <t>18/02/26</t>
-  </si>
-  <si>
-    <t>Webgiga 2026</t>
-  </si>
-  <si>
     <t>1/5</t>
   </si>
   <si>
@@ -2188,15 +2197,6 @@
     <t>Facebook 2026</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>R$  14,99</t>
-  </si>
-  <si>
-    <t>Google 2026</t>
-  </si>
-  <si>
     <t>4.03.03.09.06 Marketing - outros gastos (CV)</t>
   </si>
   <si>
@@ -2476,18 +2476,18 @@
     <t>4.04.01.05.02.01 Vale transporte</t>
   </si>
   <si>
+    <t>VT jul26/1</t>
+  </si>
+  <si>
+    <t>R$  458,32</t>
+  </si>
+  <si>
     <t>VT julho26/1</t>
   </si>
   <si>
     <t>R$  325,97</t>
   </si>
   <si>
-    <t>VT jul26/1</t>
-  </si>
-  <si>
-    <t>R$  458,32</t>
-  </si>
-  <si>
     <t>4.04.02 GASTOS GERAIS ADMINISTRATIVOS</t>
   </si>
   <si>
@@ -2645,50 +2645,6 @@
   </si>
   <si>
     <t>R$  5,95</t>
-  </si>
-  <si>
-    <t>713/1</t>
-  </si>
-  <si>
-    <t>R$  144,10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reembolso materiais descartáveis
-</t>
-  </si>
-  <si>
-    <t>716/1</t>
-  </si>
-  <si>
-    <t>Marinete</t>
-  </si>
-  <si>
-    <t>R$  108,03</t>
-  </si>
-  <si>
-    <t>Doces festa junina e bandeirinha</t>
-  </si>
-  <si>
-    <t>710/1</t>
-  </si>
-  <si>
-    <t>R$  476,48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reembolso espetinho e bebida festa junina
-</t>
-  </si>
-  <si>
-    <t>717/1</t>
-  </si>
-  <si>
-    <t>Pão de Açúcar</t>
-  </si>
-  <si>
-    <t>R$  62,45</t>
-  </si>
-  <si>
-    <t>materiais consumo loja</t>
   </si>
   <si>
     <t>724/1</t>
@@ -2710,6 +2666,38 @@
 </t>
   </si>
   <si>
+    <t>713/1</t>
+  </si>
+  <si>
+    <t>R$  144,10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reembolso materiais descartáveis
+</t>
+  </si>
+  <si>
+    <t>716/1</t>
+  </si>
+  <si>
+    <t>Marinete</t>
+  </si>
+  <si>
+    <t>R$  108,03</t>
+  </si>
+  <si>
+    <t>Doces festa junina e bandeirinha</t>
+  </si>
+  <si>
+    <t>710/1</t>
+  </si>
+  <si>
+    <t>R$  476,48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reembolso espetinho e bebida festa junina
+</t>
+  </si>
+  <si>
     <t>715/1</t>
   </si>
   <si>
@@ -2722,6 +2710,18 @@
     <t>Insumos para cuscuz festa juninas</t>
   </si>
   <si>
+    <t>717/1</t>
+  </si>
+  <si>
+    <t>Pão de Açúcar</t>
+  </si>
+  <si>
+    <t>R$  62,45</t>
+  </si>
+  <si>
+    <t>materiais consumo loja</t>
+  </si>
+  <si>
     <t>707/1</t>
   </si>
   <si>
@@ -2839,6 +2839,21 @@
     <t>21/05/26</t>
   </si>
   <si>
+    <t>64/2</t>
+  </si>
+  <si>
+    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  146,67</t>
+  </si>
+  <si>
+    <t>24/06/26</t>
+  </si>
+  <si>
+    <t>ISO Implantação -Saude ocupacional</t>
+  </si>
+  <si>
     <t>3/6</t>
   </si>
   <si>
@@ -2849,21 +2864,6 @@
   </si>
   <si>
     <t>Promob 2026/2</t>
-  </si>
-  <si>
-    <t>64/2</t>
-  </si>
-  <si>
-    <t>ISO IMPLANTACAO EM SAUDE OCUPACIONAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  146,67</t>
-  </si>
-  <si>
-    <t>24/06/26</t>
-  </si>
-  <si>
-    <t>ISO Implantação -Saude ocupacional</t>
   </si>
   <si>
     <t>63/2</t>
@@ -6242,13 +6242,13 @@
         <v>194</v>
       </c>
       <c r="J62" t="s">
-        <v>69</v>
+        <v>190</v>
       </c>
       <c r="K62" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="L62" t="s">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="M62" t="s">
         <v>180</v>
@@ -6283,7 +6283,7 @@
         <v>34</v>
       </c>
       <c r="E63" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F63" t="s">
         <v>55</v>
@@ -6292,19 +6292,19 @@
         <v>40</v>
       </c>
       <c r="H63" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I63" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J63" t="s">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="K63" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="L63" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="M63" t="s">
         <v>180</v>
@@ -6316,7 +6316,7 @@
         <v>47</v>
       </c>
       <c r="P63" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q63" t="s">
         <v>46</v>
@@ -12455,7 +12455,7 @@
         <v>324</v>
       </c>
       <c r="I173" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="J173" t="s">
         <v>465</v>
@@ -12476,7 +12476,7 @@
         <v>47</v>
       </c>
       <c r="P173" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="Q173" t="s">
         <v>46</v>
@@ -12508,10 +12508,10 @@
         <v>40</v>
       </c>
       <c r="H174" t="s">
+        <v>466</v>
+      </c>
+      <c r="I174" t="s">
         <v>467</v>
-      </c>
-      <c r="I174" t="s">
-        <v>466</v>
       </c>
       <c r="J174" t="s">
         <v>465</v>
@@ -12532,7 +12532,7 @@
         <v>47</v>
       </c>
       <c r="P174" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Q174" t="s">
         <v>46</v>
@@ -21076,7 +21076,7 @@
         <v>40</v>
       </c>
       <c r="H327" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
       <c r="I327" t="s">
         <v>646</v>
@@ -21132,7 +21132,7 @@
         <v>40</v>
       </c>
       <c r="H328" t="s">
-        <v>473</v>
+        <v>535</v>
       </c>
       <c r="I328" t="s">
         <v>647</v>
@@ -21657,7 +21657,7 @@
         <v>46</v>
       </c>
       <c r="O337" t="s">
-        <v>47</v>
+        <v>667</v>
       </c>
       <c r="P337" t="s">
         <v>665</v>
@@ -21683,7 +21683,7 @@
         <v>34</v>
       </c>
       <c r="E338" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F338" t="s">
         <v>39</v>
@@ -21695,7 +21695,7 @@
         <v>660</v>
       </c>
       <c r="I338" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="J338" t="s">
         <v>335</v>
@@ -21713,10 +21713,10 @@
         <v>46</v>
       </c>
       <c r="O338" t="s">
+        <v>670</v>
+      </c>
+      <c r="P338" t="s">
         <v>669</v>
-      </c>
-      <c r="P338" t="s">
-        <v>668</v>
       </c>
       <c r="Q338" t="s">
         <v>46</v>
@@ -21739,7 +21739,7 @@
         <v>34</v>
       </c>
       <c r="E339" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F339" t="s">
         <v>39</v>
@@ -21751,7 +21751,7 @@
         <v>660</v>
       </c>
       <c r="I339" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="J339" t="s">
         <v>335</v>
@@ -21769,10 +21769,10 @@
         <v>46</v>
       </c>
       <c r="O339" t="s">
+        <v>673</v>
+      </c>
+      <c r="P339" t="s">
         <v>672</v>
-      </c>
-      <c r="P339" t="s">
-        <v>671</v>
       </c>
       <c r="Q339" t="s">
         <v>46</v>
@@ -21795,7 +21795,7 @@
         <v>34</v>
       </c>
       <c r="E340" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F340" t="s">
         <v>39</v>
@@ -21807,7 +21807,7 @@
         <v>660</v>
       </c>
       <c r="I340" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="J340" t="s">
         <v>335</v>
@@ -21825,10 +21825,10 @@
         <v>46</v>
       </c>
       <c r="O340" t="s">
+        <v>676</v>
+      </c>
+      <c r="P340" t="s">
         <v>675</v>
-      </c>
-      <c r="P340" t="s">
-        <v>674</v>
       </c>
       <c r="Q340" t="s">
         <v>46</v>
@@ -21851,7 +21851,7 @@
         <v>34</v>
       </c>
       <c r="E341" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F341" t="s">
         <v>39</v>
@@ -21863,7 +21863,7 @@
         <v>660</v>
       </c>
       <c r="I341" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J341" t="s">
         <v>335</v>
@@ -21881,10 +21881,10 @@
         <v>46</v>
       </c>
       <c r="O341" t="s">
+        <v>679</v>
+      </c>
+      <c r="P341" t="s">
         <v>678</v>
-      </c>
-      <c r="P341" t="s">
-        <v>677</v>
       </c>
       <c r="Q341" t="s">
         <v>46</v>
@@ -21907,7 +21907,7 @@
         <v>34</v>
       </c>
       <c r="E342" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F342" t="s">
         <v>39</v>
@@ -21919,7 +21919,7 @@
         <v>660</v>
       </c>
       <c r="I342" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J342" t="s">
         <v>335</v>
@@ -21937,10 +21937,10 @@
         <v>46</v>
       </c>
       <c r="O342" t="s">
+        <v>47</v>
+      </c>
+      <c r="P342" t="s">
         <v>681</v>
-      </c>
-      <c r="P342" t="s">
-        <v>680</v>
       </c>
       <c r="Q342" t="s">
         <v>46</v>
@@ -22075,25 +22075,25 @@
         <v>33</v>
       </c>
       <c r="E345" t="s">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="F345" t="s">
-        <v>39</v>
+        <v>686</v>
       </c>
       <c r="G345" t="s">
         <v>40</v>
       </c>
       <c r="H345" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I345" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J345" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K345" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L345" t="s">
         <v>34</v>
@@ -22105,13 +22105,13 @@
         <v>46</v>
       </c>
       <c r="O345" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="P345" t="s">
-        <v>687</v>
+        <v>34</v>
       </c>
       <c r="Q345" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R345" t="s">
         <v>34</v>
@@ -22131,25 +22131,25 @@
         <v>34</v>
       </c>
       <c r="E346" t="s">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="F346" t="s">
+        <v>207</v>
+      </c>
+      <c r="G346" t="s">
+        <v>40</v>
+      </c>
+      <c r="H346" t="s">
+        <v>687</v>
+      </c>
+      <c r="I346" t="s">
         <v>688</v>
       </c>
-      <c r="G346" t="s">
-        <v>40</v>
-      </c>
-      <c r="H346" t="s">
-        <v>686</v>
-      </c>
-      <c r="I346" t="s">
-        <v>687</v>
-      </c>
       <c r="J346" t="s">
-        <v>59</v>
+        <v>302</v>
       </c>
       <c r="K346" t="s">
-        <v>59</v>
+        <v>247</v>
       </c>
       <c r="L346" t="s">
         <v>34</v>
@@ -22161,13 +22161,13 @@
         <v>46</v>
       </c>
       <c r="O346" t="s">
-        <v>34</v>
+        <v>303</v>
       </c>
       <c r="P346" t="s">
-        <v>34</v>
+        <v>688</v>
       </c>
       <c r="Q346" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R346" t="s">
         <v>34</v>
@@ -22187,7 +22187,7 @@
         <v>34</v>
       </c>
       <c r="E347" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="F347" t="s">
         <v>207</v>
@@ -22196,16 +22196,16 @@
         <v>40</v>
       </c>
       <c r="H347" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I347" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J347" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K347" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L347" t="s">
         <v>34</v>
@@ -22217,10 +22217,10 @@
         <v>46</v>
       </c>
       <c r="O347" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="P347" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="Q347" t="s">
         <v>46</v>
@@ -22243,25 +22243,25 @@
         <v>34</v>
       </c>
       <c r="E348" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="F348" t="s">
+        <v>207</v>
+      </c>
+      <c r="G348" t="s">
+        <v>40</v>
+      </c>
+      <c r="H348" t="s">
+        <v>687</v>
+      </c>
+      <c r="I348" t="s">
         <v>688</v>
       </c>
-      <c r="G348" t="s">
-        <v>40</v>
-      </c>
-      <c r="H348" t="s">
-        <v>686</v>
-      </c>
-      <c r="I348" t="s">
-        <v>687</v>
-      </c>
       <c r="J348" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K348" t="s">
-        <v>247</v>
+        <v>58</v>
       </c>
       <c r="L348" t="s">
         <v>34</v>
@@ -22273,13 +22273,13 @@
         <v>46</v>
       </c>
       <c r="O348" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="P348" t="s">
-        <v>34</v>
+        <v>688</v>
       </c>
       <c r="Q348" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R348" t="s">
         <v>34</v>
@@ -22299,25 +22299,25 @@
         <v>34</v>
       </c>
       <c r="E349" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="F349" t="s">
-        <v>207</v>
+        <v>39</v>
       </c>
       <c r="G349" t="s">
         <v>40</v>
       </c>
       <c r="H349" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I349" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J349" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="K349" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="L349" t="s">
         <v>34</v>
@@ -22329,10 +22329,10 @@
         <v>46</v>
       </c>
       <c r="O349" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="P349" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="Q349" t="s">
         <v>46</v>
@@ -22364,10 +22364,10 @@
         <v>40</v>
       </c>
       <c r="H350" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I350" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J350" t="s">
         <v>109</v>
@@ -22388,7 +22388,7 @@
         <v>489</v>
       </c>
       <c r="P350" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="Q350" t="s">
         <v>46</v>
@@ -22411,7 +22411,7 @@
         <v>34</v>
       </c>
       <c r="E351" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="F351" t="s">
         <v>207</v>
@@ -22420,16 +22420,16 @@
         <v>40</v>
       </c>
       <c r="H351" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I351" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J351" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="K351" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="L351" t="s">
         <v>34</v>
@@ -22441,10 +22441,10 @@
         <v>46</v>
       </c>
       <c r="O351" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="P351" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="Q351" t="s">
         <v>46</v>
@@ -22467,25 +22467,25 @@
         <v>34</v>
       </c>
       <c r="E352" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="F352" t="s">
+        <v>207</v>
+      </c>
+      <c r="G352" t="s">
+        <v>40</v>
+      </c>
+      <c r="H352" t="s">
+        <v>687</v>
+      </c>
+      <c r="I352" t="s">
         <v>688</v>
       </c>
-      <c r="G352" t="s">
-        <v>40</v>
-      </c>
-      <c r="H352" t="s">
-        <v>686</v>
-      </c>
-      <c r="I352" t="s">
-        <v>687</v>
-      </c>
       <c r="J352" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="K352" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="L352" t="s">
         <v>34</v>
@@ -22497,13 +22497,13 @@
         <v>46</v>
       </c>
       <c r="O352" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="P352" t="s">
-        <v>34</v>
+        <v>688</v>
       </c>
       <c r="Q352" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R352" t="s">
         <v>34</v>
@@ -22523,19 +22523,19 @@
         <v>34</v>
       </c>
       <c r="E353" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F353" t="s">
+        <v>207</v>
+      </c>
+      <c r="G353" t="s">
+        <v>40</v>
+      </c>
+      <c r="H353" t="s">
+        <v>687</v>
+      </c>
+      <c r="I353" t="s">
         <v>688</v>
-      </c>
-      <c r="G353" t="s">
-        <v>40</v>
-      </c>
-      <c r="H353" t="s">
-        <v>686</v>
-      </c>
-      <c r="I353" t="s">
-        <v>687</v>
       </c>
       <c r="J353" t="s">
         <v>59</v>
@@ -22553,13 +22553,13 @@
         <v>46</v>
       </c>
       <c r="O353" t="s">
-        <v>34</v>
+        <v>281</v>
       </c>
       <c r="P353" t="s">
-        <v>34</v>
+        <v>688</v>
       </c>
       <c r="Q353" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R353" t="s">
         <v>34</v>
@@ -22579,25 +22579,25 @@
         <v>34</v>
       </c>
       <c r="E354" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="F354" t="s">
+        <v>207</v>
+      </c>
+      <c r="G354" t="s">
+        <v>40</v>
+      </c>
+      <c r="H354" t="s">
+        <v>687</v>
+      </c>
+      <c r="I354" t="s">
         <v>688</v>
       </c>
-      <c r="G354" t="s">
-        <v>40</v>
-      </c>
-      <c r="H354" t="s">
-        <v>686</v>
-      </c>
-      <c r="I354" t="s">
-        <v>687</v>
-      </c>
       <c r="J354" t="s">
-        <v>359</v>
+        <v>59</v>
       </c>
       <c r="K354" t="s">
-        <v>359</v>
+        <v>59</v>
       </c>
       <c r="L354" t="s">
         <v>34</v>
@@ -22609,13 +22609,13 @@
         <v>46</v>
       </c>
       <c r="O354" t="s">
-        <v>34</v>
+        <v>233</v>
       </c>
       <c r="P354" t="s">
-        <v>34</v>
+        <v>688</v>
       </c>
       <c r="Q354" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R354" t="s">
         <v>34</v>
@@ -22635,7 +22635,7 @@
         <v>34</v>
       </c>
       <c r="E355" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="F355" t="s">
         <v>207</v>
@@ -22644,16 +22644,16 @@
         <v>40</v>
       </c>
       <c r="H355" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I355" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J355" t="s">
-        <v>302</v>
+        <v>452</v>
       </c>
       <c r="K355" t="s">
-        <v>247</v>
+        <v>452</v>
       </c>
       <c r="L355" t="s">
         <v>34</v>
@@ -22665,10 +22665,10 @@
         <v>46</v>
       </c>
       <c r="O355" t="s">
-        <v>303</v>
+        <v>88</v>
       </c>
       <c r="P355" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="Q355" t="s">
         <v>46</v>
@@ -22691,25 +22691,25 @@
         <v>34</v>
       </c>
       <c r="E356" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F356" t="s">
-        <v>207</v>
+        <v>686</v>
       </c>
       <c r="G356" t="s">
         <v>40</v>
       </c>
       <c r="H356" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I356" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J356" t="s">
-        <v>59</v>
+        <v>359</v>
       </c>
       <c r="K356" t="s">
-        <v>59</v>
+        <v>359</v>
       </c>
       <c r="L356" t="s">
         <v>34</v>
@@ -22721,13 +22721,13 @@
         <v>46</v>
       </c>
       <c r="O356" t="s">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="P356" t="s">
-        <v>687</v>
+        <v>34</v>
       </c>
       <c r="Q356" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R356" t="s">
         <v>34</v>
@@ -22756,10 +22756,10 @@
         <v>40</v>
       </c>
       <c r="H357" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I357" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J357" t="s">
         <v>74</v>
@@ -22780,7 +22780,7 @@
         <v>106</v>
       </c>
       <c r="P357" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="Q357" t="s">
         <v>46</v>
@@ -22803,25 +22803,25 @@
         <v>34</v>
       </c>
       <c r="E358" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="F358" t="s">
-        <v>207</v>
+        <v>686</v>
       </c>
       <c r="G358" t="s">
         <v>40</v>
       </c>
       <c r="H358" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I358" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J358" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="K358" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="L358" t="s">
         <v>34</v>
@@ -22833,13 +22833,13 @@
         <v>46</v>
       </c>
       <c r="O358" t="s">
-        <v>288</v>
+        <v>34</v>
       </c>
       <c r="P358" t="s">
-        <v>687</v>
+        <v>34</v>
       </c>
       <c r="Q358" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R358" t="s">
         <v>34</v>
@@ -22859,25 +22859,25 @@
         <v>34</v>
       </c>
       <c r="E359" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="F359" t="s">
+        <v>686</v>
+      </c>
+      <c r="G359" t="s">
+        <v>40</v>
+      </c>
+      <c r="H359" t="s">
+        <v>687</v>
+      </c>
+      <c r="I359" t="s">
         <v>688</v>
       </c>
-      <c r="G359" t="s">
-        <v>40</v>
-      </c>
-      <c r="H359" t="s">
-        <v>686</v>
-      </c>
-      <c r="I359" t="s">
-        <v>687</v>
-      </c>
       <c r="J359" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="K359" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="L359" t="s">
         <v>34</v>
@@ -22915,19 +22915,19 @@
         <v>34</v>
       </c>
       <c r="E360" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="F360" t="s">
+        <v>686</v>
+      </c>
+      <c r="G360" t="s">
+        <v>40</v>
+      </c>
+      <c r="H360" t="s">
+        <v>687</v>
+      </c>
+      <c r="I360" t="s">
         <v>688</v>
-      </c>
-      <c r="G360" t="s">
-        <v>40</v>
-      </c>
-      <c r="H360" t="s">
-        <v>686</v>
-      </c>
-      <c r="I360" t="s">
-        <v>687</v>
       </c>
       <c r="J360" t="s">
         <v>59</v>
@@ -22971,25 +22971,25 @@
         <v>34</v>
       </c>
       <c r="E361" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F361" t="s">
-        <v>207</v>
+        <v>686</v>
       </c>
       <c r="G361" t="s">
         <v>40</v>
       </c>
       <c r="H361" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I361" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J361" t="s">
         <v>59</v>
       </c>
       <c r="K361" t="s">
-        <v>59</v>
+        <v>247</v>
       </c>
       <c r="L361" t="s">
         <v>34</v>
@@ -23001,13 +23001,13 @@
         <v>46</v>
       </c>
       <c r="O361" t="s">
-        <v>281</v>
+        <v>34</v>
       </c>
       <c r="P361" t="s">
-        <v>687</v>
+        <v>34</v>
       </c>
       <c r="Q361" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R361" t="s">
         <v>34</v>
@@ -23027,25 +23027,25 @@
         <v>34</v>
       </c>
       <c r="E362" t="s">
-        <v>291</v>
+        <v>234</v>
       </c>
       <c r="F362" t="s">
-        <v>207</v>
+        <v>686</v>
       </c>
       <c r="G362" t="s">
         <v>40</v>
       </c>
       <c r="H362" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I362" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J362" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="K362" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="L362" t="s">
         <v>34</v>
@@ -23057,13 +23057,13 @@
         <v>46</v>
       </c>
       <c r="O362" t="s">
-        <v>233</v>
+        <v>34</v>
       </c>
       <c r="P362" t="s">
-        <v>687</v>
+        <v>34</v>
       </c>
       <c r="Q362" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R362" t="s">
         <v>34</v>
@@ -23083,25 +23083,25 @@
         <v>34</v>
       </c>
       <c r="E363" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F363" t="s">
-        <v>207</v>
+        <v>686</v>
       </c>
       <c r="G363" t="s">
         <v>40</v>
       </c>
       <c r="H363" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I363" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J363" t="s">
-        <v>452</v>
+        <v>59</v>
       </c>
       <c r="K363" t="s">
-        <v>452</v>
+        <v>59</v>
       </c>
       <c r="L363" t="s">
         <v>34</v>
@@ -23113,13 +23113,13 @@
         <v>46</v>
       </c>
       <c r="O363" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="P363" t="s">
-        <v>687</v>
+        <v>34</v>
       </c>
       <c r="Q363" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R363" t="s">
         <v>34</v>
@@ -23139,25 +23139,25 @@
         <v>34</v>
       </c>
       <c r="E364" t="s">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="F364" t="s">
+        <v>207</v>
+      </c>
+      <c r="G364" t="s">
+        <v>40</v>
+      </c>
+      <c r="H364" t="s">
+        <v>687</v>
+      </c>
+      <c r="I364" t="s">
         <v>688</v>
       </c>
-      <c r="G364" t="s">
-        <v>40</v>
-      </c>
-      <c r="H364" t="s">
-        <v>686</v>
-      </c>
-      <c r="I364" t="s">
-        <v>687</v>
-      </c>
       <c r="J364" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="K364" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="L364" t="s">
         <v>34</v>
@@ -23169,13 +23169,13 @@
         <v>46</v>
       </c>
       <c r="O364" t="s">
-        <v>34</v>
+        <v>288</v>
       </c>
       <c r="P364" t="s">
-        <v>34</v>
+        <v>688</v>
       </c>
       <c r="Q364" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R364" t="s">
         <v>34</v>
@@ -23198,16 +23198,16 @@
         <v>320</v>
       </c>
       <c r="F365" t="s">
+        <v>686</v>
+      </c>
+      <c r="G365" t="s">
+        <v>40</v>
+      </c>
+      <c r="H365" t="s">
+        <v>687</v>
+      </c>
+      <c r="I365" t="s">
         <v>688</v>
-      </c>
-      <c r="G365" t="s">
-        <v>40</v>
-      </c>
-      <c r="H365" t="s">
-        <v>686</v>
-      </c>
-      <c r="I365" t="s">
-        <v>687</v>
       </c>
       <c r="J365" t="s">
         <v>74</v>
@@ -23546,13 +23546,13 @@
         <v>711</v>
       </c>
       <c r="J371" t="s">
+        <v>367</v>
+      </c>
+      <c r="K371" t="s">
+        <v>363</v>
+      </c>
+      <c r="L371" t="s">
         <v>712</v>
-      </c>
-      <c r="K371" t="s">
-        <v>318</v>
-      </c>
-      <c r="L371" t="s">
-        <v>713</v>
       </c>
       <c r="M371" t="s">
         <v>707</v>
@@ -23596,19 +23596,19 @@
         <v>40</v>
       </c>
       <c r="H372" t="s">
+        <v>713</v>
+      </c>
+      <c r="I372" t="s">
         <v>714</v>
       </c>
-      <c r="I372" t="s">
+      <c r="J372" t="s">
         <v>715</v>
-      </c>
-      <c r="J372" t="s">
-        <v>716</v>
       </c>
       <c r="K372" t="s">
         <v>117</v>
       </c>
       <c r="L372" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="M372" t="s">
         <v>707</v>
@@ -23620,7 +23620,7 @@
         <v>47</v>
       </c>
       <c r="P372" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Q372" t="s">
         <v>46</v>
@@ -23643,7 +23643,7 @@
         <v>34</v>
       </c>
       <c r="E373" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="F373" t="s">
         <v>207</v>
@@ -23652,19 +23652,19 @@
         <v>40</v>
       </c>
       <c r="H373" t="s">
+        <v>717</v>
+      </c>
+      <c r="I373" t="s">
+        <v>718</v>
+      </c>
+      <c r="J373" t="s">
         <v>719</v>
       </c>
-      <c r="I373" t="s">
+      <c r="K373" t="s">
+        <v>318</v>
+      </c>
+      <c r="L373" t="s">
         <v>720</v>
-      </c>
-      <c r="J373" t="s">
-        <v>216</v>
-      </c>
-      <c r="K373" t="s">
-        <v>175</v>
-      </c>
-      <c r="L373" t="s">
-        <v>721</v>
       </c>
       <c r="M373" t="s">
         <v>707</v>
@@ -23676,7 +23676,7 @@
         <v>47</v>
       </c>
       <c r="P373" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="Q373" t="s">
         <v>46</v>
@@ -23699,7 +23699,7 @@
         <v>34</v>
       </c>
       <c r="E374" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="F374" t="s">
         <v>207</v>
@@ -23714,10 +23714,10 @@
         <v>723</v>
       </c>
       <c r="J374" t="s">
-        <v>367</v>
+        <v>216</v>
       </c>
       <c r="K374" t="s">
-        <v>363</v>
+        <v>175</v>
       </c>
       <c r="L374" t="s">
         <v>724</v>
@@ -23994,7 +23994,7 @@
         <v>122</v>
       </c>
       <c r="J379" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="K379" t="s">
         <v>363</v>
@@ -24162,7 +24162,7 @@
         <v>745</v>
       </c>
       <c r="J382" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="K382" t="s">
         <v>363</v>
@@ -24218,7 +24218,7 @@
         <v>748</v>
       </c>
       <c r="J383" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="K383" t="s">
         <v>363</v>
@@ -24274,7 +24274,7 @@
         <v>751</v>
       </c>
       <c r="J384" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="K384" t="s">
         <v>363</v>
@@ -24315,7 +24315,7 @@
         <v>34</v>
       </c>
       <c r="E385" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F385" t="s">
         <v>207</v>
@@ -24722,7 +24722,7 @@
         <v>122</v>
       </c>
       <c r="J392" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="K392" t="s">
         <v>363</v>
@@ -24834,7 +24834,7 @@
         <v>776</v>
       </c>
       <c r="J394" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="K394" t="s">
         <v>363</v>
@@ -24890,7 +24890,7 @@
         <v>779</v>
       </c>
       <c r="J395" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="K395" t="s">
         <v>363</v>
@@ -24996,10 +24996,10 @@
         <v>40</v>
       </c>
       <c r="H397" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="I397" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="J397" t="s">
         <v>210</v>
@@ -25020,7 +25020,7 @@
         <v>47</v>
       </c>
       <c r="P397" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="Q397" t="s">
         <v>46</v>
@@ -25108,10 +25108,10 @@
         <v>40</v>
       </c>
       <c r="H399" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="I399" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="J399" t="s">
         <v>210</v>
@@ -25132,7 +25132,7 @@
         <v>47</v>
       </c>
       <c r="P399" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Q399" t="s">
         <v>46</v>
@@ -25382,7 +25382,7 @@
         <v>806</v>
       </c>
       <c r="F404" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="G404" t="s">
         <v>40</v>
@@ -25438,7 +25438,7 @@
         <v>206</v>
       </c>
       <c r="F405" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="G405" t="s">
         <v>40</v>
@@ -25668,7 +25668,7 @@
         <v>40</v>
       </c>
       <c r="H409" t="s">
-        <v>473</v>
+        <v>535</v>
       </c>
       <c r="I409" t="s">
         <v>819</v>
@@ -25724,7 +25724,7 @@
         <v>40</v>
       </c>
       <c r="H410" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
       <c r="I410" t="s">
         <v>821</v>
@@ -25898,7 +25898,7 @@
         <v>830</v>
       </c>
       <c r="J413" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="K413" t="s">
         <v>318</v>
@@ -25948,7 +25948,7 @@
         <v>40</v>
       </c>
       <c r="H414" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="I414" t="s">
         <v>835</v>
@@ -26178,7 +26178,7 @@
         <v>848</v>
       </c>
       <c r="J418" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="K418" t="s">
         <v>363</v>
@@ -26346,7 +26346,7 @@
         <v>860</v>
       </c>
       <c r="J421" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="K421" t="s">
         <v>861</v>
@@ -26458,7 +26458,7 @@
         <v>867</v>
       </c>
       <c r="J423" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="K423" t="s">
         <v>318</v>
@@ -26620,19 +26620,19 @@
         <v>40</v>
       </c>
       <c r="H426" t="s">
-        <v>473</v>
+        <v>876</v>
       </c>
       <c r="I426" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="J426" t="s">
-        <v>101</v>
+        <v>335</v>
       </c>
       <c r="K426" t="s">
-        <v>175</v>
+        <v>558</v>
       </c>
       <c r="L426" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="M426" t="s">
         <v>871</v>
@@ -26644,7 +26644,7 @@
         <v>47</v>
       </c>
       <c r="P426" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="Q426" t="s">
         <v>46</v>
@@ -26667,7 +26667,7 @@
         <v>34</v>
       </c>
       <c r="E427" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="F427" t="s">
         <v>39</v>
@@ -26676,16 +26676,16 @@
         <v>40</v>
       </c>
       <c r="H427" t="s">
-        <v>879</v>
+        <v>473</v>
       </c>
       <c r="I427" t="s">
         <v>880</v>
       </c>
       <c r="J427" t="s">
-        <v>335</v>
+        <v>101</v>
       </c>
       <c r="K427" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="L427" t="s">
         <v>881</v>
@@ -26732,19 +26732,19 @@
         <v>40</v>
       </c>
       <c r="H428" t="s">
-        <v>324</v>
+        <v>883</v>
       </c>
       <c r="I428" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="J428" t="s">
-        <v>58</v>
+        <v>335</v>
       </c>
       <c r="K428" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="L428" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="M428" t="s">
         <v>871</v>
@@ -26756,7 +26756,7 @@
         <v>47</v>
       </c>
       <c r="P428" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="Q428" t="s">
         <v>46</v>
@@ -26779,7 +26779,7 @@
         <v>34</v>
       </c>
       <c r="E429" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="F429" t="s">
         <v>39</v>
@@ -26788,16 +26788,16 @@
         <v>40</v>
       </c>
       <c r="H429" t="s">
-        <v>886</v>
+        <v>324</v>
       </c>
       <c r="I429" t="s">
         <v>887</v>
       </c>
       <c r="J429" t="s">
-        <v>335</v>
+        <v>58</v>
       </c>
       <c r="K429" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="L429" t="s">
         <v>888</v>
@@ -26853,7 +26853,7 @@
         <v>335</v>
       </c>
       <c r="K430" t="s">
-        <v>558</v>
+        <v>156</v>
       </c>
       <c r="L430" t="s">
         <v>892</v>
@@ -27130,7 +27130,7 @@
         <v>911</v>
       </c>
       <c r="J435" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="K435" t="s">
         <v>363</v>
@@ -27516,19 +27516,19 @@
         <v>40</v>
       </c>
       <c r="H442" t="s">
-        <v>922</v>
+        <v>937</v>
       </c>
       <c r="I442" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="J442" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="K442" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="L442" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="M442" t="s">
         <v>927</v>
@@ -27540,7 +27540,7 @@
         <v>47</v>
       </c>
       <c r="P442" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="Q442" t="s">
         <v>46</v>
@@ -27563,7 +27563,7 @@
         <v>34</v>
       </c>
       <c r="E443" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F443" t="s">
         <v>207</v>
@@ -27572,7 +27572,7 @@
         <v>40</v>
       </c>
       <c r="H443" t="s">
-        <v>941</v>
+        <v>922</v>
       </c>
       <c r="I443" t="s">
         <v>942</v>
@@ -27581,7 +27581,7 @@
         <v>943</v>
       </c>
       <c r="K443" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="L443" t="s">
         <v>944</v>
@@ -27970,7 +27970,7 @@
         <v>970</v>
       </c>
       <c r="J450" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="K450" t="s">
         <v>363</v>
@@ -28250,7 +28250,7 @@
         <v>992</v>
       </c>
       <c r="J455" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="K455" t="s">
         <v>363</v>
@@ -28306,7 +28306,7 @@
         <v>995</v>
       </c>
       <c r="J456" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="K456" t="s">
         <v>117</v>
@@ -28362,7 +28362,7 @@
         <v>1000</v>
       </c>
       <c r="J457" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="K457" t="s">
         <v>363</v>

--- a/xlsx/dre/DRE_07_2026.xlsx
+++ b/xlsx/dre/DRE_07_2026.xlsx
@@ -576,6 +576,30 @@
     <t>Digisac MP 2026</t>
   </si>
   <si>
+    <t>27/1</t>
+  </si>
+  <si>
+    <t>INSS- Previdenciária</t>
+  </si>
+  <si>
+    <t>R$  1.795,63</t>
+  </si>
+  <si>
+    <t>20/08/26</t>
+  </si>
+  <si>
+    <t>INSS</t>
+  </si>
+  <si>
+    <t>24/1</t>
+  </si>
+  <si>
+    <t>BIO-INSECTA DESINSETIZADORA &amp; DESENTUPIDORA LTDA</t>
+  </si>
+  <si>
+    <t>R$  75,90</t>
+  </si>
+  <si>
     <t>28/1</t>
   </si>
   <si>
@@ -585,31 +609,7 @@
     <t>R$  3.084,28</t>
   </si>
   <si>
-    <t>20/08/26</t>
-  </si>
-  <si>
     <t>IRRF</t>
-  </si>
-  <si>
-    <t>27/1</t>
-  </si>
-  <si>
-    <t>INSS- Previdenciária</t>
-  </si>
-  <si>
-    <t>R$  1.795,63</t>
-  </si>
-  <si>
-    <t>INSS</t>
-  </si>
-  <si>
-    <t>24/1</t>
-  </si>
-  <si>
-    <t>BIO-INSECTA DESINSETIZADORA &amp; DESENTUPIDORA LTDA</t>
-  </si>
-  <si>
-    <t>R$  75,90</t>
   </si>
   <si>
     <t>4 CUSTOS E DESPESAS</t>
@@ -997,27 +997,12 @@
 </t>
   </si>
   <si>
-    <t>25/1</t>
-  </si>
-  <si>
-    <t>R$  49,95</t>
-  </si>
-  <si>
-    <t>D4sign</t>
-  </si>
-  <si>
-    <t>Mercado livre/1</t>
+    <t>732/1</t>
   </si>
   <si>
     <t>Mercado livre</t>
   </si>
   <si>
-    <t>R$  22,46</t>
-  </si>
-  <si>
-    <t>732/1</t>
-  </si>
-  <si>
     <t>R$  38,85</t>
   </si>
   <si>
@@ -1039,7 +1024,31 @@
     <t>11/08/26</t>
   </si>
   <si>
-    <t>R$  12,40</t>
+    <t>727/1</t>
+  </si>
+  <si>
+    <t>626/1</t>
+  </si>
+  <si>
+    <t>R$  300,54</t>
+  </si>
+  <si>
+    <t>13/08/26</t>
+  </si>
+  <si>
+    <t>22/07/26</t>
+  </si>
+  <si>
+    <t>69/3</t>
+  </si>
+  <si>
+    <t>Leo Madeiras</t>
+  </si>
+  <si>
+    <t>R$  113,98</t>
+  </si>
+  <si>
+    <t>Leo madeiras</t>
   </si>
   <si>
     <t>731/1</t>
@@ -1057,6 +1066,36 @@
 </t>
   </si>
   <si>
+    <t>R$  12,40</t>
+  </si>
+  <si>
+    <t>711/1</t>
+  </si>
+  <si>
+    <t>R$  198,06</t>
+  </si>
+  <si>
+    <t>28/07/26</t>
+  </si>
+  <si>
+    <t>Estoque</t>
+  </si>
+  <si>
+    <t>25/1</t>
+  </si>
+  <si>
+    <t>R$  49,95</t>
+  </si>
+  <si>
+    <t>D4sign</t>
+  </si>
+  <si>
+    <t>Mercado livre/1</t>
+  </si>
+  <si>
+    <t>R$  22,46</t>
+  </si>
+  <si>
     <t>723/1</t>
   </si>
   <si>
@@ -1066,45 +1105,6 @@
     <t>estoque</t>
   </si>
   <si>
-    <t>727/1</t>
-  </si>
-  <si>
-    <t>626/1</t>
-  </si>
-  <si>
-    <t>R$  300,54</t>
-  </si>
-  <si>
-    <t>13/08/26</t>
-  </si>
-  <si>
-    <t>22/07/26</t>
-  </si>
-  <si>
-    <t>69/3</t>
-  </si>
-  <si>
-    <t>Leo Madeiras</t>
-  </si>
-  <si>
-    <t>R$  113,98</t>
-  </si>
-  <si>
-    <t>Leo madeiras</t>
-  </si>
-  <si>
-    <t>711/1</t>
-  </si>
-  <si>
-    <t>R$  198,06</t>
-  </si>
-  <si>
-    <t>28/07/26</t>
-  </si>
-  <si>
-    <t>Estoque</t>
-  </si>
-  <si>
     <t>67/1</t>
   </si>
   <si>
@@ -1411,21 +1411,21 @@
     <t>Retirada Lucro/1</t>
   </si>
   <si>
+    <t>LUCAS LEITE MORITA</t>
+  </si>
+  <si>
+    <t>R$  40.000,00</t>
+  </si>
+  <si>
+    <t>03/08/26</t>
+  </si>
+  <si>
+    <t>R$  20.000,00</t>
+  </si>
+  <si>
     <t>Luiz Otavio de Podesta</t>
   </si>
   <si>
-    <t>R$  20.000,00</t>
-  </si>
-  <si>
-    <t>03/08/26</t>
-  </si>
-  <si>
-    <t>LUCAS LEITE MORITA</t>
-  </si>
-  <si>
-    <t>R$  40.000,00</t>
-  </si>
-  <si>
     <t>4.03.01.02 Remuneração variável de equipe</t>
   </si>
   <si>
@@ -1771,75 +1771,75 @@
     <t>R$ 11.982,47</t>
   </si>
   <si>
+    <t>R$  941,73</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>R$  491,99</t>
+  </si>
+  <si>
+    <t>R$  411,87</t>
+  </si>
+  <si>
+    <t>R$  1.440,23</t>
+  </si>
+  <si>
+    <t>91201/2</t>
+  </si>
+  <si>
+    <t>Jose Carlos de Carvalho</t>
+  </si>
+  <si>
+    <t>84401/1</t>
+  </si>
+  <si>
+    <t>R$  164,57</t>
+  </si>
+  <si>
+    <t>84401CamilaFS</t>
+  </si>
+  <si>
+    <t>85201/1</t>
+  </si>
+  <si>
+    <t>R$  2.451,16</t>
+  </si>
+  <si>
+    <t>85201BRUNOAL</t>
+  </si>
+  <si>
+    <t>R$  252,95</t>
+  </si>
+  <si>
+    <t>R$  584,82</t>
+  </si>
+  <si>
+    <t>R$  1.698,42</t>
+  </si>
+  <si>
+    <t>R$  622,81</t>
+  </si>
+  <si>
+    <t>R$  471,77</t>
+  </si>
+  <si>
     <t>88101/2</t>
   </si>
   <si>
     <t>R$  620,43</t>
   </si>
   <si>
-    <t>R$  411,87</t>
-  </si>
-  <si>
-    <t>Jose Carlos de Carvalho</t>
-  </si>
-  <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>R$  491,99</t>
-  </si>
-  <si>
-    <t>84401/1</t>
-  </si>
-  <si>
-    <t>R$  164,57</t>
-  </si>
-  <si>
-    <t>84401CamilaFS</t>
-  </si>
-  <si>
-    <t>85201/1</t>
-  </si>
-  <si>
-    <t>R$  2.451,16</t>
-  </si>
-  <si>
-    <t>85201BRUNOAL</t>
-  </si>
-  <si>
-    <t>91201/2</t>
-  </si>
-  <si>
-    <t>R$  252,95</t>
-  </si>
-  <si>
-    <t>R$  584,82</t>
+    <t>90001/2</t>
   </si>
   <si>
     <t>R$  213,83</t>
   </si>
   <si>
-    <t>R$  1.440,23</t>
-  </si>
-  <si>
-    <t>R$  1.698,42</t>
-  </si>
-  <si>
     <t>86102/2</t>
   </si>
   <si>
-    <t>R$  622,81</t>
-  </si>
-  <si>
-    <t>90001/2</t>
-  </si>
-  <si>
-    <t>R$  471,77</t>
-  </si>
-  <si>
-    <t>R$  941,73</t>
-  </si>
-  <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
   </si>
   <si>
@@ -1960,12 +1960,12 @@
     <t>DSR julho26/1</t>
   </si>
   <si>
+    <t>R$  953,63</t>
+  </si>
+  <si>
     <t>R$  1.165,13</t>
   </si>
   <si>
-    <t>R$  953,63</t>
-  </si>
-  <si>
     <t>4.03.02 COMISSÕES E BÔNUS DE TERCEIROS</t>
   </si>
   <si>
@@ -2080,15 +2080,15 @@
     <t>4.03.03.02.05.02 Assistência técnica medição</t>
   </si>
   <si>
+    <t>L E A Medicoes Tecnicas LTDA</t>
+  </si>
+  <si>
+    <t>R$  180,00</t>
+  </si>
+  <si>
     <t>PFP</t>
   </si>
   <si>
-    <t>L E A Medicoes Tecnicas LTDA</t>
-  </si>
-  <si>
-    <t>R$  180,00</t>
-  </si>
-  <si>
     <t>4.03.03.08 Brindes (CV)</t>
   </si>
   <si>
@@ -2152,6 +2152,42 @@
     <t>12/7</t>
   </si>
   <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
+    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
+  </si>
+  <si>
+    <t>R$  4.642,50</t>
+  </si>
+  <si>
+    <t>18/02/26</t>
+  </si>
+  <si>
+    <t>Webgiga 2026</t>
+  </si>
+  <si>
+    <t>1/5</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>R$  3.750,00</t>
+  </si>
+  <si>
+    <t>Facebook 2026</t>
+  </si>
+  <si>
     <t>Google</t>
   </si>
   <si>
@@ -2161,42 +2197,6 @@
     <t>Google 2026</t>
   </si>
   <si>
-    <t>WEBGIGA SOLUCOES DIGITAIS LTDA</t>
-  </si>
-  <si>
-    <t>R$  4.642,50</t>
-  </si>
-  <si>
-    <t>18/02/26</t>
-  </si>
-  <si>
-    <t>Webgiga 2026</t>
-  </si>
-  <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
-  </si>
-  <si>
-    <t>1/5</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>R$  3.750,00</t>
-  </si>
-  <si>
-    <t>Facebook 2026</t>
-  </si>
-  <si>
     <t>4.03.03.09.06 Marketing - outros gastos (CV)</t>
   </si>
   <si>
@@ -2254,6 +2254,87 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>Estorno emprest jul/1</t>
+  </si>
+  <si>
+    <t>R$  257,40</t>
+  </si>
+  <si>
+    <t>Estorno de empréstimo</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  4.687,39</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>R$  2.365,00</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Fixo jul26/1</t>
+  </si>
+  <si>
+    <t>R$  354,84</t>
+  </si>
+  <si>
+    <t>R$  1.500,00</t>
+  </si>
+  <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>R$  1.645,16</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
+  </si>
+  <si>
+    <t>EFRAIM RIBEIRO</t>
+  </si>
+  <si>
+    <t>R$  1.060,00</t>
+  </si>
+  <si>
+    <t>09/07/26</t>
+  </si>
+  <si>
+    <t>Fixo/1</t>
+  </si>
+  <si>
+    <t>R$  2.536,00</t>
+  </si>
+  <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
     <t>GUTEMBERG DIAS GOMES</t>
   </si>
   <si>
@@ -2263,90 +2344,18 @@
     <t>Gutemberg Dias - Pagamento</t>
   </si>
   <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>R$  2.365,00</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>R$  1.645,16</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Estorno emprest jul/1</t>
-  </si>
-  <si>
-    <t>R$  257,40</t>
-  </si>
-  <si>
-    <t>Estorno de empréstimo</t>
-  </si>
-  <si>
-    <t>Fixo jul26/1</t>
-  </si>
-  <si>
-    <t>R$  354,84</t>
-  </si>
-  <si>
-    <t>R$  1.500,00</t>
-  </si>
-  <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
     <t>722/1</t>
   </si>
   <si>
     <t>06/08/26</t>
   </si>
   <si>
-    <t>EFRAIM RIBEIRO</t>
-  </si>
-  <si>
-    <t>R$  1.060,00</t>
-  </si>
-  <si>
-    <t>09/07/26</t>
-  </si>
-  <si>
-    <t>Fixo/1</t>
-  </si>
-  <si>
-    <t>R$  2.536,00</t>
-  </si>
-  <si>
     <t>Teresinha Elvira Maximino de Menezes</t>
   </si>
   <si>
     <t>Tucha - Fixo 2026</t>
   </si>
   <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
     <t>Denny Lucas do Carmo Pereira</t>
   </si>
   <si>
@@ -2356,15 +2365,6 @@
     <t>Denny Lucas - Pagamento 2026</t>
   </si>
   <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  4.687,39</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
   </si>
   <si>
@@ -2476,18 +2476,18 @@
     <t>4.04.01.05.02.01 Vale transporte</t>
   </si>
   <si>
+    <t>VT julho26/1</t>
+  </si>
+  <si>
+    <t>R$  325,97</t>
+  </si>
+  <si>
     <t>VT jul26/1</t>
   </si>
   <si>
     <t>R$  458,32</t>
   </si>
   <si>
-    <t>VT julho26/1</t>
-  </si>
-  <si>
-    <t>R$  325,97</t>
-  </si>
-  <si>
     <t>4.04.02 GASTOS GERAIS ADMINISTRATIVOS</t>
   </si>
   <si>
@@ -2645,6 +2645,50 @@
   </si>
   <si>
     <t>R$  5,95</t>
+  </si>
+  <si>
+    <t>713/1</t>
+  </si>
+  <si>
+    <t>R$  144,10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reembolso materiais descartáveis
+</t>
+  </si>
+  <si>
+    <t>716/1</t>
+  </si>
+  <si>
+    <t>Marinete</t>
+  </si>
+  <si>
+    <t>R$  108,03</t>
+  </si>
+  <si>
+    <t>Doces festa junina e bandeirinha</t>
+  </si>
+  <si>
+    <t>710/1</t>
+  </si>
+  <si>
+    <t>R$  476,48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reembolso espetinho e bebida festa junina
+</t>
+  </si>
+  <si>
+    <t>717/1</t>
+  </si>
+  <si>
+    <t>Pão de Açúcar</t>
+  </si>
+  <si>
+    <t>R$  62,45</t>
+  </si>
+  <si>
+    <t>materiais consumo loja</t>
   </si>
   <si>
     <t>724/1</t>
@@ -2666,38 +2710,6 @@
 </t>
   </si>
   <si>
-    <t>713/1</t>
-  </si>
-  <si>
-    <t>R$  144,10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reembolso materiais descartáveis
-</t>
-  </si>
-  <si>
-    <t>716/1</t>
-  </si>
-  <si>
-    <t>Marinete</t>
-  </si>
-  <si>
-    <t>R$  108,03</t>
-  </si>
-  <si>
-    <t>Doces festa junina e bandeirinha</t>
-  </si>
-  <si>
-    <t>710/1</t>
-  </si>
-  <si>
-    <t>R$  476,48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reembolso espetinho e bebida festa junina
-</t>
-  </si>
-  <si>
     <t>715/1</t>
   </si>
   <si>
@@ -2710,18 +2722,6 @@
     <t>Insumos para cuscuz festa juninas</t>
   </si>
   <si>
-    <t>717/1</t>
-  </si>
-  <si>
-    <t>Pão de Açúcar</t>
-  </si>
-  <si>
-    <t>R$  62,45</t>
-  </si>
-  <si>
-    <t>materiais consumo loja</t>
-  </si>
-  <si>
     <t>707/1</t>
   </si>
   <si>
@@ -2839,6 +2839,18 @@
     <t>21/05/26</t>
   </si>
   <si>
+    <t>3/6</t>
+  </si>
+  <si>
+    <t>R$  1.248,76</t>
+  </si>
+  <si>
+    <t>13/02/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/2</t>
+  </si>
+  <si>
     <t>64/2</t>
   </si>
   <si>
@@ -2852,18 +2864,6 @@
   </si>
   <si>
     <t>ISO Implantação -Saude ocupacional</t>
-  </si>
-  <si>
-    <t>3/6</t>
-  </si>
-  <si>
-    <t>R$  1.248,76</t>
-  </si>
-  <si>
-    <t>13/02/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/2</t>
   </si>
   <si>
     <t>63/2</t>
@@ -6242,13 +6242,13 @@
         <v>194</v>
       </c>
       <c r="J62" t="s">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="K62" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="L62" t="s">
-        <v>195</v>
+        <v>34</v>
       </c>
       <c r="M62" t="s">
         <v>180</v>
@@ -6283,7 +6283,7 @@
         <v>34</v>
       </c>
       <c r="E63" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F63" t="s">
         <v>55</v>
@@ -6292,19 +6292,19 @@
         <v>40</v>
       </c>
       <c r="H63" t="s">
+        <v>196</v>
+      </c>
+      <c r="I63" t="s">
         <v>197</v>
       </c>
-      <c r="I63" t="s">
+      <c r="J63" t="s">
+        <v>190</v>
+      </c>
+      <c r="K63" t="s">
+        <v>74</v>
+      </c>
+      <c r="L63" t="s">
         <v>198</v>
-      </c>
-      <c r="J63" t="s">
-        <v>69</v>
-      </c>
-      <c r="K63" t="s">
-        <v>101</v>
-      </c>
-      <c r="L63" t="s">
-        <v>34</v>
       </c>
       <c r="M63" t="s">
         <v>180</v>
@@ -6316,7 +6316,7 @@
         <v>47</v>
       </c>
       <c r="P63" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q63" t="s">
         <v>46</v>
@@ -8974,25 +8974,25 @@
         <v>327</v>
       </c>
       <c r="F111" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G111" t="s">
         <v>40</v>
       </c>
       <c r="H111" t="s">
-        <v>183</v>
+        <v>328</v>
       </c>
       <c r="I111" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J111" t="s">
-        <v>156</v>
+        <v>330</v>
       </c>
       <c r="K111" t="s">
-        <v>156</v>
+        <v>331</v>
       </c>
       <c r="L111" t="s">
-        <v>329</v>
+        <v>34</v>
       </c>
       <c r="M111" t="s">
         <v>322</v>
@@ -9004,7 +9004,7 @@
         <v>47</v>
       </c>
       <c r="P111" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q111" t="s">
         <v>46</v>
@@ -9027,7 +9027,7 @@
         <v>34</v>
       </c>
       <c r="E112" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F112" t="s">
         <v>39</v>
@@ -9036,16 +9036,16 @@
         <v>40</v>
       </c>
       <c r="H112" t="s">
+        <v>333</v>
+      </c>
+      <c r="I112" t="s">
+        <v>334</v>
+      </c>
+      <c r="J112" t="s">
+        <v>335</v>
+      </c>
+      <c r="K112" t="s">
         <v>331</v>
-      </c>
-      <c r="I112" t="s">
-        <v>332</v>
-      </c>
-      <c r="J112" t="s">
-        <v>175</v>
-      </c>
-      <c r="K112" t="s">
-        <v>156</v>
       </c>
       <c r="L112" t="s">
         <v>34</v>
@@ -9060,7 +9060,7 @@
         <v>47</v>
       </c>
       <c r="P112" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q112" t="s">
         <v>46</v>
@@ -9083,7 +9083,7 @@
         <v>34</v>
       </c>
       <c r="E113" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F113" t="s">
         <v>39</v>
@@ -9092,16 +9092,16 @@
         <v>40</v>
       </c>
       <c r="H113" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I113" t="s">
         <v>334</v>
       </c>
       <c r="J113" t="s">
-        <v>335</v>
+        <v>297</v>
       </c>
       <c r="K113" t="s">
-        <v>336</v>
+        <v>74</v>
       </c>
       <c r="L113" t="s">
         <v>34</v>
@@ -9148,16 +9148,16 @@
         <v>40</v>
       </c>
       <c r="H114" t="s">
+        <v>333</v>
+      </c>
+      <c r="I114" t="s">
         <v>338</v>
       </c>
-      <c r="I114" t="s">
+      <c r="J114" t="s">
         <v>339</v>
       </c>
-      <c r="J114" t="s">
+      <c r="K114" t="s">
         <v>340</v>
-      </c>
-      <c r="K114" t="s">
-        <v>336</v>
       </c>
       <c r="L114" t="s">
         <v>34</v>
@@ -9172,7 +9172,7 @@
         <v>47</v>
       </c>
       <c r="P114" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q114" t="s">
         <v>46</v>
@@ -9195,28 +9195,28 @@
         <v>34</v>
       </c>
       <c r="E115" t="s">
-        <v>293</v>
+        <v>341</v>
       </c>
       <c r="F115" t="s">
-        <v>39</v>
+        <v>207</v>
       </c>
       <c r="G115" t="s">
         <v>40</v>
       </c>
       <c r="H115" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="I115" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J115" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
       <c r="K115" t="s">
-        <v>247</v>
+        <v>91</v>
       </c>
       <c r="L115" t="s">
-        <v>34</v>
+        <v>344</v>
       </c>
       <c r="M115" t="s">
         <v>322</v>
@@ -9225,10 +9225,10 @@
         <v>46</v>
       </c>
       <c r="O115" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="P115" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q115" t="s">
         <v>46</v>
@@ -9251,7 +9251,7 @@
         <v>34</v>
       </c>
       <c r="E116" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F116" t="s">
         <v>39</v>
@@ -9260,19 +9260,19 @@
         <v>40</v>
       </c>
       <c r="H116" t="s">
+        <v>328</v>
+      </c>
+      <c r="I116" t="s">
+        <v>346</v>
+      </c>
+      <c r="J116" t="s">
+        <v>330</v>
+      </c>
+      <c r="K116" t="s">
         <v>331</v>
       </c>
-      <c r="I116" t="s">
-        <v>343</v>
-      </c>
-      <c r="J116" t="s">
-        <v>335</v>
-      </c>
-      <c r="K116" t="s">
-        <v>336</v>
-      </c>
       <c r="L116" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M116" t="s">
         <v>322</v>
@@ -9284,7 +9284,7 @@
         <v>47</v>
       </c>
       <c r="P116" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q116" t="s">
         <v>46</v>
@@ -9307,7 +9307,7 @@
         <v>34</v>
       </c>
       <c r="E117" t="s">
-        <v>345</v>
+        <v>293</v>
       </c>
       <c r="F117" t="s">
         <v>39</v>
@@ -9316,19 +9316,19 @@
         <v>40</v>
       </c>
       <c r="H117" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="I117" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J117" t="s">
-        <v>297</v>
+        <v>247</v>
       </c>
       <c r="K117" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="L117" t="s">
-        <v>347</v>
+        <v>34</v>
       </c>
       <c r="M117" t="s">
         <v>322</v>
@@ -9337,10 +9337,10 @@
         <v>46</v>
       </c>
       <c r="O117" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="P117" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q117" t="s">
         <v>46</v>
@@ -9363,7 +9363,7 @@
         <v>34</v>
       </c>
       <c r="E118" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F118" t="s">
         <v>39</v>
@@ -9372,19 +9372,19 @@
         <v>40</v>
       </c>
       <c r="H118" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="I118" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="J118" t="s">
-        <v>297</v>
+        <v>351</v>
       </c>
       <c r="K118" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="L118" t="s">
-        <v>34</v>
+        <v>352</v>
       </c>
       <c r="M118" t="s">
         <v>322</v>
@@ -9396,7 +9396,7 @@
         <v>47</v>
       </c>
       <c r="P118" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="Q118" t="s">
         <v>46</v>
@@ -9419,28 +9419,28 @@
         <v>34</v>
       </c>
       <c r="E119" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F119" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="G119" t="s">
         <v>40</v>
       </c>
       <c r="H119" t="s">
-        <v>338</v>
+        <v>183</v>
       </c>
       <c r="I119" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="J119" t="s">
-        <v>351</v>
+        <v>156</v>
       </c>
       <c r="K119" t="s">
-        <v>352</v>
+        <v>156</v>
       </c>
       <c r="L119" t="s">
-        <v>34</v>
+        <v>355</v>
       </c>
       <c r="M119" t="s">
         <v>322</v>
@@ -9452,7 +9452,7 @@
         <v>47</v>
       </c>
       <c r="P119" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="Q119" t="s">
         <v>46</v>
@@ -9475,28 +9475,28 @@
         <v>34</v>
       </c>
       <c r="E120" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F120" t="s">
-        <v>207</v>
+        <v>39</v>
       </c>
       <c r="G120" t="s">
         <v>40</v>
       </c>
       <c r="H120" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="I120" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J120" t="s">
-        <v>318</v>
+        <v>175</v>
       </c>
       <c r="K120" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="L120" t="s">
-        <v>356</v>
+        <v>34</v>
       </c>
       <c r="M120" t="s">
         <v>322</v>
@@ -9508,7 +9508,7 @@
         <v>47</v>
       </c>
       <c r="P120" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q120" t="s">
         <v>46</v>
@@ -9531,7 +9531,7 @@
         <v>34</v>
       </c>
       <c r="E121" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F121" t="s">
         <v>39</v>
@@ -9540,16 +9540,16 @@
         <v>40</v>
       </c>
       <c r="H121" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="I121" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J121" t="s">
-        <v>359</v>
+        <v>297</v>
       </c>
       <c r="K121" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="L121" t="s">
         <v>360</v>
@@ -9564,7 +9564,7 @@
         <v>47</v>
       </c>
       <c r="P121" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q121" t="s">
         <v>46</v>
@@ -9596,7 +9596,7 @@
         <v>40</v>
       </c>
       <c r="H122" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="I122" t="s">
         <v>362</v>
@@ -9652,7 +9652,7 @@
         <v>40</v>
       </c>
       <c r="H123" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="I123" t="s">
         <v>366</v>
@@ -12455,7 +12455,7 @@
         <v>324</v>
       </c>
       <c r="I173" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J173" t="s">
         <v>465</v>
@@ -12476,7 +12476,7 @@
         <v>47</v>
       </c>
       <c r="P173" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Q173" t="s">
         <v>46</v>
@@ -12508,10 +12508,10 @@
         <v>40</v>
       </c>
       <c r="H174" t="s">
+        <v>467</v>
+      </c>
+      <c r="I174" t="s">
         <v>466</v>
-      </c>
-      <c r="I174" t="s">
-        <v>467</v>
       </c>
       <c r="J174" t="s">
         <v>465</v>
@@ -12532,7 +12532,7 @@
         <v>47</v>
       </c>
       <c r="P174" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Q174" t="s">
         <v>46</v>
@@ -12682,7 +12682,7 @@
         <v>474</v>
       </c>
       <c r="J177" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K177" t="s">
         <v>247</v>
@@ -12738,7 +12738,7 @@
         <v>475</v>
       </c>
       <c r="J178" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K178" t="s">
         <v>247</v>
@@ -12794,7 +12794,7 @@
         <v>477</v>
       </c>
       <c r="J179" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K179" t="s">
         <v>247</v>
@@ -12850,7 +12850,7 @@
         <v>478</v>
       </c>
       <c r="J180" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K180" t="s">
         <v>247</v>
@@ -12906,7 +12906,7 @@
         <v>479</v>
       </c>
       <c r="J181" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K181" t="s">
         <v>247</v>
@@ -12962,7 +12962,7 @@
         <v>480</v>
       </c>
       <c r="J182" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K182" t="s">
         <v>247</v>
@@ -13018,7 +13018,7 @@
         <v>481</v>
       </c>
       <c r="J183" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K183" t="s">
         <v>247</v>
@@ -13074,7 +13074,7 @@
         <v>482</v>
       </c>
       <c r="J184" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K184" t="s">
         <v>247</v>
@@ -13130,7 +13130,7 @@
         <v>484</v>
       </c>
       <c r="J185" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K185" t="s">
         <v>247</v>
@@ -13186,7 +13186,7 @@
         <v>485</v>
       </c>
       <c r="J186" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K186" t="s">
         <v>247</v>
@@ -13242,7 +13242,7 @@
         <v>486</v>
       </c>
       <c r="J187" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K187" t="s">
         <v>247</v>
@@ -13298,7 +13298,7 @@
         <v>488</v>
       </c>
       <c r="J188" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K188" t="s">
         <v>247</v>
@@ -13354,7 +13354,7 @@
         <v>490</v>
       </c>
       <c r="J189" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K189" t="s">
         <v>247</v>
@@ -13410,7 +13410,7 @@
         <v>491</v>
       </c>
       <c r="J190" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K190" t="s">
         <v>247</v>
@@ -13466,7 +13466,7 @@
         <v>492</v>
       </c>
       <c r="J191" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K191" t="s">
         <v>247</v>
@@ -13522,7 +13522,7 @@
         <v>493</v>
       </c>
       <c r="J192" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K192" t="s">
         <v>247</v>
@@ -13578,7 +13578,7 @@
         <v>494</v>
       </c>
       <c r="J193" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K193" t="s">
         <v>247</v>
@@ -13634,7 +13634,7 @@
         <v>495</v>
       </c>
       <c r="J194" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K194" t="s">
         <v>59</v>
@@ -13970,7 +13970,7 @@
         <v>507</v>
       </c>
       <c r="J200" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K200" t="s">
         <v>247</v>
@@ -14026,7 +14026,7 @@
         <v>508</v>
       </c>
       <c r="J201" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K201" t="s">
         <v>59</v>
@@ -14082,7 +14082,7 @@
         <v>509</v>
       </c>
       <c r="J202" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K202" t="s">
         <v>247</v>
@@ -14138,7 +14138,7 @@
         <v>510</v>
       </c>
       <c r="J203" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K203" t="s">
         <v>247</v>
@@ -14194,7 +14194,7 @@
         <v>511</v>
       </c>
       <c r="J204" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K204" t="s">
         <v>247</v>
@@ -14250,7 +14250,7 @@
         <v>512</v>
       </c>
       <c r="J205" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K205" t="s">
         <v>247</v>
@@ -14306,7 +14306,7 @@
         <v>513</v>
       </c>
       <c r="J206" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K206" t="s">
         <v>247</v>
@@ -14362,7 +14362,7 @@
         <v>514</v>
       </c>
       <c r="J207" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K207" t="s">
         <v>247</v>
@@ -14418,7 +14418,7 @@
         <v>515</v>
       </c>
       <c r="J208" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K208" t="s">
         <v>247</v>
@@ -14474,7 +14474,7 @@
         <v>516</v>
       </c>
       <c r="J209" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K209" t="s">
         <v>247</v>
@@ -14530,7 +14530,7 @@
         <v>517</v>
       </c>
       <c r="J210" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K210" t="s">
         <v>247</v>
@@ -14586,7 +14586,7 @@
         <v>518</v>
       </c>
       <c r="J211" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K211" t="s">
         <v>247</v>
@@ -14642,7 +14642,7 @@
         <v>519</v>
       </c>
       <c r="J212" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K212" t="s">
         <v>247</v>
@@ -14698,7 +14698,7 @@
         <v>520</v>
       </c>
       <c r="J213" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K213" t="s">
         <v>247</v>
@@ -14754,7 +14754,7 @@
         <v>521</v>
       </c>
       <c r="J214" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K214" t="s">
         <v>247</v>
@@ -14810,7 +14810,7 @@
         <v>522</v>
       </c>
       <c r="J215" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K215" t="s">
         <v>247</v>
@@ -14866,7 +14866,7 @@
         <v>524</v>
       </c>
       <c r="J216" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K216" t="s">
         <v>247</v>
@@ -14922,7 +14922,7 @@
         <v>525</v>
       </c>
       <c r="J217" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K217" t="s">
         <v>247</v>
@@ -14978,7 +14978,7 @@
         <v>526</v>
       </c>
       <c r="J218" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K218" t="s">
         <v>247</v>
@@ -15034,7 +15034,7 @@
         <v>528</v>
       </c>
       <c r="J219" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K219" t="s">
         <v>247</v>
@@ -15090,7 +15090,7 @@
         <v>529</v>
       </c>
       <c r="J220" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K220" t="s">
         <v>247</v>
@@ -15146,7 +15146,7 @@
         <v>530</v>
       </c>
       <c r="J221" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K221" t="s">
         <v>247</v>
@@ -15202,7 +15202,7 @@
         <v>531</v>
       </c>
       <c r="J222" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K222" t="s">
         <v>247</v>
@@ -15258,7 +15258,7 @@
         <v>532</v>
       </c>
       <c r="J223" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K223" t="s">
         <v>247</v>
@@ -15314,7 +15314,7 @@
         <v>534</v>
       </c>
       <c r="J224" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K224" t="s">
         <v>247</v>
@@ -15370,7 +15370,7 @@
         <v>536</v>
       </c>
       <c r="J225" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K225" t="s">
         <v>247</v>
@@ -15426,7 +15426,7 @@
         <v>537</v>
       </c>
       <c r="J226" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K226" t="s">
         <v>247</v>
@@ -15482,7 +15482,7 @@
         <v>538</v>
       </c>
       <c r="J227" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K227" t="s">
         <v>247</v>
@@ -15538,7 +15538,7 @@
         <v>540</v>
       </c>
       <c r="J228" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K228" t="s">
         <v>247</v>
@@ -15594,7 +15594,7 @@
         <v>478</v>
       </c>
       <c r="J229" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K229" t="s">
         <v>247</v>
@@ -15650,7 +15650,7 @@
         <v>475</v>
       </c>
       <c r="J230" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K230" t="s">
         <v>247</v>
@@ -15706,7 +15706,7 @@
         <v>477</v>
       </c>
       <c r="J231" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K231" t="s">
         <v>247</v>
@@ -15762,7 +15762,7 @@
         <v>541</v>
       </c>
       <c r="J232" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K232" t="s">
         <v>247</v>
@@ -15818,7 +15818,7 @@
         <v>479</v>
       </c>
       <c r="J233" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K233" t="s">
         <v>247</v>
@@ -15874,7 +15874,7 @@
         <v>480</v>
       </c>
       <c r="J234" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K234" t="s">
         <v>247</v>
@@ -15930,7 +15930,7 @@
         <v>481</v>
       </c>
       <c r="J235" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K235" t="s">
         <v>247</v>
@@ -15986,7 +15986,7 @@
         <v>482</v>
       </c>
       <c r="J236" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K236" t="s">
         <v>247</v>
@@ -16042,7 +16042,7 @@
         <v>484</v>
       </c>
       <c r="J237" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K237" t="s">
         <v>247</v>
@@ -16098,7 +16098,7 @@
         <v>485</v>
       </c>
       <c r="J238" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K238" t="s">
         <v>247</v>
@@ -16154,7 +16154,7 @@
         <v>486</v>
       </c>
       <c r="J239" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K239" t="s">
         <v>247</v>
@@ -16210,7 +16210,7 @@
         <v>488</v>
       </c>
       <c r="J240" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K240" t="s">
         <v>247</v>
@@ -16266,7 +16266,7 @@
         <v>490</v>
       </c>
       <c r="J241" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K241" t="s">
         <v>247</v>
@@ -16322,7 +16322,7 @@
         <v>491</v>
       </c>
       <c r="J242" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K242" t="s">
         <v>247</v>
@@ -16378,7 +16378,7 @@
         <v>492</v>
       </c>
       <c r="J243" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K243" t="s">
         <v>247</v>
@@ -16434,7 +16434,7 @@
         <v>493</v>
       </c>
       <c r="J244" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K244" t="s">
         <v>247</v>
@@ -16490,7 +16490,7 @@
         <v>494</v>
       </c>
       <c r="J245" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K245" t="s">
         <v>247</v>
@@ -16546,7 +16546,7 @@
         <v>495</v>
       </c>
       <c r="J246" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K246" t="s">
         <v>59</v>
@@ -16602,7 +16602,7 @@
         <v>542</v>
       </c>
       <c r="J247" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K247" t="s">
         <v>247</v>
@@ -16658,7 +16658,7 @@
         <v>544</v>
       </c>
       <c r="J248" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K248" t="s">
         <v>247</v>
@@ -16714,7 +16714,7 @@
         <v>545</v>
       </c>
       <c r="J249" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K249" t="s">
         <v>247</v>
@@ -16770,7 +16770,7 @@
         <v>546</v>
       </c>
       <c r="J250" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K250" t="s">
         <v>247</v>
@@ -16826,7 +16826,7 @@
         <v>547</v>
       </c>
       <c r="J251" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K251" t="s">
         <v>247</v>
@@ -16882,7 +16882,7 @@
         <v>548</v>
       </c>
       <c r="J252" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K252" t="s">
         <v>247</v>
@@ -16938,7 +16938,7 @@
         <v>549</v>
       </c>
       <c r="J253" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K253" t="s">
         <v>247</v>
@@ -16994,7 +16994,7 @@
         <v>550</v>
       </c>
       <c r="J254" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K254" t="s">
         <v>247</v>
@@ -17050,7 +17050,7 @@
         <v>551</v>
       </c>
       <c r="J255" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K255" t="s">
         <v>247</v>
@@ -17106,7 +17106,7 @@
         <v>552</v>
       </c>
       <c r="J256" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K256" t="s">
         <v>59</v>
@@ -18002,7 +18002,7 @@
         <v>573</v>
       </c>
       <c r="J272" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K272" t="s">
         <v>247</v>
@@ -18058,7 +18058,7 @@
         <v>574</v>
       </c>
       <c r="J273" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K273" t="s">
         <v>247</v>
@@ -18114,7 +18114,7 @@
         <v>575</v>
       </c>
       <c r="J274" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K274" t="s">
         <v>247</v>
@@ -18170,7 +18170,7 @@
         <v>576</v>
       </c>
       <c r="J275" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K275" t="s">
         <v>247</v>
@@ -18226,7 +18226,7 @@
         <v>579</v>
       </c>
       <c r="J276" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K276" t="s">
         <v>247</v>
@@ -18267,7 +18267,7 @@
         <v>33</v>
       </c>
       <c r="E277" t="s">
-        <v>583</v>
+        <v>405</v>
       </c>
       <c r="F277" t="s">
         <v>497</v>
@@ -18279,13 +18279,13 @@
         <v>236</v>
       </c>
       <c r="I277" t="s">
-        <v>563</v>
+        <v>583</v>
       </c>
       <c r="J277" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="K277" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="L277" t="s">
         <v>34</v>
@@ -18323,7 +18323,7 @@
         <v>34</v>
       </c>
       <c r="E278" t="s">
-        <v>382</v>
+        <v>305</v>
       </c>
       <c r="F278" t="s">
         <v>497</v>
@@ -18332,16 +18332,16 @@
         <v>40</v>
       </c>
       <c r="H278" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="I278" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J278" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="K278" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="L278" t="s">
         <v>34</v>
@@ -18391,7 +18391,7 @@
         <v>236</v>
       </c>
       <c r="I279" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="J279" t="s">
         <v>59</v>
@@ -18435,25 +18435,25 @@
         <v>34</v>
       </c>
       <c r="E280" t="s">
-        <v>300</v>
+        <v>417</v>
       </c>
       <c r="F280" t="s">
-        <v>243</v>
+        <v>497</v>
       </c>
       <c r="G280" t="s">
         <v>40</v>
       </c>
       <c r="H280" t="s">
-        <v>578</v>
+        <v>236</v>
       </c>
       <c r="I280" t="s">
-        <v>496</v>
+        <v>587</v>
       </c>
       <c r="J280" t="s">
-        <v>307</v>
+        <v>59</v>
       </c>
       <c r="K280" t="s">
-        <v>247</v>
+        <v>59</v>
       </c>
       <c r="L280" t="s">
         <v>34</v>
@@ -18465,13 +18465,13 @@
         <v>46</v>
       </c>
       <c r="O280" t="s">
-        <v>303</v>
+        <v>34</v>
       </c>
       <c r="P280" t="s">
-        <v>496</v>
+        <v>34</v>
       </c>
       <c r="Q280" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R280" t="s">
         <v>34</v>
@@ -18491,25 +18491,25 @@
         <v>34</v>
       </c>
       <c r="E281" t="s">
-        <v>258</v>
+        <v>588</v>
       </c>
       <c r="F281" t="s">
-        <v>243</v>
+        <v>497</v>
       </c>
       <c r="G281" t="s">
         <v>40</v>
       </c>
       <c r="H281" t="s">
-        <v>586</v>
+        <v>236</v>
       </c>
       <c r="I281" t="s">
-        <v>477</v>
+        <v>566</v>
       </c>
       <c r="J281" t="s">
-        <v>335</v>
+        <v>58</v>
       </c>
       <c r="K281" t="s">
-        <v>247</v>
+        <v>58</v>
       </c>
       <c r="L281" t="s">
         <v>34</v>
@@ -18521,13 +18521,13 @@
         <v>46</v>
       </c>
       <c r="O281" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="P281" t="s">
-        <v>477</v>
+        <v>34</v>
       </c>
       <c r="Q281" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R281" t="s">
         <v>34</v>
@@ -18547,25 +18547,25 @@
         <v>34</v>
       </c>
       <c r="E282" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="F282" t="s">
-        <v>497</v>
+        <v>243</v>
       </c>
       <c r="G282" t="s">
         <v>40</v>
       </c>
       <c r="H282" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="I282" t="s">
-        <v>588</v>
+        <v>496</v>
       </c>
       <c r="J282" t="s">
-        <v>58</v>
+        <v>307</v>
       </c>
       <c r="K282" t="s">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="L282" t="s">
         <v>34</v>
@@ -18577,13 +18577,13 @@
         <v>46</v>
       </c>
       <c r="O282" t="s">
-        <v>34</v>
+        <v>303</v>
       </c>
       <c r="P282" t="s">
-        <v>34</v>
+        <v>496</v>
       </c>
       <c r="Q282" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R282" t="s">
         <v>34</v>
@@ -18603,7 +18603,7 @@
         <v>34</v>
       </c>
       <c r="E283" t="s">
-        <v>589</v>
+        <v>258</v>
       </c>
       <c r="F283" t="s">
         <v>243</v>
@@ -18612,13 +18612,13 @@
         <v>40</v>
       </c>
       <c r="H283" t="s">
-        <v>539</v>
+        <v>589</v>
       </c>
       <c r="I283" t="s">
-        <v>590</v>
+        <v>477</v>
       </c>
       <c r="J283" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K283" t="s">
         <v>247</v>
@@ -18633,10 +18633,10 @@
         <v>46</v>
       </c>
       <c r="O283" t="s">
-        <v>591</v>
+        <v>88</v>
       </c>
       <c r="P283" t="s">
-        <v>590</v>
+        <v>477</v>
       </c>
       <c r="Q283" t="s">
         <v>46</v>
@@ -18659,7 +18659,7 @@
         <v>34</v>
       </c>
       <c r="E284" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F284" t="s">
         <v>243</v>
@@ -18671,10 +18671,10 @@
         <v>539</v>
       </c>
       <c r="I284" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J284" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K284" t="s">
         <v>247</v>
@@ -18689,10 +18689,10 @@
         <v>46</v>
       </c>
       <c r="O284" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="P284" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="Q284" t="s">
         <v>46</v>
@@ -18715,25 +18715,25 @@
         <v>34</v>
       </c>
       <c r="E285" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F285" t="s">
-        <v>497</v>
+        <v>243</v>
       </c>
       <c r="G285" t="s">
         <v>40</v>
       </c>
       <c r="H285" t="s">
-        <v>236</v>
+        <v>539</v>
       </c>
       <c r="I285" t="s">
-        <v>566</v>
+        <v>594</v>
       </c>
       <c r="J285" t="s">
-        <v>58</v>
+        <v>330</v>
       </c>
       <c r="K285" t="s">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="L285" t="s">
         <v>34</v>
@@ -18745,13 +18745,13 @@
         <v>46</v>
       </c>
       <c r="O285" t="s">
-        <v>34</v>
+        <v>595</v>
       </c>
       <c r="P285" t="s">
-        <v>34</v>
+        <v>594</v>
       </c>
       <c r="Q285" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R285" t="s">
         <v>34</v>
@@ -18771,7 +18771,7 @@
         <v>34</v>
       </c>
       <c r="E286" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="F286" t="s">
         <v>243</v>
@@ -18780,16 +18780,16 @@
         <v>40</v>
       </c>
       <c r="H286" t="s">
-        <v>578</v>
+        <v>539</v>
       </c>
       <c r="I286" t="s">
-        <v>596</v>
+        <v>495</v>
       </c>
       <c r="J286" t="s">
         <v>307</v>
       </c>
       <c r="K286" t="s">
-        <v>247</v>
+        <v>59</v>
       </c>
       <c r="L286" t="s">
         <v>34</v>
@@ -18801,10 +18801,10 @@
         <v>46</v>
       </c>
       <c r="O286" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="P286" t="s">
-        <v>596</v>
+        <v>495</v>
       </c>
       <c r="Q286" t="s">
         <v>46</v>
@@ -18883,7 +18883,7 @@
         <v>34</v>
       </c>
       <c r="E288" t="s">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="F288" t="s">
         <v>243</v>
@@ -18892,16 +18892,16 @@
         <v>40</v>
       </c>
       <c r="H288" t="s">
-        <v>539</v>
+        <v>578</v>
       </c>
       <c r="I288" t="s">
-        <v>495</v>
+        <v>596</v>
       </c>
       <c r="J288" t="s">
         <v>307</v>
       </c>
       <c r="K288" t="s">
-        <v>59</v>
+        <v>247</v>
       </c>
       <c r="L288" t="s">
         <v>34</v>
@@ -18913,10 +18913,10 @@
         <v>46</v>
       </c>
       <c r="O288" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="P288" t="s">
-        <v>495</v>
+        <v>596</v>
       </c>
       <c r="Q288" t="s">
         <v>46</v>
@@ -18939,7 +18939,7 @@
         <v>34</v>
       </c>
       <c r="E289" t="s">
-        <v>396</v>
+        <v>313</v>
       </c>
       <c r="F289" t="s">
         <v>497</v>
@@ -18948,16 +18948,16 @@
         <v>40</v>
       </c>
       <c r="H289" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="I289" t="s">
-        <v>597</v>
+        <v>484</v>
       </c>
       <c r="J289" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="K289" t="s">
-        <v>109</v>
+        <v>247</v>
       </c>
       <c r="L289" t="s">
         <v>34</v>
@@ -18995,7 +18995,7 @@
         <v>34</v>
       </c>
       <c r="E290" t="s">
-        <v>295</v>
+        <v>396</v>
       </c>
       <c r="F290" t="s">
         <v>497</v>
@@ -19004,16 +19004,16 @@
         <v>40</v>
       </c>
       <c r="H290" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="I290" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J290" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="K290" t="s">
-        <v>247</v>
+        <v>109</v>
       </c>
       <c r="L290" t="s">
         <v>34</v>
@@ -19051,7 +19051,7 @@
         <v>34</v>
       </c>
       <c r="E291" t="s">
-        <v>417</v>
+        <v>388</v>
       </c>
       <c r="F291" t="s">
         <v>497</v>
@@ -19063,13 +19063,13 @@
         <v>236</v>
       </c>
       <c r="I291" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J291" t="s">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="K291" t="s">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="L291" t="s">
         <v>34</v>
@@ -19107,7 +19107,7 @@
         <v>34</v>
       </c>
       <c r="E292" t="s">
-        <v>313</v>
+        <v>409</v>
       </c>
       <c r="F292" t="s">
         <v>497</v>
@@ -19116,16 +19116,16 @@
         <v>40</v>
       </c>
       <c r="H292" t="s">
-        <v>587</v>
+        <v>236</v>
       </c>
       <c r="I292" t="s">
-        <v>484</v>
+        <v>599</v>
       </c>
       <c r="J292" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="K292" t="s">
-        <v>247</v>
+        <v>146</v>
       </c>
       <c r="L292" t="s">
         <v>34</v>
@@ -19163,7 +19163,7 @@
         <v>34</v>
       </c>
       <c r="E293" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F293" t="s">
         <v>497</v>
@@ -19172,16 +19172,16 @@
         <v>40</v>
       </c>
       <c r="H293" t="s">
-        <v>236</v>
+        <v>578</v>
       </c>
       <c r="I293" t="s">
         <v>600</v>
       </c>
       <c r="J293" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="K293" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="L293" t="s">
         <v>34</v>
@@ -19231,13 +19231,13 @@
         <v>236</v>
       </c>
       <c r="I294" t="s">
-        <v>541</v>
+        <v>563</v>
       </c>
       <c r="J294" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="K294" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="L294" t="s">
         <v>34</v>
@@ -19275,7 +19275,7 @@
         <v>34</v>
       </c>
       <c r="E295" t="s">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="F295" t="s">
         <v>497</v>
@@ -19284,16 +19284,16 @@
         <v>40</v>
       </c>
       <c r="H295" t="s">
-        <v>236</v>
+        <v>578</v>
       </c>
       <c r="I295" t="s">
         <v>602</v>
       </c>
       <c r="J295" t="s">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="K295" t="s">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="L295" t="s">
         <v>34</v>
@@ -19387,7 +19387,7 @@
         <v>34</v>
       </c>
       <c r="E297" t="s">
-        <v>392</v>
+        <v>295</v>
       </c>
       <c r="F297" t="s">
         <v>497</v>
@@ -19396,16 +19396,16 @@
         <v>40</v>
       </c>
       <c r="H297" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="I297" t="s">
         <v>604</v>
       </c>
       <c r="J297" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="K297" t="s">
-        <v>132</v>
+        <v>247</v>
       </c>
       <c r="L297" t="s">
         <v>34</v>
@@ -19443,7 +19443,7 @@
         <v>34</v>
       </c>
       <c r="E298" t="s">
-        <v>405</v>
+        <v>605</v>
       </c>
       <c r="F298" t="s">
         <v>497</v>
@@ -19455,13 +19455,13 @@
         <v>236</v>
       </c>
       <c r="I298" t="s">
-        <v>605</v>
+        <v>541</v>
       </c>
       <c r="J298" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="K298" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="L298" t="s">
         <v>34</v>
@@ -21076,7 +21076,7 @@
         <v>40</v>
       </c>
       <c r="H327" t="s">
-        <v>473</v>
+        <v>535</v>
       </c>
       <c r="I327" t="s">
         <v>646</v>
@@ -21132,7 +21132,7 @@
         <v>40</v>
       </c>
       <c r="H328" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
       <c r="I328" t="s">
         <v>647</v>
@@ -21642,7 +21642,7 @@
         <v>665</v>
       </c>
       <c r="J337" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K337" t="s">
         <v>666</v>
@@ -21698,7 +21698,7 @@
         <v>669</v>
       </c>
       <c r="J338" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K338" t="s">
         <v>666</v>
@@ -21754,7 +21754,7 @@
         <v>672</v>
       </c>
       <c r="J339" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K339" t="s">
         <v>666</v>
@@ -21810,7 +21810,7 @@
         <v>675</v>
       </c>
       <c r="J340" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K340" t="s">
         <v>666</v>
@@ -21866,7 +21866,7 @@
         <v>678</v>
       </c>
       <c r="J341" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K341" t="s">
         <v>666</v>
@@ -21922,7 +21922,7 @@
         <v>681</v>
       </c>
       <c r="J342" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K342" t="s">
         <v>666</v>
@@ -22075,25 +22075,25 @@
         <v>33</v>
       </c>
       <c r="E345" t="s">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="F345" t="s">
+        <v>39</v>
+      </c>
+      <c r="G345" t="s">
+        <v>40</v>
+      </c>
+      <c r="H345" t="s">
         <v>686</v>
       </c>
-      <c r="G345" t="s">
-        <v>40</v>
-      </c>
-      <c r="H345" t="s">
+      <c r="I345" t="s">
         <v>687</v>
       </c>
-      <c r="I345" t="s">
-        <v>688</v>
-      </c>
       <c r="J345" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K345" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L345" t="s">
         <v>34</v>
@@ -22105,13 +22105,13 @@
         <v>46</v>
       </c>
       <c r="O345" t="s">
-        <v>34</v>
+        <v>138</v>
       </c>
       <c r="P345" t="s">
-        <v>34</v>
+        <v>687</v>
       </c>
       <c r="Q345" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R345" t="s">
         <v>34</v>
@@ -22131,25 +22131,25 @@
         <v>34</v>
       </c>
       <c r="E346" t="s">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="F346" t="s">
-        <v>207</v>
+        <v>688</v>
       </c>
       <c r="G346" t="s">
         <v>40</v>
       </c>
       <c r="H346" t="s">
+        <v>686</v>
+      </c>
+      <c r="I346" t="s">
         <v>687</v>
       </c>
-      <c r="I346" t="s">
-        <v>688</v>
-      </c>
       <c r="J346" t="s">
-        <v>302</v>
+        <v>59</v>
       </c>
       <c r="K346" t="s">
-        <v>247</v>
+        <v>59</v>
       </c>
       <c r="L346" t="s">
         <v>34</v>
@@ -22161,13 +22161,13 @@
         <v>46</v>
       </c>
       <c r="O346" t="s">
-        <v>303</v>
+        <v>34</v>
       </c>
       <c r="P346" t="s">
-        <v>688</v>
+        <v>34</v>
       </c>
       <c r="Q346" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R346" t="s">
         <v>34</v>
@@ -22187,7 +22187,7 @@
         <v>34</v>
       </c>
       <c r="E347" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="F347" t="s">
         <v>207</v>
@@ -22196,16 +22196,16 @@
         <v>40</v>
       </c>
       <c r="H347" t="s">
+        <v>686</v>
+      </c>
+      <c r="I347" t="s">
         <v>687</v>
       </c>
-      <c r="I347" t="s">
-        <v>688</v>
-      </c>
       <c r="J347" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K347" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L347" t="s">
         <v>34</v>
@@ -22217,10 +22217,10 @@
         <v>46</v>
       </c>
       <c r="O347" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="P347" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Q347" t="s">
         <v>46</v>
@@ -22243,25 +22243,25 @@
         <v>34</v>
       </c>
       <c r="E348" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="F348" t="s">
-        <v>207</v>
+        <v>688</v>
       </c>
       <c r="G348" t="s">
         <v>40</v>
       </c>
       <c r="H348" t="s">
+        <v>686</v>
+      </c>
+      <c r="I348" t="s">
         <v>687</v>
       </c>
-      <c r="I348" t="s">
-        <v>688</v>
-      </c>
       <c r="J348" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K348" t="s">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="L348" t="s">
         <v>34</v>
@@ -22273,13 +22273,13 @@
         <v>46</v>
       </c>
       <c r="O348" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="P348" t="s">
-        <v>688</v>
+        <v>34</v>
       </c>
       <c r="Q348" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R348" t="s">
         <v>34</v>
@@ -22299,25 +22299,25 @@
         <v>34</v>
       </c>
       <c r="E349" t="s">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="F349" t="s">
-        <v>39</v>
+        <v>207</v>
       </c>
       <c r="G349" t="s">
         <v>40</v>
       </c>
       <c r="H349" t="s">
+        <v>686</v>
+      </c>
+      <c r="I349" t="s">
         <v>687</v>
       </c>
-      <c r="I349" t="s">
-        <v>688</v>
-      </c>
       <c r="J349" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="K349" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="L349" t="s">
         <v>34</v>
@@ -22329,10 +22329,10 @@
         <v>46</v>
       </c>
       <c r="O349" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="P349" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Q349" t="s">
         <v>46</v>
@@ -22364,10 +22364,10 @@
         <v>40</v>
       </c>
       <c r="H350" t="s">
+        <v>686</v>
+      </c>
+      <c r="I350" t="s">
         <v>687</v>
-      </c>
-      <c r="I350" t="s">
-        <v>688</v>
       </c>
       <c r="J350" t="s">
         <v>109</v>
@@ -22388,7 +22388,7 @@
         <v>489</v>
       </c>
       <c r="P350" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Q350" t="s">
         <v>46</v>
@@ -22411,7 +22411,7 @@
         <v>34</v>
       </c>
       <c r="E351" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="F351" t="s">
         <v>207</v>
@@ -22420,16 +22420,16 @@
         <v>40</v>
       </c>
       <c r="H351" t="s">
+        <v>686</v>
+      </c>
+      <c r="I351" t="s">
         <v>687</v>
       </c>
-      <c r="I351" t="s">
-        <v>688</v>
-      </c>
       <c r="J351" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="K351" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="L351" t="s">
         <v>34</v>
@@ -22441,10 +22441,10 @@
         <v>46</v>
       </c>
       <c r="O351" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="P351" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Q351" t="s">
         <v>46</v>
@@ -22467,25 +22467,25 @@
         <v>34</v>
       </c>
       <c r="E352" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="F352" t="s">
-        <v>207</v>
+        <v>688</v>
       </c>
       <c r="G352" t="s">
         <v>40</v>
       </c>
       <c r="H352" t="s">
+        <v>686</v>
+      </c>
+      <c r="I352" t="s">
         <v>687</v>
       </c>
-      <c r="I352" t="s">
-        <v>688</v>
-      </c>
       <c r="J352" t="s">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="K352" t="s">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="L352" t="s">
         <v>34</v>
@@ -22497,13 +22497,13 @@
         <v>46</v>
       </c>
       <c r="O352" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="P352" t="s">
-        <v>688</v>
+        <v>34</v>
       </c>
       <c r="Q352" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R352" t="s">
         <v>34</v>
@@ -22523,19 +22523,19 @@
         <v>34</v>
       </c>
       <c r="E353" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F353" t="s">
-        <v>207</v>
+        <v>688</v>
       </c>
       <c r="G353" t="s">
         <v>40</v>
       </c>
       <c r="H353" t="s">
+        <v>686</v>
+      </c>
+      <c r="I353" t="s">
         <v>687</v>
-      </c>
-      <c r="I353" t="s">
-        <v>688</v>
       </c>
       <c r="J353" t="s">
         <v>59</v>
@@ -22553,13 +22553,13 @@
         <v>46</v>
       </c>
       <c r="O353" t="s">
-        <v>281</v>
+        <v>34</v>
       </c>
       <c r="P353" t="s">
-        <v>688</v>
+        <v>34</v>
       </c>
       <c r="Q353" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R353" t="s">
         <v>34</v>
@@ -22579,25 +22579,25 @@
         <v>34</v>
       </c>
       <c r="E354" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="F354" t="s">
-        <v>207</v>
+        <v>688</v>
       </c>
       <c r="G354" t="s">
         <v>40</v>
       </c>
       <c r="H354" t="s">
+        <v>686</v>
+      </c>
+      <c r="I354" t="s">
         <v>687</v>
       </c>
-      <c r="I354" t="s">
-        <v>688</v>
-      </c>
       <c r="J354" t="s">
-        <v>59</v>
+        <v>351</v>
       </c>
       <c r="K354" t="s">
-        <v>59</v>
+        <v>351</v>
       </c>
       <c r="L354" t="s">
         <v>34</v>
@@ -22609,13 +22609,13 @@
         <v>46</v>
       </c>
       <c r="O354" t="s">
-        <v>233</v>
+        <v>34</v>
       </c>
       <c r="P354" t="s">
-        <v>688</v>
+        <v>34</v>
       </c>
       <c r="Q354" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R354" t="s">
         <v>34</v>
@@ -22635,7 +22635,7 @@
         <v>34</v>
       </c>
       <c r="E355" t="s">
-        <v>258</v>
+        <v>300</v>
       </c>
       <c r="F355" t="s">
         <v>207</v>
@@ -22644,16 +22644,16 @@
         <v>40</v>
       </c>
       <c r="H355" t="s">
+        <v>686</v>
+      </c>
+      <c r="I355" t="s">
         <v>687</v>
       </c>
-      <c r="I355" t="s">
-        <v>688</v>
-      </c>
       <c r="J355" t="s">
-        <v>452</v>
+        <v>302</v>
       </c>
       <c r="K355" t="s">
-        <v>452</v>
+        <v>247</v>
       </c>
       <c r="L355" t="s">
         <v>34</v>
@@ -22665,10 +22665,10 @@
         <v>46</v>
       </c>
       <c r="O355" t="s">
-        <v>88</v>
+        <v>303</v>
       </c>
       <c r="P355" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Q355" t="s">
         <v>46</v>
@@ -22691,25 +22691,25 @@
         <v>34</v>
       </c>
       <c r="E356" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F356" t="s">
+        <v>207</v>
+      </c>
+      <c r="G356" t="s">
+        <v>40</v>
+      </c>
+      <c r="H356" t="s">
         <v>686</v>
       </c>
-      <c r="G356" t="s">
-        <v>40</v>
-      </c>
-      <c r="H356" t="s">
+      <c r="I356" t="s">
         <v>687</v>
       </c>
-      <c r="I356" t="s">
-        <v>688</v>
-      </c>
       <c r="J356" t="s">
-        <v>359</v>
+        <v>59</v>
       </c>
       <c r="K356" t="s">
-        <v>359</v>
+        <v>59</v>
       </c>
       <c r="L356" t="s">
         <v>34</v>
@@ -22721,13 +22721,13 @@
         <v>46</v>
       </c>
       <c r="O356" t="s">
-        <v>34</v>
+        <v>138</v>
       </c>
       <c r="P356" t="s">
-        <v>34</v>
+        <v>687</v>
       </c>
       <c r="Q356" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R356" t="s">
         <v>34</v>
@@ -22756,10 +22756,10 @@
         <v>40</v>
       </c>
       <c r="H357" t="s">
+        <v>686</v>
+      </c>
+      <c r="I357" t="s">
         <v>687</v>
-      </c>
-      <c r="I357" t="s">
-        <v>688</v>
       </c>
       <c r="J357" t="s">
         <v>74</v>
@@ -22780,7 +22780,7 @@
         <v>106</v>
       </c>
       <c r="P357" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Q357" t="s">
         <v>46</v>
@@ -22803,25 +22803,25 @@
         <v>34</v>
       </c>
       <c r="E358" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="F358" t="s">
+        <v>207</v>
+      </c>
+      <c r="G358" t="s">
+        <v>40</v>
+      </c>
+      <c r="H358" t="s">
         <v>686</v>
       </c>
-      <c r="G358" t="s">
-        <v>40</v>
-      </c>
-      <c r="H358" t="s">
+      <c r="I358" t="s">
         <v>687</v>
       </c>
-      <c r="I358" t="s">
-        <v>688</v>
-      </c>
       <c r="J358" t="s">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="K358" t="s">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="L358" t="s">
         <v>34</v>
@@ -22833,13 +22833,13 @@
         <v>46</v>
       </c>
       <c r="O358" t="s">
-        <v>34</v>
+        <v>288</v>
       </c>
       <c r="P358" t="s">
-        <v>34</v>
+        <v>687</v>
       </c>
       <c r="Q358" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R358" t="s">
         <v>34</v>
@@ -22859,25 +22859,25 @@
         <v>34</v>
       </c>
       <c r="E359" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="F359" t="s">
+        <v>688</v>
+      </c>
+      <c r="G359" t="s">
+        <v>40</v>
+      </c>
+      <c r="H359" t="s">
         <v>686</v>
       </c>
-      <c r="G359" t="s">
-        <v>40</v>
-      </c>
-      <c r="H359" t="s">
+      <c r="I359" t="s">
         <v>687</v>
       </c>
-      <c r="I359" t="s">
-        <v>688</v>
-      </c>
       <c r="J359" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="K359" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="L359" t="s">
         <v>34</v>
@@ -22915,19 +22915,19 @@
         <v>34</v>
       </c>
       <c r="E360" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="F360" t="s">
+        <v>688</v>
+      </c>
+      <c r="G360" t="s">
+        <v>40</v>
+      </c>
+      <c r="H360" t="s">
         <v>686</v>
       </c>
-      <c r="G360" t="s">
-        <v>40</v>
-      </c>
-      <c r="H360" t="s">
+      <c r="I360" t="s">
         <v>687</v>
-      </c>
-      <c r="I360" t="s">
-        <v>688</v>
       </c>
       <c r="J360" t="s">
         <v>59</v>
@@ -22971,25 +22971,25 @@
         <v>34</v>
       </c>
       <c r="E361" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F361" t="s">
+        <v>207</v>
+      </c>
+      <c r="G361" t="s">
+        <v>40</v>
+      </c>
+      <c r="H361" t="s">
         <v>686</v>
       </c>
-      <c r="G361" t="s">
-        <v>40</v>
-      </c>
-      <c r="H361" t="s">
+      <c r="I361" t="s">
         <v>687</v>
-      </c>
-      <c r="I361" t="s">
-        <v>688</v>
       </c>
       <c r="J361" t="s">
         <v>59</v>
       </c>
       <c r="K361" t="s">
-        <v>247</v>
+        <v>59</v>
       </c>
       <c r="L361" t="s">
         <v>34</v>
@@ -23001,13 +23001,13 @@
         <v>46</v>
       </c>
       <c r="O361" t="s">
-        <v>34</v>
+        <v>281</v>
       </c>
       <c r="P361" t="s">
-        <v>34</v>
+        <v>687</v>
       </c>
       <c r="Q361" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R361" t="s">
         <v>34</v>
@@ -23027,25 +23027,25 @@
         <v>34</v>
       </c>
       <c r="E362" t="s">
-        <v>234</v>
+        <v>291</v>
       </c>
       <c r="F362" t="s">
+        <v>207</v>
+      </c>
+      <c r="G362" t="s">
+        <v>40</v>
+      </c>
+      <c r="H362" t="s">
         <v>686</v>
       </c>
-      <c r="G362" t="s">
-        <v>40</v>
-      </c>
-      <c r="H362" t="s">
+      <c r="I362" t="s">
         <v>687</v>
       </c>
-      <c r="I362" t="s">
-        <v>688</v>
-      </c>
       <c r="J362" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="K362" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="L362" t="s">
         <v>34</v>
@@ -23057,13 +23057,13 @@
         <v>46</v>
       </c>
       <c r="O362" t="s">
-        <v>34</v>
+        <v>233</v>
       </c>
       <c r="P362" t="s">
-        <v>34</v>
+        <v>687</v>
       </c>
       <c r="Q362" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R362" t="s">
         <v>34</v>
@@ -23083,25 +23083,25 @@
         <v>34</v>
       </c>
       <c r="E363" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="F363" t="s">
+        <v>207</v>
+      </c>
+      <c r="G363" t="s">
+        <v>40</v>
+      </c>
+      <c r="H363" t="s">
         <v>686</v>
       </c>
-      <c r="G363" t="s">
-        <v>40</v>
-      </c>
-      <c r="H363" t="s">
+      <c r="I363" t="s">
         <v>687</v>
       </c>
-      <c r="I363" t="s">
-        <v>688</v>
-      </c>
       <c r="J363" t="s">
-        <v>59</v>
+        <v>452</v>
       </c>
       <c r="K363" t="s">
-        <v>59</v>
+        <v>452</v>
       </c>
       <c r="L363" t="s">
         <v>34</v>
@@ -23113,13 +23113,13 @@
         <v>46</v>
       </c>
       <c r="O363" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="P363" t="s">
-        <v>34</v>
+        <v>687</v>
       </c>
       <c r="Q363" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R363" t="s">
         <v>34</v>
@@ -23139,25 +23139,25 @@
         <v>34</v>
       </c>
       <c r="E364" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
       <c r="F364" t="s">
-        <v>207</v>
+        <v>688</v>
       </c>
       <c r="G364" t="s">
         <v>40</v>
       </c>
       <c r="H364" t="s">
+        <v>686</v>
+      </c>
+      <c r="I364" t="s">
         <v>687</v>
       </c>
-      <c r="I364" t="s">
-        <v>688</v>
-      </c>
       <c r="J364" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="K364" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="L364" t="s">
         <v>34</v>
@@ -23169,13 +23169,13 @@
         <v>46</v>
       </c>
       <c r="O364" t="s">
-        <v>288</v>
+        <v>34</v>
       </c>
       <c r="P364" t="s">
-        <v>688</v>
+        <v>34</v>
       </c>
       <c r="Q364" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="R364" t="s">
         <v>34</v>
@@ -23198,16 +23198,16 @@
         <v>320</v>
       </c>
       <c r="F365" t="s">
+        <v>688</v>
+      </c>
+      <c r="G365" t="s">
+        <v>40</v>
+      </c>
+      <c r="H365" t="s">
         <v>686</v>
       </c>
-      <c r="G365" t="s">
-        <v>40</v>
-      </c>
-      <c r="H365" t="s">
+      <c r="I365" t="s">
         <v>687</v>
-      </c>
-      <c r="I365" t="s">
-        <v>688</v>
       </c>
       <c r="J365" t="s">
         <v>74</v>
@@ -23546,13 +23546,13 @@
         <v>711</v>
       </c>
       <c r="J371" t="s">
-        <v>367</v>
+        <v>712</v>
       </c>
       <c r="K371" t="s">
-        <v>363</v>
+        <v>318</v>
       </c>
       <c r="L371" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M371" t="s">
         <v>707</v>
@@ -23596,19 +23596,19 @@
         <v>40</v>
       </c>
       <c r="H372" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="I372" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="J372" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="K372" t="s">
         <v>117</v>
       </c>
       <c r="L372" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M372" t="s">
         <v>707</v>
@@ -23620,7 +23620,7 @@
         <v>47</v>
       </c>
       <c r="P372" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Q372" t="s">
         <v>46</v>
@@ -23643,7 +23643,7 @@
         <v>34</v>
       </c>
       <c r="E373" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="F373" t="s">
         <v>207</v>
@@ -23652,19 +23652,19 @@
         <v>40</v>
       </c>
       <c r="H373" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="I373" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="J373" t="s">
-        <v>719</v>
+        <v>216</v>
       </c>
       <c r="K373" t="s">
-        <v>318</v>
+        <v>175</v>
       </c>
       <c r="L373" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M373" t="s">
         <v>707</v>
@@ -23676,7 +23676,7 @@
         <v>47</v>
       </c>
       <c r="P373" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="Q373" t="s">
         <v>46</v>
@@ -23699,7 +23699,7 @@
         <v>34</v>
       </c>
       <c r="E374" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="F374" t="s">
         <v>207</v>
@@ -23714,10 +23714,10 @@
         <v>723</v>
       </c>
       <c r="J374" t="s">
-        <v>216</v>
+        <v>367</v>
       </c>
       <c r="K374" t="s">
-        <v>175</v>
+        <v>363</v>
       </c>
       <c r="L374" t="s">
         <v>724</v>
@@ -23994,7 +23994,7 @@
         <v>122</v>
       </c>
       <c r="J379" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="K379" t="s">
         <v>363</v>
@@ -24147,25 +24147,25 @@
         <v>33</v>
       </c>
       <c r="E382" t="s">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="F382" t="s">
-        <v>207</v>
+        <v>39</v>
       </c>
       <c r="G382" t="s">
         <v>40</v>
       </c>
       <c r="H382" t="s">
-        <v>744</v>
+        <v>535</v>
       </c>
       <c r="I382" t="s">
         <v>745</v>
       </c>
       <c r="J382" t="s">
-        <v>719</v>
+        <v>318</v>
       </c>
       <c r="K382" t="s">
-        <v>363</v>
+        <v>318</v>
       </c>
       <c r="L382" t="s">
         <v>746</v>
@@ -24218,7 +24218,7 @@
         <v>748</v>
       </c>
       <c r="J383" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="K383" t="s">
         <v>363</v>
@@ -24274,7 +24274,7 @@
         <v>751</v>
       </c>
       <c r="J384" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="K384" t="s">
         <v>363</v>
@@ -24315,7 +24315,7 @@
         <v>34</v>
       </c>
       <c r="E385" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="F385" t="s">
         <v>207</v>
@@ -24324,13 +24324,13 @@
         <v>40</v>
       </c>
       <c r="H385" t="s">
-        <v>473</v>
+        <v>753</v>
       </c>
       <c r="I385" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="J385" t="s">
-        <v>754</v>
+        <v>712</v>
       </c>
       <c r="K385" t="s">
         <v>363</v>
@@ -24348,7 +24348,7 @@
         <v>47</v>
       </c>
       <c r="P385" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="Q385" t="s">
         <v>46</v>
@@ -24380,7 +24380,7 @@
         <v>40</v>
       </c>
       <c r="H386" t="s">
-        <v>535</v>
+        <v>589</v>
       </c>
       <c r="I386" t="s">
         <v>757</v>
@@ -24389,10 +24389,10 @@
         <v>318</v>
       </c>
       <c r="K386" t="s">
-        <v>318</v>
+        <v>452</v>
       </c>
       <c r="L386" t="s">
-        <v>758</v>
+        <v>34</v>
       </c>
       <c r="M386" t="s">
         <v>743</v>
@@ -24427,28 +24427,28 @@
         <v>34</v>
       </c>
       <c r="E387" t="s">
+        <v>182</v>
+      </c>
+      <c r="F387" t="s">
+        <v>207</v>
+      </c>
+      <c r="G387" t="s">
+        <v>40</v>
+      </c>
+      <c r="H387" t="s">
+        <v>539</v>
+      </c>
+      <c r="I387" t="s">
+        <v>758</v>
+      </c>
+      <c r="J387" t="s">
         <v>759</v>
       </c>
-      <c r="F387" t="s">
-        <v>39</v>
-      </c>
-      <c r="G387" t="s">
-        <v>40</v>
-      </c>
-      <c r="H387" t="s">
-        <v>586</v>
-      </c>
-      <c r="I387" t="s">
+      <c r="K387" t="s">
+        <v>363</v>
+      </c>
+      <c r="L387" t="s">
         <v>760</v>
-      </c>
-      <c r="J387" t="s">
-        <v>318</v>
-      </c>
-      <c r="K387" t="s">
-        <v>452</v>
-      </c>
-      <c r="L387" t="s">
-        <v>34</v>
       </c>
       <c r="M387" t="s">
         <v>743</v>
@@ -24460,7 +24460,7 @@
         <v>47</v>
       </c>
       <c r="P387" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="Q387" t="s">
         <v>46</v>
@@ -24483,7 +24483,7 @@
         <v>34</v>
       </c>
       <c r="E388" t="s">
-        <v>182</v>
+        <v>718</v>
       </c>
       <c r="F388" t="s">
         <v>207</v>
@@ -24492,7 +24492,7 @@
         <v>40</v>
       </c>
       <c r="H388" t="s">
-        <v>539</v>
+        <v>473</v>
       </c>
       <c r="I388" t="s">
         <v>761</v>
@@ -24539,7 +24539,7 @@
         <v>34</v>
       </c>
       <c r="E389" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="F389" t="s">
         <v>39</v>
@@ -24548,16 +24548,16 @@
         <v>40</v>
       </c>
       <c r="H389" t="s">
-        <v>578</v>
+        <v>764</v>
       </c>
       <c r="I389" t="s">
-        <v>122</v>
+        <v>765</v>
       </c>
       <c r="J389" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="K389" t="s">
-        <v>318</v>
+        <v>97</v>
       </c>
       <c r="L389" t="s">
         <v>34</v>
@@ -24572,7 +24572,7 @@
         <v>47</v>
       </c>
       <c r="P389" t="s">
-        <v>122</v>
+        <v>765</v>
       </c>
       <c r="Q389" t="s">
         <v>46</v>
@@ -24595,7 +24595,7 @@
         <v>34</v>
       </c>
       <c r="E390" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="F390" t="s">
         <v>39</v>
@@ -24604,16 +24604,16 @@
         <v>40</v>
       </c>
       <c r="H390" t="s">
-        <v>766</v>
+        <v>527</v>
       </c>
       <c r="I390" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="J390" t="s">
-        <v>768</v>
+        <v>318</v>
       </c>
       <c r="K390" t="s">
-        <v>97</v>
+        <v>318</v>
       </c>
       <c r="L390" t="s">
         <v>34</v>
@@ -24628,7 +24628,7 @@
         <v>47</v>
       </c>
       <c r="P390" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="Q390" t="s">
         <v>46</v>
@@ -24651,28 +24651,28 @@
         <v>34</v>
       </c>
       <c r="E391" t="s">
+        <v>182</v>
+      </c>
+      <c r="F391" t="s">
+        <v>207</v>
+      </c>
+      <c r="G391" t="s">
+        <v>40</v>
+      </c>
+      <c r="H391" t="s">
+        <v>543</v>
+      </c>
+      <c r="I391" t="s">
+        <v>768</v>
+      </c>
+      <c r="J391" t="s">
         <v>769</v>
       </c>
-      <c r="F391" t="s">
-        <v>39</v>
-      </c>
-      <c r="G391" t="s">
-        <v>40</v>
-      </c>
-      <c r="H391" t="s">
-        <v>527</v>
-      </c>
-      <c r="I391" t="s">
+      <c r="K391" t="s">
+        <v>363</v>
+      </c>
+      <c r="L391" t="s">
         <v>770</v>
-      </c>
-      <c r="J391" t="s">
-        <v>318</v>
-      </c>
-      <c r="K391" t="s">
-        <v>318</v>
-      </c>
-      <c r="L391" t="s">
-        <v>34</v>
       </c>
       <c r="M391" t="s">
         <v>743</v>
@@ -24684,7 +24684,7 @@
         <v>47</v>
       </c>
       <c r="P391" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="Q391" t="s">
         <v>46</v>
@@ -24719,16 +24719,16 @@
         <v>771</v>
       </c>
       <c r="I392" t="s">
-        <v>122</v>
+        <v>772</v>
       </c>
       <c r="J392" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="K392" t="s">
         <v>363</v>
       </c>
       <c r="L392" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="M392" t="s">
         <v>743</v>
@@ -24740,7 +24740,7 @@
         <v>47</v>
       </c>
       <c r="P392" t="s">
-        <v>122</v>
+        <v>772</v>
       </c>
       <c r="Q392" t="s">
         <v>46</v>
@@ -24763,28 +24763,28 @@
         <v>34</v>
       </c>
       <c r="E393" t="s">
-        <v>182</v>
+        <v>774</v>
       </c>
       <c r="F393" t="s">
-        <v>207</v>
+        <v>39</v>
       </c>
       <c r="G393" t="s">
         <v>40</v>
       </c>
       <c r="H393" t="s">
-        <v>543</v>
+        <v>578</v>
       </c>
       <c r="I393" t="s">
-        <v>770</v>
+        <v>122</v>
       </c>
       <c r="J393" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="K393" t="s">
-        <v>363</v>
+        <v>318</v>
       </c>
       <c r="L393" t="s">
-        <v>774</v>
+        <v>34</v>
       </c>
       <c r="M393" t="s">
         <v>743</v>
@@ -24796,7 +24796,7 @@
         <v>47</v>
       </c>
       <c r="P393" t="s">
-        <v>770</v>
+        <v>122</v>
       </c>
       <c r="Q393" t="s">
         <v>46</v>
@@ -24828,13 +24828,13 @@
         <v>40</v>
       </c>
       <c r="H394" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="I394" t="s">
-        <v>776</v>
+        <v>122</v>
       </c>
       <c r="J394" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="K394" t="s">
         <v>363</v>
@@ -24852,7 +24852,7 @@
         <v>47</v>
       </c>
       <c r="P394" t="s">
-        <v>776</v>
+        <v>122</v>
       </c>
       <c r="Q394" t="s">
         <v>46</v>
@@ -24890,7 +24890,7 @@
         <v>779</v>
       </c>
       <c r="J395" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="K395" t="s">
         <v>363</v>
@@ -24996,10 +24996,10 @@
         <v>40</v>
       </c>
       <c r="H397" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="I397" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="J397" t="s">
         <v>210</v>
@@ -25020,7 +25020,7 @@
         <v>47</v>
       </c>
       <c r="P397" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="Q397" t="s">
         <v>46</v>
@@ -25108,10 +25108,10 @@
         <v>40</v>
       </c>
       <c r="H399" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I399" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="J399" t="s">
         <v>210</v>
@@ -25132,7 +25132,7 @@
         <v>47</v>
       </c>
       <c r="P399" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Q399" t="s">
         <v>46</v>
@@ -25382,7 +25382,7 @@
         <v>806</v>
       </c>
       <c r="F404" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="G404" t="s">
         <v>40</v>
@@ -25438,7 +25438,7 @@
         <v>206</v>
       </c>
       <c r="F405" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="G405" t="s">
         <v>40</v>
@@ -25668,7 +25668,7 @@
         <v>40</v>
       </c>
       <c r="H409" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
       <c r="I409" t="s">
         <v>819</v>
@@ -25724,7 +25724,7 @@
         <v>40</v>
       </c>
       <c r="H410" t="s">
-        <v>473</v>
+        <v>535</v>
       </c>
       <c r="I410" t="s">
         <v>821</v>
@@ -25898,7 +25898,7 @@
         <v>830</v>
       </c>
       <c r="J413" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="K413" t="s">
         <v>318</v>
@@ -25948,7 +25948,7 @@
         <v>40</v>
       </c>
       <c r="H414" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="I414" t="s">
         <v>835</v>
@@ -26178,7 +26178,7 @@
         <v>848</v>
       </c>
       <c r="J418" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="K418" t="s">
         <v>363</v>
@@ -26346,7 +26346,7 @@
         <v>860</v>
       </c>
       <c r="J421" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="K421" t="s">
         <v>861</v>
@@ -26458,7 +26458,7 @@
         <v>867</v>
       </c>
       <c r="J423" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="K423" t="s">
         <v>318</v>
@@ -26570,7 +26570,7 @@
         <v>874</v>
       </c>
       <c r="J425" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K425" t="s">
         <v>74</v>
@@ -26620,19 +26620,19 @@
         <v>40</v>
       </c>
       <c r="H426" t="s">
+        <v>473</v>
+      </c>
+      <c r="I426" t="s">
         <v>876</v>
       </c>
-      <c r="I426" t="s">
+      <c r="J426" t="s">
+        <v>101</v>
+      </c>
+      <c r="K426" t="s">
+        <v>175</v>
+      </c>
+      <c r="L426" t="s">
         <v>877</v>
-      </c>
-      <c r="J426" t="s">
-        <v>335</v>
-      </c>
-      <c r="K426" t="s">
-        <v>558</v>
-      </c>
-      <c r="L426" t="s">
-        <v>878</v>
       </c>
       <c r="M426" t="s">
         <v>871</v>
@@ -26644,7 +26644,7 @@
         <v>47</v>
       </c>
       <c r="P426" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="Q426" t="s">
         <v>46</v>
@@ -26667,7 +26667,7 @@
         <v>34</v>
       </c>
       <c r="E427" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F427" t="s">
         <v>39</v>
@@ -26676,16 +26676,16 @@
         <v>40</v>
       </c>
       <c r="H427" t="s">
-        <v>473</v>
+        <v>879</v>
       </c>
       <c r="I427" t="s">
         <v>880</v>
       </c>
       <c r="J427" t="s">
-        <v>101</v>
+        <v>330</v>
       </c>
       <c r="K427" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="L427" t="s">
         <v>881</v>
@@ -26732,19 +26732,19 @@
         <v>40</v>
       </c>
       <c r="H428" t="s">
+        <v>324</v>
+      </c>
+      <c r="I428" t="s">
         <v>883</v>
       </c>
-      <c r="I428" t="s">
+      <c r="J428" t="s">
+        <v>58</v>
+      </c>
+      <c r="K428" t="s">
+        <v>175</v>
+      </c>
+      <c r="L428" t="s">
         <v>884</v>
-      </c>
-      <c r="J428" t="s">
-        <v>335</v>
-      </c>
-      <c r="K428" t="s">
-        <v>156</v>
-      </c>
-      <c r="L428" t="s">
-        <v>885</v>
       </c>
       <c r="M428" t="s">
         <v>871</v>
@@ -26756,7 +26756,7 @@
         <v>47</v>
       </c>
       <c r="P428" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="Q428" t="s">
         <v>46</v>
@@ -26779,7 +26779,7 @@
         <v>34</v>
       </c>
       <c r="E429" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F429" t="s">
         <v>39</v>
@@ -26788,16 +26788,16 @@
         <v>40</v>
       </c>
       <c r="H429" t="s">
-        <v>324</v>
+        <v>886</v>
       </c>
       <c r="I429" t="s">
         <v>887</v>
       </c>
       <c r="J429" t="s">
-        <v>58</v>
+        <v>330</v>
       </c>
       <c r="K429" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="L429" t="s">
         <v>888</v>
@@ -26850,10 +26850,10 @@
         <v>891</v>
       </c>
       <c r="J430" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K430" t="s">
-        <v>156</v>
+        <v>558</v>
       </c>
       <c r="L430" t="s">
         <v>892</v>
@@ -26906,7 +26906,7 @@
         <v>895</v>
       </c>
       <c r="J431" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K431" t="s">
         <v>156</v>
@@ -26962,7 +26962,7 @@
         <v>899</v>
       </c>
       <c r="J432" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="K432" t="s">
         <v>69</v>
@@ -27130,7 +27130,7 @@
         <v>911</v>
       </c>
       <c r="J435" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="K435" t="s">
         <v>363</v>
@@ -27351,7 +27351,7 @@
         <v>928</v>
       </c>
       <c r="I439" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="J439" t="s">
         <v>367</v>
@@ -27372,7 +27372,7 @@
         <v>47</v>
       </c>
       <c r="P439" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="Q439" t="s">
         <v>46</v>
@@ -27516,19 +27516,19 @@
         <v>40</v>
       </c>
       <c r="H442" t="s">
+        <v>922</v>
+      </c>
+      <c r="I442" t="s">
         <v>937</v>
       </c>
-      <c r="I442" t="s">
+      <c r="J442" t="s">
         <v>938</v>
       </c>
-      <c r="J442" t="s">
+      <c r="K442" t="s">
+        <v>363</v>
+      </c>
+      <c r="L442" t="s">
         <v>939</v>
-      </c>
-      <c r="K442" t="s">
-        <v>352</v>
-      </c>
-      <c r="L442" t="s">
-        <v>940</v>
       </c>
       <c r="M442" t="s">
         <v>927</v>
@@ -27540,7 +27540,7 @@
         <v>47</v>
       </c>
       <c r="P442" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="Q442" t="s">
         <v>46</v>
@@ -27563,7 +27563,7 @@
         <v>34</v>
       </c>
       <c r="E443" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F443" t="s">
         <v>207</v>
@@ -27572,7 +27572,7 @@
         <v>40</v>
       </c>
       <c r="H443" t="s">
-        <v>922</v>
+        <v>941</v>
       </c>
       <c r="I443" t="s">
         <v>942</v>
@@ -27581,7 +27581,7 @@
         <v>943</v>
       </c>
       <c r="K443" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="L443" t="s">
         <v>944</v>
@@ -27970,7 +27970,7 @@
         <v>970</v>
       </c>
       <c r="J450" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="K450" t="s">
         <v>363</v>
@@ -28194,7 +28194,7 @@
         <v>988</v>
       </c>
       <c r="J454" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="K454" t="s">
         <v>58</v>
@@ -28250,7 +28250,7 @@
         <v>992</v>
       </c>
       <c r="J455" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="K455" t="s">
         <v>363</v>
@@ -28306,7 +28306,7 @@
         <v>995</v>
       </c>
       <c r="J456" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="K456" t="s">
         <v>117</v>
@@ -28362,7 +28362,7 @@
         <v>1000</v>
       </c>
       <c r="J457" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="K457" t="s">
         <v>363</v>
@@ -28468,7 +28468,7 @@
         <v>40</v>
       </c>
       <c r="H459" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="I459" t="s">
         <v>1006</v>
@@ -28698,7 +28698,7 @@
         <v>1014</v>
       </c>
       <c r="J463" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K463" t="s">
         <v>558</v>
@@ -34693,7 +34693,7 @@
         <v>109</v>
       </c>
       <c r="K570" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="L570" t="s">
         <v>1147</v>

--- a/xlsx/dre/DRE_07_2026.xlsx
+++ b/xlsx/dre/DRE_07_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10102" uniqueCount="1157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10102" uniqueCount="1159">
   <si>
     <t>Movimentações Financeiras</t>
   </si>
@@ -615,7 +615,7 @@
     <t>4 CUSTOS E DESPESAS</t>
   </si>
   <si>
-    <t>R$ 797.086,03</t>
+    <t>R$ 790.718,54</t>
   </si>
   <si>
     <t>4.01 DEDUÇÕES DE RECEITA</t>
@@ -2017,10 +2017,28 @@
     <t>R$  43,64</t>
   </si>
   <si>
+    <t>R$  20,84</t>
+  </si>
+  <si>
     <t>R$  74,29</t>
   </si>
   <si>
-    <t>R$  20,84</t>
+    <t>ADM EF/0</t>
+  </si>
+  <si>
+    <t>R$  77,99</t>
+  </si>
+  <si>
+    <t>12/07/26</t>
+  </si>
+  <si>
+    <t>13301/0</t>
+  </si>
+  <si>
+    <t>R$  11,05</t>
+  </si>
+  <si>
+    <t>FlaviaCM0013301</t>
   </si>
   <si>
     <t>16003/0</t>
@@ -2029,12 +2047,18 @@
     <t>R$  66,90</t>
   </si>
   <si>
-    <t>12/07/26</t>
-  </si>
-  <si>
     <t>AnaCAL0016003</t>
   </si>
   <si>
+    <t>76901/0</t>
+  </si>
+  <si>
+    <t>R$  41,15</t>
+  </si>
+  <si>
+    <t>76901JoaoMCC</t>
+  </si>
+  <si>
     <t>49301/0</t>
   </si>
   <si>
@@ -2044,24 +2068,6 @@
     <t>49301GuilhermeBN</t>
   </si>
   <si>
-    <t>13301/0</t>
-  </si>
-  <si>
-    <t>R$  11,05</t>
-  </si>
-  <si>
-    <t>FlaviaCM0013301</t>
-  </si>
-  <si>
-    <t>76901/0</t>
-  </si>
-  <si>
-    <t>R$  41,15</t>
-  </si>
-  <si>
-    <t>76901JoaoMCC</t>
-  </si>
-  <si>
     <t>42001UB/0</t>
   </si>
   <si>
@@ -2069,12 +2075,6 @@
   </si>
   <si>
     <t>42001LaysSB</t>
-  </si>
-  <si>
-    <t>ADM EF/0</t>
-  </si>
-  <si>
-    <t>R$  77,99</t>
   </si>
   <si>
     <t>4.03.03.02 Agregados e outros gastos de montagens</t>
@@ -3106,7 +3106,7 @@
     <t>4.07 DESPESAS FINANCEIRAS VARIÁVEIS</t>
   </si>
   <si>
-    <t>R$ 50.601,76</t>
+    <t>R$ 44.234,27</t>
   </si>
   <si>
     <t>4.07.01 DESPESAS FINANCEIRAS VARIÁVEIS</t>
@@ -3121,73 +3121,79 @@
     <t>Italíneacredi</t>
   </si>
   <si>
-    <t>R$  1.247,55</t>
+    <t>R$  34,45</t>
   </si>
   <si>
     <t>Título referente a Valor da Taxa Financeira</t>
   </si>
   <si>
-    <t>R$  434,46</t>
-  </si>
-  <si>
-    <t>R$  990,70</t>
-  </si>
-  <si>
-    <t>R$  12.052,71</t>
-  </si>
-  <si>
-    <t>R$  55,77</t>
-  </si>
-  <si>
-    <t>R$  667,09</t>
-  </si>
-  <si>
-    <t>R$  3.546,50</t>
-  </si>
-  <si>
-    <t>R$  2.735,99</t>
-  </si>
-  <si>
-    <t>R$  3.852,58</t>
-  </si>
-  <si>
-    <t>R$  4.019,29</t>
-  </si>
-  <si>
-    <t>R$  3.328,95</t>
-  </si>
-  <si>
-    <t>R$  1.284,24</t>
-  </si>
-  <si>
-    <t>R$  1.222,02</t>
-  </si>
-  <si>
-    <t>R$  1.068,34</t>
-  </si>
-  <si>
-    <t>R$  6.909,31</t>
+    <t>R$  341,71</t>
+  </si>
+  <si>
+    <t>R$  938,57</t>
+  </si>
+  <si>
+    <t>R$  11.877,44</t>
+  </si>
+  <si>
+    <t>88401LAISCORREAOML</t>
+  </si>
+  <si>
+    <t>R$  3.861,51</t>
+  </si>
+  <si>
+    <t>R$  944,68</t>
+  </si>
+  <si>
+    <t>R$  4.217,37</t>
+  </si>
+  <si>
+    <t>R$  491,79</t>
+  </si>
+  <si>
+    <t>R$  2.489,40</t>
+  </si>
+  <si>
+    <t>R$  3.788,53</t>
+  </si>
+  <si>
+    <t>R$  694,73</t>
+  </si>
+  <si>
+    <t>R$  2.002,63</t>
+  </si>
+  <si>
+    <t>R$  49,35</t>
+  </si>
+  <si>
+    <t>R$  1.366,02</t>
+  </si>
+  <si>
+    <t>R$  1.186,15</t>
+  </si>
+  <si>
+    <t>R$  829,56</t>
+  </si>
+  <si>
+    <t>R$  3.962,01</t>
   </si>
   <si>
     <t>PAGSEGURO</t>
   </si>
   <si>
-    <t>R$  118,00</t>
-  </si>
-  <si>
-    <t>R$  3.917,20</t>
-  </si>
-  <si>
-    <t>R$  694,73</t>
-  </si>
-  <si>
-    <t>R$  987,17</t>
-  </si>
-  <si>
-    <t>R$  48,92</t>
-  </si>
-  <si>
-    <t>R$  1.420,24</t>
+    <t>R$  44,40</t>
+  </si>
+  <si>
+    <t>91201GUSTAVOMW</t>
+  </si>
+  <si>
+    <t>R$  941,95</t>
+  </si>
+  <si>
+    <t>R$  1.210,32</t>
+  </si>
+  <si>
+    <t>R$  2.961,70</t>
   </si>
   <si>
     <t>6.01 ATIVO</t>
@@ -3349,7 +3355,7 @@
     <t>7.08 (-) DESPESAS E RECEITAS FINANCEIRAS</t>
   </si>
   <si>
-    <t>R$ 50.608,50</t>
+    <t>R$ 44.241,01</t>
   </si>
   <si>
     <t>7.08.01 Despesas e receitas financeiras fixas</t>
@@ -3367,7 +3373,7 @@
     <t>7.09 = RESULTADO OPERACIONAL</t>
   </si>
   <si>
-    <t>R$ -38.904,99</t>
+    <t>R$ -32.537,50</t>
   </si>
   <si>
     <t>7.11 = RESULTADO LÍQUIDO DO EXERCÍCIO</t>
@@ -3382,7 +3388,7 @@
     <t>7.50.02 TOTAL DOS CUSTOS VARIÁVEIS</t>
   </si>
   <si>
-    <t>R$ 684.196,97</t>
+    <t>R$ 677.829,48</t>
   </si>
   <si>
     <t>7.50.02.01 Deduções de receita</t>
@@ -3415,13 +3421,13 @@
     <t>7.60.02 TOTAL DE VENDAS - VALOR À VISTA</t>
   </si>
   <si>
-    <t>R$ 707.579,28</t>
+    <t>R$ 713.946,77</t>
   </si>
   <si>
     <t>7.60.03 TOTAL DE VENDAS - VALOR LÍQUIDO</t>
   </si>
   <si>
-    <t>R$ 702.552,78</t>
+    <t>R$ 708.920,27</t>
   </si>
   <si>
     <t>7.60.06 CUSTO DAS VENDAS - MERCADORIA</t>
@@ -3448,7 +3454,7 @@
     <t>7.70 BREAK-EVEN POINT</t>
   </si>
   <si>
-    <t>R$ 1.156.875,32</t>
+    <t>R$ 1.065.198,30</t>
   </si>
   <si>
     <t>7.80.01 Mark Up Negociado</t>
@@ -3463,13 +3469,13 @@
     <t>7.80.02 Mark Up à Vista</t>
   </si>
   <si>
+    <t>2,39</t>
+  </si>
+  <si>
+    <t>7.80.03 Mark Up Líquido</t>
+  </si>
+  <si>
     <t>2,37</t>
-  </si>
-  <si>
-    <t>7.80.03 Mark Up Líquido</t>
-  </si>
-  <si>
-    <t>2,35</t>
   </si>
   <si>
     <t>9 NÃO OPERACIONAL</t>
@@ -21710,7 +21716,7 @@
         <v>34</v>
       </c>
       <c r="E338" t="s">
-        <v>84</v>
+        <v>316</v>
       </c>
       <c r="F338" t="s">
         <v>39</v>
@@ -21725,10 +21731,10 @@
         <v>665</v>
       </c>
       <c r="J338" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="K338" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="L338" t="s">
         <v>34</v>
@@ -21740,7 +21746,7 @@
         <v>46</v>
       </c>
       <c r="O338" t="s">
-        <v>88</v>
+        <v>319</v>
       </c>
       <c r="P338" t="s">
         <v>665</v>
@@ -21766,7 +21772,7 @@
         <v>34</v>
       </c>
       <c r="E339" t="s">
-        <v>316</v>
+        <v>84</v>
       </c>
       <c r="F339" t="s">
         <v>39</v>
@@ -21781,10 +21787,10 @@
         <v>666</v>
       </c>
       <c r="J339" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="K339" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="L339" t="s">
         <v>34</v>
@@ -21796,7 +21802,7 @@
         <v>46</v>
       </c>
       <c r="O339" t="s">
-        <v>319</v>
+        <v>88</v>
       </c>
       <c r="P339" t="s">
         <v>666</v>
@@ -21852,7 +21858,7 @@
         <v>46</v>
       </c>
       <c r="O340" t="s">
-        <v>670</v>
+        <v>47</v>
       </c>
       <c r="P340" t="s">
         <v>668</v>
@@ -21878,7 +21884,7 @@
         <v>34</v>
       </c>
       <c r="E341" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F341" t="s">
         <v>39</v>
@@ -21890,7 +21896,7 @@
         <v>663</v>
       </c>
       <c r="I341" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="J341" t="s">
         <v>332</v>
@@ -21908,10 +21914,10 @@
         <v>46</v>
       </c>
       <c r="O341" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="P341" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="Q341" t="s">
         <v>46</v>
@@ -21934,7 +21940,7 @@
         <v>34</v>
       </c>
       <c r="E342" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F342" t="s">
         <v>39</v>
@@ -21946,7 +21952,7 @@
         <v>663</v>
       </c>
       <c r="I342" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="J342" t="s">
         <v>332</v>
@@ -21964,10 +21970,10 @@
         <v>46</v>
       </c>
       <c r="O342" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="P342" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="Q342" t="s">
         <v>46</v>
@@ -21990,7 +21996,7 @@
         <v>34</v>
       </c>
       <c r="E343" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="F343" t="s">
         <v>39</v>
@@ -22002,7 +22008,7 @@
         <v>663</v>
       </c>
       <c r="I343" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J343" t="s">
         <v>332</v>
@@ -22020,10 +22026,10 @@
         <v>46</v>
       </c>
       <c r="O343" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="P343" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="Q343" t="s">
         <v>46</v>
@@ -22046,7 +22052,7 @@
         <v>34</v>
       </c>
       <c r="E344" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F344" t="s">
         <v>39</v>
@@ -22058,7 +22064,7 @@
         <v>663</v>
       </c>
       <c r="I344" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="J344" t="s">
         <v>332</v>
@@ -22076,10 +22082,10 @@
         <v>46</v>
       </c>
       <c r="O344" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="P344" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="Q344" t="s">
         <v>46</v>
@@ -22102,7 +22108,7 @@
         <v>34</v>
       </c>
       <c r="E345" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F345" t="s">
         <v>39</v>
@@ -22114,7 +22120,7 @@
         <v>663</v>
       </c>
       <c r="I345" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="J345" t="s">
         <v>332</v>
@@ -22132,10 +22138,10 @@
         <v>46</v>
       </c>
       <c r="O345" t="s">
-        <v>47</v>
+        <v>684</v>
       </c>
       <c r="P345" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q345" t="s">
         <v>46</v>
@@ -29214,10 +29220,10 @@
         <v>33</v>
       </c>
       <c r="E472" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="F472" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G472" t="s">
         <v>40</v>
@@ -29229,10 +29235,10 @@
         <v>1030</v>
       </c>
       <c r="J472" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="K472" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="L472" t="s">
         <v>1031</v>
@@ -29244,13 +29250,13 @@
         <v>46</v>
       </c>
       <c r="O472" t="s">
-        <v>34</v>
+        <v>525</v>
       </c>
       <c r="P472" t="s">
-        <v>34</v>
+        <v>1030</v>
       </c>
       <c r="Q472" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R472" t="s">
         <v>34</v>
@@ -29273,7 +29279,7 @@
         <v>250</v>
       </c>
       <c r="F473" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G473" t="s">
         <v>40</v>
@@ -29300,13 +29306,13 @@
         <v>46</v>
       </c>
       <c r="O473" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="P473" t="s">
-        <v>34</v>
+        <v>1032</v>
       </c>
       <c r="Q473" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R473" t="s">
         <v>34</v>
@@ -29326,10 +29332,10 @@
         <v>34</v>
       </c>
       <c r="E474" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="F474" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G474" t="s">
         <v>40</v>
@@ -29341,10 +29347,10 @@
         <v>1033</v>
       </c>
       <c r="J474" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="K474" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="L474" t="s">
         <v>1031</v>
@@ -29356,13 +29362,13 @@
         <v>46</v>
       </c>
       <c r="O474" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="P474" t="s">
-        <v>34</v>
+        <v>1033</v>
       </c>
       <c r="Q474" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R474" t="s">
         <v>34</v>
@@ -29385,7 +29391,7 @@
         <v>267</v>
       </c>
       <c r="F475" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G475" t="s">
         <v>40</v>
@@ -29412,13 +29418,13 @@
         <v>46</v>
       </c>
       <c r="O475" t="s">
-        <v>34</v>
+        <v>1035</v>
       </c>
       <c r="P475" t="s">
-        <v>34</v>
+        <v>1034</v>
       </c>
       <c r="Q475" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R475" t="s">
         <v>34</v>
@@ -29438,10 +29444,10 @@
         <v>34</v>
       </c>
       <c r="E476" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="F476" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G476" t="s">
         <v>40</v>
@@ -29450,13 +29456,13 @@
         <v>1029</v>
       </c>
       <c r="I476" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="J476" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="K476" t="s">
-        <v>233</v>
+        <v>59</v>
       </c>
       <c r="L476" t="s">
         <v>1031</v>
@@ -29468,13 +29474,13 @@
         <v>46</v>
       </c>
       <c r="O476" t="s">
-        <v>34</v>
+        <v>276</v>
       </c>
       <c r="P476" t="s">
-        <v>34</v>
+        <v>1036</v>
       </c>
       <c r="Q476" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R476" t="s">
         <v>34</v>
@@ -29494,10 +29500,10 @@
         <v>34</v>
       </c>
       <c r="E477" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="F477" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G477" t="s">
         <v>40</v>
@@ -29506,13 +29512,13 @@
         <v>1029</v>
       </c>
       <c r="I477" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="J477" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="K477" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="L477" t="s">
         <v>1031</v>
@@ -29524,13 +29530,13 @@
         <v>46</v>
       </c>
       <c r="O477" t="s">
-        <v>34</v>
+        <v>147</v>
       </c>
       <c r="P477" t="s">
-        <v>34</v>
+        <v>1037</v>
       </c>
       <c r="Q477" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R477" t="s">
         <v>34</v>
@@ -29550,10 +29556,10 @@
         <v>34</v>
       </c>
       <c r="E478" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F478" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G478" t="s">
         <v>40</v>
@@ -29562,13 +29568,13 @@
         <v>1029</v>
       </c>
       <c r="I478" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="J478" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="K478" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="L478" t="s">
         <v>1031</v>
@@ -29580,13 +29586,13 @@
         <v>46</v>
       </c>
       <c r="O478" t="s">
-        <v>34</v>
+        <v>478</v>
       </c>
       <c r="P478" t="s">
-        <v>34</v>
+        <v>1038</v>
       </c>
       <c r="Q478" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R478" t="s">
         <v>34</v>
@@ -29606,10 +29612,10 @@
         <v>34</v>
       </c>
       <c r="E479" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="F479" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G479" t="s">
         <v>40</v>
@@ -29618,13 +29624,13 @@
         <v>1029</v>
       </c>
       <c r="I479" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="J479" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="K479" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="L479" t="s">
         <v>1031</v>
@@ -29636,13 +29642,13 @@
         <v>46</v>
       </c>
       <c r="O479" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="P479" t="s">
-        <v>34</v>
+        <v>1039</v>
       </c>
       <c r="Q479" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R479" t="s">
         <v>34</v>
@@ -29662,10 +29668,10 @@
         <v>34</v>
       </c>
       <c r="E480" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="F480" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G480" t="s">
         <v>40</v>
@@ -29674,7 +29680,7 @@
         <v>1029</v>
       </c>
       <c r="I480" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="J480" t="s">
         <v>59</v>
@@ -29692,13 +29698,13 @@
         <v>46</v>
       </c>
       <c r="O480" t="s">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="P480" t="s">
-        <v>34</v>
+        <v>1040</v>
       </c>
       <c r="Q480" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R480" t="s">
         <v>34</v>
@@ -29718,10 +29724,10 @@
         <v>34</v>
       </c>
       <c r="E481" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F481" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G481" t="s">
         <v>40</v>
@@ -29730,13 +29736,13 @@
         <v>1029</v>
       </c>
       <c r="I481" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="J481" t="s">
         <v>59</v>
       </c>
       <c r="K481" t="s">
-        <v>233</v>
+        <v>59</v>
       </c>
       <c r="L481" t="s">
         <v>1031</v>
@@ -29748,13 +29754,13 @@
         <v>46</v>
       </c>
       <c r="O481" t="s">
-        <v>34</v>
+        <v>138</v>
       </c>
       <c r="P481" t="s">
-        <v>34</v>
+        <v>1041</v>
       </c>
       <c r="Q481" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R481" t="s">
         <v>34</v>
@@ -29774,10 +29780,10 @@
         <v>34</v>
       </c>
       <c r="E482" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="F482" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G482" t="s">
         <v>40</v>
@@ -29786,13 +29792,13 @@
         <v>1029</v>
       </c>
       <c r="I482" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="J482" t="s">
-        <v>59</v>
+        <v>298</v>
       </c>
       <c r="K482" t="s">
-        <v>59</v>
+        <v>233</v>
       </c>
       <c r="L482" t="s">
         <v>1031</v>
@@ -29804,13 +29810,13 @@
         <v>46</v>
       </c>
       <c r="O482" t="s">
-        <v>34</v>
+        <v>299</v>
       </c>
       <c r="P482" t="s">
-        <v>34</v>
+        <v>1042</v>
       </c>
       <c r="Q482" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R482" t="s">
         <v>34</v>
@@ -29830,10 +29836,10 @@
         <v>34</v>
       </c>
       <c r="E483" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="F483" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G483" t="s">
         <v>40</v>
@@ -29842,13 +29848,13 @@
         <v>1029</v>
       </c>
       <c r="I483" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="J483" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="K483" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="L483" t="s">
         <v>1031</v>
@@ -29860,13 +29866,13 @@
         <v>46</v>
       </c>
       <c r="O483" t="s">
-        <v>34</v>
+        <v>288</v>
       </c>
       <c r="P483" t="s">
-        <v>34</v>
+        <v>1043</v>
       </c>
       <c r="Q483" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R483" t="s">
         <v>34</v>
@@ -29886,10 +29892,10 @@
         <v>34</v>
       </c>
       <c r="E484" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="F484" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G484" t="s">
         <v>40</v>
@@ -29898,13 +29904,13 @@
         <v>1029</v>
       </c>
       <c r="I484" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="J484" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="K484" t="s">
-        <v>58</v>
+        <v>233</v>
       </c>
       <c r="L484" t="s">
         <v>1031</v>
@@ -29916,13 +29922,13 @@
         <v>46</v>
       </c>
       <c r="O484" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="P484" t="s">
-        <v>34</v>
+        <v>1044</v>
       </c>
       <c r="Q484" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R484" t="s">
         <v>34</v>
@@ -29942,10 +29948,10 @@
         <v>34</v>
       </c>
       <c r="E485" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="F485" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G485" t="s">
         <v>40</v>
@@ -29954,13 +29960,13 @@
         <v>1029</v>
       </c>
       <c r="I485" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="J485" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K485" t="s">
-        <v>59</v>
+        <v>233</v>
       </c>
       <c r="L485" t="s">
         <v>1031</v>
@@ -29972,13 +29978,13 @@
         <v>46</v>
       </c>
       <c r="O485" t="s">
-        <v>34</v>
+        <v>249</v>
       </c>
       <c r="P485" t="s">
-        <v>34</v>
+        <v>1045</v>
       </c>
       <c r="Q485" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R485" t="s">
         <v>34</v>
@@ -29998,10 +30004,10 @@
         <v>34</v>
       </c>
       <c r="E486" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="F486" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G486" t="s">
         <v>40</v>
@@ -30010,13 +30016,13 @@
         <v>1029</v>
       </c>
       <c r="I486" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="J486" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="K486" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="L486" t="s">
         <v>1031</v>
@@ -30028,13 +30034,13 @@
         <v>46</v>
       </c>
       <c r="O486" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="P486" t="s">
-        <v>34</v>
+        <v>1046</v>
       </c>
       <c r="Q486" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R486" t="s">
         <v>34</v>
@@ -30054,25 +30060,25 @@
         <v>34</v>
       </c>
       <c r="E487" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="F487" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G487" t="s">
         <v>40</v>
       </c>
       <c r="H487" t="s">
-        <v>1046</v>
+        <v>1029</v>
       </c>
       <c r="I487" t="s">
         <v>1047</v>
       </c>
       <c r="J487" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K487" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L487" t="s">
         <v>1031</v>
@@ -30084,13 +30090,13 @@
         <v>46</v>
       </c>
       <c r="O487" t="s">
-        <v>34</v>
+        <v>151</v>
       </c>
       <c r="P487" t="s">
-        <v>34</v>
+        <v>1047</v>
       </c>
       <c r="Q487" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R487" t="s">
         <v>34</v>
@@ -30110,10 +30116,10 @@
         <v>34</v>
       </c>
       <c r="E488" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="F488" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G488" t="s">
         <v>40</v>
@@ -30128,7 +30134,7 @@
         <v>59</v>
       </c>
       <c r="K488" t="s">
-        <v>59</v>
+        <v>233</v>
       </c>
       <c r="L488" t="s">
         <v>1031</v>
@@ -30140,13 +30146,13 @@
         <v>46</v>
       </c>
       <c r="O488" t="s">
-        <v>34</v>
+        <v>271</v>
       </c>
       <c r="P488" t="s">
-        <v>34</v>
+        <v>1048</v>
       </c>
       <c r="Q488" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R488" t="s">
         <v>34</v>
@@ -30166,7 +30172,7 @@
         <v>34</v>
       </c>
       <c r="E489" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="F489" t="s">
         <v>243</v>
@@ -30175,16 +30181,16 @@
         <v>40</v>
       </c>
       <c r="H489" t="s">
-        <v>1029</v>
+        <v>1049</v>
       </c>
       <c r="I489" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="J489" t="s">
-        <v>298</v>
+        <v>58</v>
       </c>
       <c r="K489" t="s">
-        <v>233</v>
+        <v>58</v>
       </c>
       <c r="L489" t="s">
         <v>1031</v>
@@ -30196,10 +30202,10 @@
         <v>46</v>
       </c>
       <c r="O489" t="s">
-        <v>299</v>
+        <v>1051</v>
       </c>
       <c r="P489" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="Q489" t="s">
         <v>46</v>
@@ -30222,10 +30228,10 @@
         <v>34</v>
       </c>
       <c r="E490" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="F490" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G490" t="s">
         <v>40</v>
@@ -30234,13 +30240,13 @@
         <v>1029</v>
       </c>
       <c r="I490" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="J490" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="K490" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="L490" t="s">
         <v>1031</v>
@@ -30252,13 +30258,13 @@
         <v>46</v>
       </c>
       <c r="O490" t="s">
-        <v>34</v>
+        <v>450</v>
       </c>
       <c r="P490" t="s">
-        <v>34</v>
+        <v>1052</v>
       </c>
       <c r="Q490" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R490" t="s">
         <v>34</v>
@@ -30278,10 +30284,10 @@
         <v>34</v>
       </c>
       <c r="E491" t="s">
-        <v>234</v>
+        <v>281</v>
       </c>
       <c r="F491" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G491" t="s">
         <v>40</v>
@@ -30290,13 +30296,13 @@
         <v>1029</v>
       </c>
       <c r="I491" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="J491" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="K491" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="L491" t="s">
         <v>1031</v>
@@ -30308,13 +30314,13 @@
         <v>46</v>
       </c>
       <c r="O491" t="s">
-        <v>34</v>
+        <v>283</v>
       </c>
       <c r="P491" t="s">
-        <v>34</v>
+        <v>1053</v>
       </c>
       <c r="Q491" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R491" t="s">
         <v>34</v>
@@ -30334,10 +30340,10 @@
         <v>34</v>
       </c>
       <c r="E492" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="F492" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="G492" t="s">
         <v>40</v>
@@ -30346,13 +30352,13 @@
         <v>1029</v>
       </c>
       <c r="I492" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="J492" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="K492" t="s">
-        <v>233</v>
+        <v>109</v>
       </c>
       <c r="L492" t="s">
         <v>1031</v>
@@ -30364,13 +30370,13 @@
         <v>46</v>
       </c>
       <c r="O492" t="s">
-        <v>34</v>
+        <v>491</v>
       </c>
       <c r="P492" t="s">
-        <v>34</v>
+        <v>1054</v>
       </c>
       <c r="Q492" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R492" t="s">
         <v>34</v>
@@ -30378,7 +30384,7 @@
     </row>
     <row r="493">
       <c r="A493" t="s" s="1">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="B493" t="s" s="1">
         <v>32</v>
@@ -30434,7 +30440,7 @@
     </row>
     <row r="494">
       <c r="A494" t="s" s="1">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B494" t="s" s="1">
         <v>32</v>
@@ -30490,7 +30496,7 @@
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B495" t="s">
         <v>32</v>
@@ -30546,7 +30552,7 @@
     </row>
     <row r="496">
       <c r="A496" t="s" s="1">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B496" t="s" s="1">
         <v>49</v>
@@ -30602,7 +30608,7 @@
     </row>
     <row r="497">
       <c r="A497" t="s" s="1">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="B497" t="s" s="1">
         <v>49</v>
@@ -30658,7 +30664,7 @@
     </row>
     <row r="498">
       <c r="A498" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B498" t="s">
         <v>49</v>
@@ -30714,7 +30720,7 @@
     </row>
     <row r="499">
       <c r="A499" t="s" s="1">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B499" t="s" s="1">
         <v>202</v>
@@ -30770,7 +30776,7 @@
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B500" t="s">
         <v>202</v>
@@ -30826,13 +30832,13 @@
     </row>
     <row r="501">
       <c r="A501" t="s" s="1">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B501" t="s" s="1">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="C501" t="s" s="1">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="D501" t="s" s="1">
         <v>33</v>
@@ -30882,7 +30888,7 @@
     </row>
     <row r="502">
       <c r="A502" t="s" s="1">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B502" t="s" s="1">
         <v>224</v>
@@ -30938,7 +30944,7 @@
     </row>
     <row r="503">
       <c r="A503" t="s" s="1">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B503" t="s" s="1">
         <v>226</v>
@@ -30994,7 +31000,7 @@
     </row>
     <row r="504">
       <c r="A504" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="B504" t="s">
         <v>226</v>
@@ -31050,7 +31056,7 @@
     </row>
     <row r="505">
       <c r="A505" t="s" s="1">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B505" t="s" s="1">
         <v>371</v>
@@ -31106,7 +31112,7 @@
     </row>
     <row r="506">
       <c r="A506" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B506" t="s">
         <v>371</v>
@@ -31162,13 +31168,13 @@
     </row>
     <row r="507">
       <c r="A507" t="s" s="1">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B507" t="s" s="1">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C507" t="s" s="1">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D507" t="s" s="1">
         <v>33</v>
@@ -31218,13 +31224,13 @@
     </row>
     <row r="508">
       <c r="A508" t="s" s="1">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B508" t="s" s="1">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C508" t="s" s="1">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="D508" t="s" s="1">
         <v>33</v>
@@ -31274,7 +31280,7 @@
     </row>
     <row r="509">
       <c r="A509" t="s" s="1">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B509" t="s" s="1">
         <v>458</v>
@@ -31330,7 +31336,7 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="1">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B510" t="s" s="1">
         <v>460</v>
@@ -31386,7 +31392,7 @@
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B511" t="s">
         <v>462</v>
@@ -31442,7 +31448,7 @@
     </row>
     <row r="512">
       <c r="A512" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="B512" t="s">
         <v>471</v>
@@ -31498,7 +31504,7 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="1">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B513" t="s" s="1">
         <v>652</v>
@@ -31554,7 +31560,7 @@
     </row>
     <row r="514">
       <c r="A514" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="B514" t="s">
         <v>652</v>
@@ -31610,7 +31616,7 @@
     </row>
     <row r="515">
       <c r="A515" t="s" s="1">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="B515" t="s" s="1">
         <v>659</v>
@@ -31666,7 +31672,7 @@
     </row>
     <row r="516">
       <c r="A516" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="B516" t="s">
         <v>661</v>
@@ -31722,7 +31728,7 @@
     </row>
     <row r="517">
       <c r="A517" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B517" t="s">
         <v>686</v>
@@ -31778,7 +31784,7 @@
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="B518" t="s">
         <v>693</v>
@@ -31834,7 +31840,7 @@
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="B519" t="s">
         <v>700</v>
@@ -31890,7 +31896,7 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="1">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="B520" t="s" s="1">
         <v>735</v>
@@ -31946,7 +31952,7 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="1">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B521" t="s" s="1">
         <v>737</v>
@@ -32002,7 +32008,7 @@
     </row>
     <row r="522">
       <c r="A522" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B522" t="s">
         <v>739</v>
@@ -32058,7 +32064,7 @@
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B523" t="s">
         <v>743</v>
@@ -32114,7 +32120,7 @@
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B524" t="s">
         <v>799</v>
@@ -32170,7 +32176,7 @@
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B525" t="s">
         <v>812</v>
@@ -32226,7 +32232,7 @@
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B526" t="s">
         <v>824</v>
@@ -32282,7 +32288,7 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="1">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B527" t="s" s="1">
         <v>832</v>
@@ -32338,7 +32344,7 @@
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B528" t="s">
         <v>834</v>
@@ -32394,7 +32400,7 @@
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="B529" t="s">
         <v>846</v>
@@ -32450,7 +32456,7 @@
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="B530" t="s">
         <v>854</v>
@@ -32506,7 +32512,7 @@
     </row>
     <row r="531">
       <c r="A531" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="B531" t="s">
         <v>860</v>
@@ -32562,7 +32568,7 @@
     </row>
     <row r="532">
       <c r="A532" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="B532" t="s">
         <v>873</v>
@@ -32618,7 +32624,7 @@
     </row>
     <row r="533">
       <c r="A533" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B533" t="s">
         <v>879</v>
@@ -32674,7 +32680,7 @@
     </row>
     <row r="534">
       <c r="A534" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="B534" t="s">
         <v>911</v>
@@ -32730,7 +32736,7 @@
     </row>
     <row r="535">
       <c r="A535" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B535" t="s">
         <v>935</v>
@@ -32786,7 +32792,7 @@
     </row>
     <row r="536">
       <c r="A536" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="B536" t="s">
         <v>962</v>
@@ -32842,7 +32848,7 @@
     </row>
     <row r="537">
       <c r="A537" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B537" t="s">
         <v>975</v>
@@ -32898,7 +32904,7 @@
     </row>
     <row r="538">
       <c r="A538" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B538" t="s">
         <v>987</v>
@@ -32954,7 +32960,7 @@
     </row>
     <row r="539">
       <c r="A539" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="B539" t="s">
         <v>1012</v>
@@ -33010,13 +33016,13 @@
     </row>
     <row r="540">
       <c r="A540" t="s" s="1">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B540" t="s" s="1">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C540" t="s" s="1">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D540" t="s" s="1">
         <v>33</v>
@@ -33066,13 +33072,13 @@
     </row>
     <row r="541">
       <c r="A541" t="s" s="1">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="B541" t="s" s="1">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="C541" t="s" s="1">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="D541" t="s" s="1">
         <v>33</v>
@@ -33122,7 +33128,7 @@
     </row>
     <row r="542">
       <c r="A542" t="s" s="1">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B542" t="s" s="1">
         <v>1017</v>
@@ -33178,7 +33184,7 @@
     </row>
     <row r="543">
       <c r="A543" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B543" t="s">
         <v>1017</v>
@@ -33234,7 +33240,7 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="1">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B544" t="s" s="1">
         <v>1025</v>
@@ -33290,7 +33296,7 @@
     </row>
     <row r="545">
       <c r="A545" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="B545" t="s">
         <v>1025</v>
@@ -33346,13 +33352,13 @@
     </row>
     <row r="546">
       <c r="A546" t="s" s="1">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B546" t="s" s="1">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C546" t="s" s="1">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="D546" t="s" s="1">
         <v>33</v>
@@ -33402,13 +33408,13 @@
     </row>
     <row r="547">
       <c r="A547" t="s" s="1">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B547" t="s" s="1">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C547" t="s" s="1">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="D547" t="s" s="1">
         <v>33</v>
@@ -33458,13 +33464,13 @@
     </row>
     <row r="548">
       <c r="A548" t="s" s="1">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="B548" t="s" s="1">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C548" t="s" s="1">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D548" t="s" s="1">
         <v>33</v>
@@ -33514,7 +33520,7 @@
     </row>
     <row r="549">
       <c r="A549" t="s" s="1">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="B549" t="s" s="1">
         <v>49</v>
@@ -33570,13 +33576,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="1">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B550" t="s" s="1">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="C550" t="s" s="1">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="D550" t="s" s="1">
         <v>33</v>
@@ -33626,7 +33632,7 @@
     </row>
     <row r="551">
       <c r="A551" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B551" t="s">
         <v>202</v>
@@ -33682,7 +33688,7 @@
     </row>
     <row r="552">
       <c r="A552" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B552" t="s">
         <v>224</v>
@@ -33738,7 +33744,7 @@
     </row>
     <row r="553">
       <c r="A553" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B553" t="s">
         <v>458</v>
@@ -33794,7 +33800,7 @@
     </row>
     <row r="554">
       <c r="A554" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="B554" t="s">
         <v>1025</v>
@@ -33850,13 +33856,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="1">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="B555" t="s" s="1">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="C555" t="s" s="1">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="D555" t="s" s="1">
         <v>33</v>
@@ -33906,7 +33912,7 @@
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B556" t="s">
         <v>735</v>
@@ -33962,7 +33968,7 @@
     </row>
     <row r="557">
       <c r="A557" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B557" t="s">
         <v>1017</v>
@@ -34018,7 +34024,7 @@
     </row>
     <row r="558">
       <c r="A558" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B558" t="s">
         <v>49</v>
@@ -34074,13 +34080,13 @@
     </row>
     <row r="559">
       <c r="A559" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B559" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="C559" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="D559" t="s">
         <v>33</v>
@@ -34130,13 +34136,13 @@
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="B560" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="C560" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="D560" t="s">
         <v>33</v>
@@ -34186,7 +34192,7 @@
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="B561" t="s">
         <v>226</v>
@@ -34242,7 +34248,7 @@
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B562" t="s">
         <v>460</v>
@@ -34298,7 +34304,7 @@
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="B563" t="s">
         <v>737</v>
@@ -34354,7 +34360,7 @@
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="B564" t="s">
         <v>834</v>
@@ -34410,7 +34416,7 @@
     </row>
     <row r="565">
       <c r="A565" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="B565" t="s">
         <v>202</v>
@@ -34466,13 +34472,13 @@
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B566" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C566" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D566" t="s">
         <v>33</v>
@@ -34522,13 +34528,13 @@
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="B567" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C567" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D567" t="s">
         <v>33</v>
@@ -34578,13 +34584,13 @@
     </row>
     <row r="568">
       <c r="A568" t="s" s="1">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="B568" t="s" s="1">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="C568" t="s" s="1">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D568" t="s" s="1">
         <v>33</v>
@@ -34634,16 +34640,16 @@
     </row>
     <row r="569">
       <c r="A569" t="s" s="1">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="B569" t="s" s="1">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="C569" t="s" s="1">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="D569" t="s" s="1">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="E569" t="s" s="1">
         <v>34</v>
@@ -34690,16 +34696,16 @@
     </row>
     <row r="570">
       <c r="A570" t="s" s="1">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="B570" t="s" s="1">
+        <v>1146</v>
+      </c>
+      <c r="C570" t="s" s="1">
+        <v>1146</v>
+      </c>
+      <c r="D570" t="s" s="1">
         <v>1144</v>
-      </c>
-      <c r="C570" t="s" s="1">
-        <v>1144</v>
-      </c>
-      <c r="D570" t="s" s="1">
-        <v>1142</v>
       </c>
       <c r="E570" t="s" s="1">
         <v>34</v>
@@ -34746,16 +34752,16 @@
     </row>
     <row r="571">
       <c r="A571" t="s" s="1">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="B571" t="s" s="1">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="C571" t="s" s="1">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="D571" t="s" s="1">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="E571" t="s" s="1">
         <v>34</v>
@@ -34802,13 +34808,13 @@
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="B572" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="C572" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="D572" t="s">
         <v>33</v>
@@ -34858,19 +34864,19 @@
     </row>
     <row r="573">
       <c r="A573" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B573" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="C573" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="D573" t="s">
         <v>33</v>
       </c>
       <c r="E573" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="F573" t="s">
         <v>39</v>
@@ -34879,7 +34885,7 @@
         <v>40</v>
       </c>
       <c r="H573" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="I573" t="s">
         <v>57</v>
@@ -34891,10 +34897,10 @@
         <v>175</v>
       </c>
       <c r="L573" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="M573" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="N573" t="s">
         <v>46</v>
@@ -34914,7 +34920,7 @@
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B574" t="s">
         <v>34</v>
@@ -34926,7 +34932,7 @@
         <v>34</v>
       </c>
       <c r="E574" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="F574" t="s">
         <v>39</v>
@@ -34935,7 +34941,7 @@
         <v>40</v>
       </c>
       <c r="H574" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="I574" t="s">
         <v>57</v>
@@ -34947,10 +34953,10 @@
         <v>91</v>
       </c>
       <c r="L574" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="M574" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="N574" t="s">
         <v>46</v>
@@ -34970,7 +34976,7 @@
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B575" t="s">
         <v>34</v>
@@ -34982,7 +34988,7 @@
         <v>34</v>
       </c>
       <c r="E575" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="F575" t="s">
         <v>39</v>
@@ -34991,7 +34997,7 @@
         <v>40</v>
       </c>
       <c r="H575" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="I575" t="s">
         <v>174</v>
@@ -35003,10 +35009,10 @@
         <v>342</v>
       </c>
       <c r="L575" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="M575" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="N575" t="s">
         <v>46</v>
